--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/06,26/26,06,26 ПОКОМ ЗПФ/Копия дв 250626 бррсч пок зпф от Боярко.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/06,26/26,06,26 ПОКОМ ЗПФ/Копия дв 250626 бррсч пок зпф от Боярко.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\06,26\26,06,26 ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FDD4CE-F747-48B2-816C-2E96BD0373CC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{432BB1E5-59B6-439A-9518-4DED38F60F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,15 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AK$68</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -702,7 +694,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -736,13 +728,8 @@
     <xf numFmtId="2" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1063,7 +1050,7 @@
     <col min="13" max="14" width="0.85546875" customWidth="1"/>
     <col min="15" max="16" width="6" customWidth="1"/>
     <col min="17" max="17" width="7" customWidth="1"/>
-    <col min="18" max="18" width="7" style="37" customWidth="1"/>
+    <col min="18" max="18" width="7" style="32" customWidth="1"/>
     <col min="19" max="19" width="7" customWidth="1"/>
     <col min="20" max="20" width="9.42578125" customWidth="1"/>
     <col min="21" max="21" width="7" customWidth="1"/>
@@ -1099,8 +1086,8 @@
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
-      <c r="S1" s="38">
-        <v>1.44</v>
+      <c r="S1" s="33">
+        <v>0.83</v>
       </c>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
@@ -1440,11 +1427,11 @@
       </c>
       <c r="S5" s="4">
         <f t="shared" si="0"/>
-        <v>21917.779200000001</v>
+        <v>13619.562199999997</v>
       </c>
       <c r="T5" s="4">
         <f t="shared" si="0"/>
-        <v>22629.8</v>
+        <v>14001.8</v>
       </c>
       <c r="U5" s="4">
         <f t="shared" si="0"/>
@@ -1476,22 +1463,22 @@
       <c r="AD5" s="1"/>
       <c r="AE5" s="17">
         <f>SUM(AE6:AE498)</f>
-        <v>10798.208640000001</v>
+        <v>6666.1068800000012</v>
       </c>
       <c r="AF5" s="10"/>
       <c r="AG5" s="4">
         <f>SUM(AG6:AG498)</f>
-        <v>2814</v>
+        <v>1740</v>
       </c>
       <c r="AH5" s="4">
         <f>SUM(AH6:AH498)</f>
-        <v>10992.08</v>
+        <v>6785.2400000000016</v>
       </c>
       <c r="AI5" s="1"/>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="17">
         <f>SUM(AK6:AK498)</f>
-        <v>31.430952380952377</v>
+        <v>19.358730158730165</v>
       </c>
       <c r="AL5" s="1"/>
       <c r="AM5" s="1"/>
@@ -1845,8 +1832,8 @@
         <v>100</v>
       </c>
       <c r="S9" s="5">
-        <f>R9*$S$1</f>
-        <v>144</v>
+        <f>R9</f>
+        <v>100</v>
       </c>
       <c r="T9" s="5">
         <f t="shared" ref="T9:T29" si="5">AF9*AG9</f>
@@ -1882,7 +1869,7 @@
       <c r="AD9" s="1"/>
       <c r="AE9" s="10">
         <f t="shared" ref="AE9:AE40" si="6">G9*S9</f>
-        <v>31.68</v>
+        <v>22</v>
       </c>
       <c r="AF9" s="10">
         <v>12</v>
@@ -1967,8 +1954,8 @@
         <v>100</v>
       </c>
       <c r="S10" s="5">
-        <f t="shared" ref="S10:S17" si="10">R10*$S$1</f>
-        <v>144</v>
+        <f t="shared" ref="S10:S29" si="10">R10</f>
+        <v>100</v>
       </c>
       <c r="T10" s="5">
         <f t="shared" si="5"/>
@@ -2004,7 +1991,7 @@
       <c r="AD10" s="1"/>
       <c r="AE10" s="10">
         <f t="shared" si="6"/>
-        <v>43.199999999999996</v>
+        <v>30</v>
       </c>
       <c r="AF10" s="10">
         <v>12</v>
@@ -2093,18 +2080,18 @@
         <v>655</v>
       </c>
       <c r="S11" s="5">
-        <f t="shared" si="10"/>
-        <v>943.19999999999993</v>
+        <f>R11*$S$1</f>
+        <v>543.65</v>
       </c>
       <c r="T11" s="5">
         <f t="shared" si="5"/>
-        <v>924</v>
+        <v>504</v>
       </c>
       <c r="U11" s="5"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1">
         <f t="shared" si="3"/>
-        <v>15.736111111111111</v>
+        <v>9.9027777777777786</v>
       </c>
       <c r="X11" s="1">
         <f t="shared" si="4"/>
@@ -2128,18 +2115,18 @@
       <c r="AD11" s="1"/>
       <c r="AE11" s="10">
         <f t="shared" si="6"/>
-        <v>264.096</v>
+        <v>152.22200000000001</v>
       </c>
       <c r="AF11" s="10">
         <v>6</v>
       </c>
       <c r="AG11" s="1">
         <f t="shared" si="7"/>
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AH11" s="1">
         <f t="shared" si="8"/>
-        <v>258.72000000000003</v>
+        <v>141.12</v>
       </c>
       <c r="AI11" s="1">
         <v>14</v>
@@ -2149,7 +2136,7 @@
       </c>
       <c r="AK11" s="10">
         <f t="shared" si="9"/>
-        <v>1.1000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AL11" s="1"/>
       <c r="AM11" s="1"/>
@@ -2216,11 +2203,11 @@
       </c>
       <c r="S12" s="5">
         <f t="shared" si="10"/>
-        <v>288</v>
+        <v>200</v>
       </c>
       <c r="T12" s="5">
         <f t="shared" si="5"/>
-        <v>336</v>
+        <v>168</v>
       </c>
       <c r="U12" s="29">
         <v>200</v>
@@ -2228,7 +2215,7 @@
       <c r="V12" s="19"/>
       <c r="W12" s="1">
         <f t="shared" si="3"/>
-        <v>35.230769230769234</v>
+        <v>30.923076923076923</v>
       </c>
       <c r="X12" s="1">
         <f t="shared" si="4"/>
@@ -2252,18 +2239,18 @@
       <c r="AD12" s="1"/>
       <c r="AE12" s="10">
         <f t="shared" si="6"/>
-        <v>69.12</v>
+        <v>48</v>
       </c>
       <c r="AF12" s="10">
         <v>12</v>
       </c>
       <c r="AG12" s="1">
         <f t="shared" si="7"/>
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AH12" s="1">
         <f t="shared" si="8"/>
-        <v>80.64</v>
+        <v>40.32</v>
       </c>
       <c r="AI12" s="1">
         <v>14</v>
@@ -2273,7 +2260,7 @@
       </c>
       <c r="AK12" s="10">
         <f t="shared" si="9"/>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AL12" s="1"/>
       <c r="AM12" s="1"/>
@@ -2342,11 +2329,11 @@
       </c>
       <c r="S13" s="5">
         <f t="shared" si="10"/>
-        <v>432</v>
+        <v>300</v>
       </c>
       <c r="T13" s="5">
         <f t="shared" si="5"/>
-        <v>504</v>
+        <v>336</v>
       </c>
       <c r="U13" s="29">
         <v>300</v>
@@ -2354,7 +2341,7 @@
       <c r="V13" s="19"/>
       <c r="W13" s="1">
         <f t="shared" si="3"/>
-        <v>10.967741935483872</v>
+        <v>8.8833746898263026</v>
       </c>
       <c r="X13" s="1">
         <f t="shared" si="4"/>
@@ -2378,18 +2365,18 @@
       <c r="AD13" s="1"/>
       <c r="AE13" s="10">
         <f t="shared" si="6"/>
-        <v>103.67999999999999</v>
+        <v>72</v>
       </c>
       <c r="AF13" s="10">
         <v>12</v>
       </c>
       <c r="AG13" s="1">
         <f t="shared" si="7"/>
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AH13" s="1">
         <f t="shared" si="8"/>
-        <v>120.96</v>
+        <v>80.64</v>
       </c>
       <c r="AI13" s="1">
         <v>14</v>
@@ -2399,7 +2386,7 @@
       </c>
       <c r="AK13" s="10">
         <f t="shared" si="9"/>
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="AL13" s="1"/>
       <c r="AM13" s="1"/>
@@ -2468,11 +2455,11 @@
       </c>
       <c r="S14" s="5">
         <f t="shared" si="10"/>
-        <v>432</v>
+        <v>300</v>
       </c>
       <c r="T14" s="5">
         <f t="shared" si="5"/>
-        <v>504</v>
+        <v>336</v>
       </c>
       <c r="U14" s="29">
         <v>300</v>
@@ -2480,7 +2467,7 @@
       <c r="V14" s="19"/>
       <c r="W14" s="1">
         <f t="shared" si="3"/>
-        <v>20.579399141630901</v>
+        <v>16.974248927038627</v>
       </c>
       <c r="X14" s="1">
         <f t="shared" si="4"/>
@@ -2504,18 +2491,18 @@
       <c r="AD14" s="1"/>
       <c r="AE14" s="10">
         <f t="shared" si="6"/>
-        <v>103.67999999999999</v>
+        <v>72</v>
       </c>
       <c r="AF14" s="10">
         <v>12</v>
       </c>
       <c r="AG14" s="1">
         <f t="shared" si="7"/>
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AH14" s="1">
         <f t="shared" si="8"/>
-        <v>120.96</v>
+        <v>80.64</v>
       </c>
       <c r="AI14" s="1">
         <v>14</v>
@@ -2525,7 +2512,7 @@
       </c>
       <c r="AK14" s="10">
         <f t="shared" si="9"/>
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="AL14" s="1"/>
       <c r="AM14" s="1"/>
@@ -2595,18 +2582,18 @@
         <v>437.39999999999986</v>
       </c>
       <c r="S15" s="5">
-        <f t="shared" si="10"/>
-        <v>629.85599999999977</v>
+        <f>R15*$S$1</f>
+        <v>363.04199999999986</v>
       </c>
       <c r="T15" s="5">
         <f t="shared" si="5"/>
-        <v>672</v>
+        <v>336</v>
       </c>
       <c r="U15" s="5"/>
       <c r="V15" s="1"/>
       <c r="W15" s="1">
         <f t="shared" si="3"/>
-        <v>16.875</v>
+        <v>12.757352941176471</v>
       </c>
       <c r="X15" s="1">
         <f t="shared" si="4"/>
@@ -2630,18 +2617,18 @@
       <c r="AD15" s="1"/>
       <c r="AE15" s="10">
         <f t="shared" si="6"/>
-        <v>151.16543999999993</v>
+        <v>87.130079999999964</v>
       </c>
       <c r="AF15" s="10">
         <v>12</v>
       </c>
       <c r="AG15" s="1">
         <f t="shared" si="7"/>
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="AH15" s="1">
         <f t="shared" si="8"/>
-        <v>161.28</v>
+        <v>80.64</v>
       </c>
       <c r="AI15" s="1">
         <v>14</v>
@@ -2651,7 +2638,7 @@
       </c>
       <c r="AK15" s="10">
         <f t="shared" si="9"/>
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="AL15" s="1"/>
       <c r="AM15" s="1"/>
@@ -2716,7 +2703,7 @@
       </c>
       <c r="S16" s="5">
         <f t="shared" si="10"/>
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="T16" s="5">
         <f t="shared" si="5"/>
@@ -2752,7 +2739,7 @@
       <c r="AD16" s="1"/>
       <c r="AE16" s="10">
         <f t="shared" si="6"/>
-        <v>69.12</v>
+        <v>48</v>
       </c>
       <c r="AF16" s="10">
         <v>8</v>
@@ -2791,54 +2778,54 @@
       <c r="AY16" s="1"/>
       <c r="AZ16" s="1"/>
     </row>
-    <row r="17" spans="1:52" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="32" t="s">
+    <row r="17" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="1">
         <v>2</v>
       </c>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32">
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1">
         <v>2</v>
       </c>
-      <c r="G17" s="33">
+      <c r="G17" s="14">
         <v>0.09</v>
       </c>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32" t="s">
+      <c r="H17" s="1"/>
+      <c r="I17" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32">
+      <c r="J17" s="1"/>
+      <c r="K17" s="1">
         <v>32</v>
       </c>
-      <c r="L17" s="32">
+      <c r="L17" s="1">
         <f t="shared" si="1"/>
         <v>-32</v>
       </c>
-      <c r="M17" s="32"/>
-      <c r="N17" s="32"/>
-      <c r="O17" s="32">
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1">
         <v>0</v>
       </c>
-      <c r="P17" s="32">
+      <c r="P17" s="1">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="34"/>
-      <c r="R17" s="34">
+      <c r="Q17" s="5"/>
+      <c r="R17" s="5">
         <v>180</v>
       </c>
       <c r="S17" s="5">
         <f t="shared" si="10"/>
-        <v>259.2</v>
-      </c>
-      <c r="T17" s="34">
+        <v>180</v>
+      </c>
+      <c r="T17" s="5">
         <f t="shared" si="5"/>
         <v>336</v>
       </c>
@@ -2846,70 +2833,70 @@
         <v>150</v>
       </c>
       <c r="V17" s="19"/>
-      <c r="W17" s="32" t="e">
+      <c r="W17" s="1" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X17" s="32" t="e">
+      <c r="X17" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y17" s="32">
+      <c r="Y17" s="1">
         <v>0</v>
       </c>
-      <c r="Z17" s="32">
+      <c r="Z17" s="1">
         <v>0</v>
       </c>
-      <c r="AA17" s="32">
+      <c r="AA17" s="1">
         <v>0</v>
       </c>
-      <c r="AB17" s="32">
+      <c r="AB17" s="1">
         <v>0</v>
       </c>
-      <c r="AC17" s="32">
+      <c r="AC17" s="1">
         <v>42.2</v>
       </c>
-      <c r="AD17" s="32"/>
-      <c r="AE17" s="35">
+      <c r="AD17" s="1"/>
+      <c r="AE17" s="10">
         <f t="shared" si="6"/>
-        <v>23.327999999999999</v>
-      </c>
-      <c r="AF17" s="35">
+        <v>16.2</v>
+      </c>
+      <c r="AF17" s="10">
         <v>24</v>
       </c>
-      <c r="AG17" s="32">
+      <c r="AG17" s="1">
         <f t="shared" si="7"/>
         <v>14</v>
       </c>
-      <c r="AH17" s="32">
+      <c r="AH17" s="1">
         <f t="shared" si="8"/>
         <v>30.24</v>
       </c>
-      <c r="AI17" s="32">
+      <c r="AI17" s="1">
         <v>14</v>
       </c>
-      <c r="AJ17" s="32">
+      <c r="AJ17" s="1">
         <v>126</v>
       </c>
-      <c r="AK17" s="35">
+      <c r="AK17" s="10">
         <f t="shared" si="9"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="AL17" s="32"/>
-      <c r="AM17" s="32"/>
-      <c r="AN17" s="32"/>
-      <c r="AO17" s="32"/>
-      <c r="AP17" s="32"/>
-      <c r="AQ17" s="32"/>
-      <c r="AR17" s="32"/>
-      <c r="AS17" s="32"/>
-      <c r="AT17" s="32"/>
-      <c r="AU17" s="32"/>
-      <c r="AV17" s="32"/>
-      <c r="AW17" s="32"/>
-      <c r="AX17" s="32"/>
-      <c r="AY17" s="32"/>
-      <c r="AZ17" s="32"/>
+      <c r="AL17" s="1"/>
+      <c r="AM17" s="1"/>
+      <c r="AN17" s="1"/>
+      <c r="AO17" s="1"/>
+      <c r="AP17" s="1"/>
+      <c r="AQ17" s="1"/>
+      <c r="AR17" s="1"/>
+      <c r="AS17" s="1"/>
+      <c r="AT17" s="1"/>
+      <c r="AU17" s="1"/>
+      <c r="AV17" s="1"/>
+      <c r="AW17" s="1"/>
+      <c r="AX17" s="1"/>
+      <c r="AY17" s="1"/>
+      <c r="AZ17" s="1"/>
     </row>
     <row r="18" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -2956,7 +2943,10 @@
       </c>
       <c r="Q18" s="5"/>
       <c r="R18" s="5"/>
-      <c r="S18" s="5"/>
+      <c r="S18" s="5">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="T18" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -3073,7 +3063,10 @@
       </c>
       <c r="Q19" s="5"/>
       <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
+      <c r="S19" s="5">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="T19" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -3193,12 +3186,12 @@
         <v>200</v>
       </c>
       <c r="S20" s="5">
-        <f t="shared" ref="S20:S28" si="11">R20*$S$1</f>
-        <v>288</v>
+        <f t="shared" si="10"/>
+        <v>200</v>
       </c>
       <c r="T20" s="5">
         <f t="shared" si="5"/>
-        <v>336</v>
+        <v>168</v>
       </c>
       <c r="U20" s="29">
         <v>200</v>
@@ -3206,7 +3199,7 @@
       <c r="V20" s="19"/>
       <c r="W20" s="1">
         <f t="shared" si="3"/>
-        <v>420</v>
+        <v>315</v>
       </c>
       <c r="X20" s="1">
         <f t="shared" si="4"/>
@@ -3230,18 +3223,18 @@
       <c r="AD20" s="1"/>
       <c r="AE20" s="10">
         <f t="shared" si="6"/>
-        <v>57.6</v>
+        <v>40</v>
       </c>
       <c r="AF20" s="10">
         <v>12</v>
       </c>
       <c r="AG20" s="1">
         <f t="shared" si="7"/>
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AH20" s="1">
         <f t="shared" si="8"/>
-        <v>67.2</v>
+        <v>33.6</v>
       </c>
       <c r="AI20" s="1">
         <v>14</v>
@@ -3251,7 +3244,7 @@
       </c>
       <c r="AK20" s="10">
         <f t="shared" si="9"/>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AL20" s="1"/>
       <c r="AM20" s="1"/>
@@ -3319,12 +3312,12 @@
         <v>200</v>
       </c>
       <c r="S21" s="5">
-        <f t="shared" si="11"/>
-        <v>288</v>
+        <f t="shared" si="10"/>
+        <v>200</v>
       </c>
       <c r="T21" s="5">
         <f t="shared" si="5"/>
-        <v>336</v>
+        <v>168</v>
       </c>
       <c r="U21" s="29">
         <v>200</v>
@@ -3332,7 +3325,7 @@
       <c r="V21" s="19"/>
       <c r="W21" s="1">
         <f t="shared" si="3"/>
-        <v>33.04195804195804</v>
+        <v>27.167832167832167</v>
       </c>
       <c r="X21" s="1">
         <f t="shared" si="4"/>
@@ -3356,18 +3349,18 @@
       <c r="AD21" s="1"/>
       <c r="AE21" s="10">
         <f t="shared" si="6"/>
-        <v>57.6</v>
+        <v>40</v>
       </c>
       <c r="AF21" s="10">
         <v>12</v>
       </c>
       <c r="AG21" s="1">
         <f t="shared" si="7"/>
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AH21" s="1">
         <f t="shared" si="8"/>
-        <v>67.2</v>
+        <v>33.6</v>
       </c>
       <c r="AI21" s="1">
         <v>14</v>
@@ -3377,7 +3370,7 @@
       </c>
       <c r="AK21" s="10">
         <f t="shared" si="9"/>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AL21" s="1"/>
       <c r="AM21" s="1"/>
@@ -3445,12 +3438,12 @@
         <v>200</v>
       </c>
       <c r="S22" s="5">
-        <f t="shared" si="11"/>
-        <v>288</v>
+        <f t="shared" si="10"/>
+        <v>200</v>
       </c>
       <c r="T22" s="5">
         <f t="shared" si="5"/>
-        <v>336</v>
+        <v>168</v>
       </c>
       <c r="U22" s="29">
         <v>200</v>
@@ -3458,7 +3451,7 @@
       <c r="V22" s="19"/>
       <c r="W22" s="1">
         <f t="shared" si="3"/>
-        <v>33.692307692307693</v>
+        <v>27.23076923076923</v>
       </c>
       <c r="X22" s="1">
         <f t="shared" si="4"/>
@@ -3482,18 +3475,18 @@
       <c r="AD22" s="1"/>
       <c r="AE22" s="10">
         <f t="shared" si="6"/>
-        <v>57.6</v>
+        <v>40</v>
       </c>
       <c r="AF22" s="10">
         <v>12</v>
       </c>
       <c r="AG22" s="1">
         <f t="shared" si="7"/>
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AH22" s="1">
         <f t="shared" si="8"/>
-        <v>67.2</v>
+        <v>33.6</v>
       </c>
       <c r="AI22" s="1">
         <v>14</v>
@@ -3503,7 +3496,7 @@
       </c>
       <c r="AK22" s="10">
         <f t="shared" si="9"/>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AL22" s="1"/>
       <c r="AM22" s="1"/>
@@ -3567,12 +3560,12 @@
         <v>70</v>
       </c>
       <c r="S23" s="5">
-        <f t="shared" si="11"/>
-        <v>100.8</v>
+        <f t="shared" si="10"/>
+        <v>70</v>
       </c>
       <c r="T23" s="5">
         <f t="shared" si="5"/>
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="U23" s="29">
         <v>70</v>
@@ -3606,18 +3599,18 @@
       </c>
       <c r="AE23" s="10">
         <f t="shared" si="6"/>
-        <v>100.8</v>
+        <v>70</v>
       </c>
       <c r="AF23" s="10">
         <v>5</v>
       </c>
       <c r="AG23" s="1">
         <f t="shared" si="7"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AH23" s="1">
         <f t="shared" si="8"/>
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AI23" s="1">
         <v>12</v>
@@ -3627,7 +3620,7 @@
       </c>
       <c r="AK23" s="10">
         <f t="shared" si="9"/>
-        <v>0.2857142857142857</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="AL23" s="1"/>
       <c r="AM23" s="1"/>
@@ -3695,12 +3688,12 @@
         <v>200</v>
       </c>
       <c r="S24" s="5">
-        <f t="shared" si="11"/>
-        <v>288</v>
+        <f t="shared" si="10"/>
+        <v>200</v>
       </c>
       <c r="T24" s="5">
         <f t="shared" si="5"/>
-        <v>294</v>
+        <v>210</v>
       </c>
       <c r="U24" s="29">
         <v>200</v>
@@ -3708,7 +3701,7 @@
       <c r="V24" s="19"/>
       <c r="W24" s="1">
         <f t="shared" si="3"/>
-        <v>41.875</v>
+        <v>36.041666666666664</v>
       </c>
       <c r="X24" s="1">
         <f t="shared" si="4"/>
@@ -3732,18 +3725,18 @@
       <c r="AD24" s="1"/>
       <c r="AE24" s="10">
         <f t="shared" si="6"/>
-        <v>288</v>
+        <v>200</v>
       </c>
       <c r="AF24" s="10">
         <v>3</v>
       </c>
       <c r="AG24" s="1">
         <f t="shared" si="7"/>
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="AH24" s="1">
         <f t="shared" si="8"/>
-        <v>294</v>
+        <v>210</v>
       </c>
       <c r="AI24" s="1">
         <v>14</v>
@@ -3753,7 +3746,7 @@
       </c>
       <c r="AK24" s="10">
         <f t="shared" si="9"/>
-        <v>0.77777777777777779</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="AL24" s="1"/>
       <c r="AM24" s="1"/>
@@ -3821,12 +3814,12 @@
         <v>300</v>
       </c>
       <c r="S25" s="5">
-        <f t="shared" si="11"/>
-        <v>432</v>
+        <f t="shared" si="10"/>
+        <v>300</v>
       </c>
       <c r="T25" s="5">
         <f t="shared" si="5"/>
-        <v>420</v>
+        <v>336</v>
       </c>
       <c r="U25" s="29">
         <v>300</v>
@@ -3834,7 +3827,7 @@
       <c r="V25" s="19"/>
       <c r="W25" s="1">
         <f t="shared" si="3"/>
-        <v>17.493333333333332</v>
+        <v>16.373333333333335</v>
       </c>
       <c r="X25" s="1">
         <f t="shared" si="4"/>
@@ -3860,18 +3853,18 @@
       </c>
       <c r="AE25" s="10">
         <f t="shared" si="6"/>
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AF25" s="10">
         <v>6</v>
       </c>
       <c r="AG25" s="1">
         <f t="shared" si="7"/>
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="AH25" s="1">
         <f t="shared" si="8"/>
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="AI25" s="1">
         <v>14</v>
@@ -3881,7 +3874,7 @@
       </c>
       <c r="AK25" s="10">
         <f t="shared" si="9"/>
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AL25" s="1"/>
       <c r="AM25" s="1"/>
@@ -3949,12 +3942,12 @@
         <v>100</v>
       </c>
       <c r="S26" s="5">
-        <f t="shared" si="11"/>
-        <v>144</v>
+        <f t="shared" si="10"/>
+        <v>100</v>
       </c>
       <c r="T26" s="5">
         <f t="shared" si="5"/>
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="U26" s="29">
         <v>100</v>
@@ -3962,7 +3955,7 @@
       <c r="V26" s="19"/>
       <c r="W26" s="1">
         <f t="shared" si="3"/>
-        <v>22.569444444444443</v>
+        <v>16.736111111111111</v>
       </c>
       <c r="X26" s="1">
         <f t="shared" si="4"/>
@@ -3988,18 +3981,18 @@
       </c>
       <c r="AE26" s="10">
         <f t="shared" si="6"/>
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AF26" s="10">
         <v>6</v>
       </c>
       <c r="AG26" s="1">
         <f t="shared" si="7"/>
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AH26" s="1">
         <f t="shared" si="8"/>
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="AI26" s="1">
         <v>14</v>
@@ -4009,7 +4002,7 @@
       </c>
       <c r="AK26" s="10">
         <f t="shared" si="9"/>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AL26" s="1"/>
       <c r="AM26" s="1"/>
@@ -4075,12 +4068,12 @@
         <v>300</v>
       </c>
       <c r="S27" s="5">
-        <f t="shared" si="11"/>
-        <v>432</v>
+        <f t="shared" si="10"/>
+        <v>300</v>
       </c>
       <c r="T27" s="5">
         <f t="shared" si="5"/>
-        <v>504</v>
+        <v>336</v>
       </c>
       <c r="U27" s="29">
         <v>300</v>
@@ -4088,7 +4081,7 @@
       <c r="V27" s="19"/>
       <c r="W27" s="1">
         <f t="shared" si="3"/>
-        <v>32.941176470588239</v>
+        <v>24.705882352941178</v>
       </c>
       <c r="X27" s="1">
         <f t="shared" si="4"/>
@@ -4112,18 +4105,18 @@
       <c r="AD27" s="1"/>
       <c r="AE27" s="10">
         <f t="shared" si="6"/>
-        <v>99.36</v>
+        <v>69</v>
       </c>
       <c r="AF27" s="10">
         <v>12</v>
       </c>
       <c r="AG27" s="1">
         <f t="shared" si="7"/>
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AH27" s="1">
         <f t="shared" si="8"/>
-        <v>115.92</v>
+        <v>77.28</v>
       </c>
       <c r="AI27" s="1">
         <v>14</v>
@@ -4133,7 +4126,7 @@
       </c>
       <c r="AK27" s="10">
         <f t="shared" si="9"/>
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="AL27" s="1"/>
       <c r="AM27" s="1"/>
@@ -4201,8 +4194,8 @@
         <v>100</v>
       </c>
       <c r="S28" s="5">
-        <f t="shared" si="11"/>
-        <v>144</v>
+        <f t="shared" si="10"/>
+        <v>100</v>
       </c>
       <c r="T28" s="5">
         <f t="shared" si="5"/>
@@ -4240,7 +4233,7 @@
       </c>
       <c r="AE28" s="10">
         <f t="shared" si="6"/>
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AF28" s="10">
         <v>12</v>
@@ -4326,7 +4319,10 @@
       </c>
       <c r="Q29" s="5"/>
       <c r="R29" s="5"/>
-      <c r="S29" s="5"/>
+      <c r="S29" s="5">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="T29" s="5">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -4535,12 +4531,12 @@
         <v>300</v>
       </c>
       <c r="S31" s="5">
-        <f>R31*$S$1</f>
-        <v>432</v>
+        <f t="shared" ref="S31:S66" si="11">R31</f>
+        <v>300</v>
       </c>
       <c r="T31" s="5">
         <f t="shared" ref="T31:T68" si="12">AF31*AG31</f>
-        <v>504</v>
+        <v>336</v>
       </c>
       <c r="U31" s="29">
         <v>300</v>
@@ -4548,7 +4544,7 @@
       <c r="V31" s="19"/>
       <c r="W31" s="1">
         <f t="shared" si="3"/>
-        <v>23.086124401913878</v>
+        <v>19.066985645933016</v>
       </c>
       <c r="X31" s="1">
         <f t="shared" si="4"/>
@@ -4574,18 +4570,18 @@
       </c>
       <c r="AE31" s="10">
         <f t="shared" si="6"/>
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AF31" s="10">
         <v>12</v>
       </c>
       <c r="AG31" s="1">
         <f t="shared" ref="AG31:AG66" si="13">MROUND(S31, AF31*AI31)/AF31</f>
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AH31" s="1">
         <f t="shared" ref="AH31:AH66" si="14">AG31*AF31*G31</f>
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="AI31" s="1">
         <v>14</v>
@@ -4595,7 +4591,7 @@
       </c>
       <c r="AK31" s="10">
         <f t="shared" ref="AK31:AK66" si="15">AG31/AJ31</f>
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="AL31" s="1"/>
       <c r="AM31" s="1"/>
@@ -4658,7 +4654,10 @@
       </c>
       <c r="Q32" s="5"/>
       <c r="R32" s="5"/>
-      <c r="S32" s="5"/>
+      <c r="S32" s="5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="T32" s="5">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -4782,12 +4781,12 @@
         <v>100</v>
       </c>
       <c r="S33" s="5">
-        <f t="shared" ref="S33:S36" si="16">R33*$S$1</f>
-        <v>144</v>
+        <f t="shared" si="11"/>
+        <v>100</v>
       </c>
       <c r="T33" s="5">
         <f t="shared" si="12"/>
-        <v>192</v>
+        <v>96</v>
       </c>
       <c r="U33" s="29">
         <v>100</v>
@@ -4795,7 +4794,7 @@
       <c r="V33" s="19"/>
       <c r="W33" s="1">
         <f t="shared" si="3"/>
-        <v>25.813953488372093</v>
+        <v>20.232558139534884</v>
       </c>
       <c r="X33" s="1">
         <f t="shared" si="4"/>
@@ -4819,18 +4818,18 @@
       <c r="AD33" s="1"/>
       <c r="AE33" s="10">
         <f t="shared" si="6"/>
-        <v>100.8</v>
+        <v>70</v>
       </c>
       <c r="AF33" s="10">
         <v>8</v>
       </c>
       <c r="AG33" s="1">
         <f t="shared" si="13"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AH33" s="1">
         <f t="shared" si="14"/>
-        <v>134.39999999999998</v>
+        <v>67.199999999999989</v>
       </c>
       <c r="AI33" s="1">
         <v>12</v>
@@ -4840,7 +4839,7 @@
       </c>
       <c r="AK33" s="10">
         <f t="shared" si="15"/>
-        <v>0.2857142857142857</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="AL33" s="1"/>
       <c r="AM33" s="1"/>
@@ -4908,12 +4907,12 @@
         <v>100</v>
       </c>
       <c r="S34" s="5">
-        <f t="shared" si="16"/>
-        <v>144</v>
+        <f t="shared" si="11"/>
+        <v>100</v>
       </c>
       <c r="T34" s="5">
         <f t="shared" si="12"/>
-        <v>192</v>
+        <v>96</v>
       </c>
       <c r="U34" s="29">
         <v>100</v>
@@ -4921,7 +4920,7 @@
       <c r="V34" s="19"/>
       <c r="W34" s="1">
         <f t="shared" si="3"/>
-        <v>63.69047619047619</v>
+        <v>52.261904761904759</v>
       </c>
       <c r="X34" s="1">
         <f t="shared" si="4"/>
@@ -4945,18 +4944,18 @@
       <c r="AD34" s="1"/>
       <c r="AE34" s="10">
         <f t="shared" si="6"/>
-        <v>100.8</v>
+        <v>70</v>
       </c>
       <c r="AF34" s="10">
         <v>8</v>
       </c>
       <c r="AG34" s="1">
         <f t="shared" si="13"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AH34" s="1">
         <f t="shared" si="14"/>
-        <v>134.39999999999998</v>
+        <v>67.199999999999989</v>
       </c>
       <c r="AI34" s="1">
         <v>12</v>
@@ -4966,7 +4965,7 @@
       </c>
       <c r="AK34" s="10">
         <f t="shared" si="15"/>
-        <v>0.2857142857142857</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="AL34" s="1"/>
       <c r="AM34" s="1"/>
@@ -5034,12 +5033,12 @@
         <v>100</v>
       </c>
       <c r="S35" s="5">
-        <f t="shared" si="16"/>
-        <v>144</v>
+        <f t="shared" si="11"/>
+        <v>100</v>
       </c>
       <c r="T35" s="5">
         <f t="shared" si="12"/>
-        <v>192</v>
+        <v>96</v>
       </c>
       <c r="U35" s="29">
         <v>100</v>
@@ -5047,7 +5046,7 @@
       <c r="V35" s="19"/>
       <c r="W35" s="1">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>20.352941176470587</v>
       </c>
       <c r="X35" s="1">
         <f t="shared" si="4"/>
@@ -5071,18 +5070,18 @@
       <c r="AD35" s="1"/>
       <c r="AE35" s="10">
         <f t="shared" si="6"/>
-        <v>100.8</v>
+        <v>70</v>
       </c>
       <c r="AF35" s="10">
         <v>8</v>
       </c>
       <c r="AG35" s="1">
         <f t="shared" si="13"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AH35" s="1">
         <f t="shared" si="14"/>
-        <v>134.39999999999998</v>
+        <v>67.199999999999989</v>
       </c>
       <c r="AI35" s="1">
         <v>12</v>
@@ -5092,7 +5091,7 @@
       </c>
       <c r="AK35" s="10">
         <f t="shared" si="15"/>
-        <v>0.2857142857142857</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="AL35" s="1"/>
       <c r="AM35" s="1"/>
@@ -5162,12 +5161,12 @@
         <v>500</v>
       </c>
       <c r="S36" s="5">
-        <f t="shared" si="16"/>
-        <v>720</v>
+        <f>R36*$S$1</f>
+        <v>415</v>
       </c>
       <c r="T36" s="5">
         <f t="shared" si="12"/>
-        <v>720</v>
+        <v>360</v>
       </c>
       <c r="U36" s="29">
         <v>500</v>
@@ -5175,7 +5174,7 @@
       <c r="V36" s="19"/>
       <c r="W36" s="1">
         <f t="shared" si="3"/>
-        <v>23.741007194244602</v>
+        <v>17.266187050359711</v>
       </c>
       <c r="X36" s="1">
         <f t="shared" si="4"/>
@@ -5199,18 +5198,18 @@
       <c r="AD36" s="1"/>
       <c r="AE36" s="10">
         <f t="shared" si="6"/>
-        <v>503.99999999999994</v>
+        <v>290.5</v>
       </c>
       <c r="AF36" s="10">
         <v>10</v>
       </c>
       <c r="AG36" s="1">
         <f t="shared" si="13"/>
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="AH36" s="1">
         <f t="shared" si="14"/>
-        <v>503.99999999999994</v>
+        <v>251.99999999999997</v>
       </c>
       <c r="AI36" s="1">
         <v>12</v>
@@ -5220,7 +5219,7 @@
       </c>
       <c r="AK36" s="10">
         <f t="shared" si="15"/>
-        <v>0.8571428571428571</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="AL36" s="1"/>
       <c r="AM36" s="1"/>
@@ -5285,7 +5284,10 @@
       </c>
       <c r="Q37" s="5"/>
       <c r="R37" s="5"/>
-      <c r="S37" s="5"/>
+      <c r="S37" s="5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="T37" s="5">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -5390,7 +5392,7 @@
         <v>184</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L67" si="17">E38-K38</f>
+        <f t="shared" ref="L38:L67" si="16">E38-K38</f>
         <v>3</v>
       </c>
       <c r="M38" s="1"/>
@@ -5399,12 +5401,15 @@
         <v>600</v>
       </c>
       <c r="P38" s="1">
-        <f t="shared" ref="P38:P68" si="18">E38/5</f>
+        <f t="shared" ref="P38:P68" si="17">E38/5</f>
         <v>37.4</v>
       </c>
       <c r="Q38" s="5"/>
       <c r="R38" s="5"/>
-      <c r="S38" s="5"/>
+      <c r="S38" s="5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="T38" s="5">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -5412,11 +5417,11 @@
       <c r="U38" s="5"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1">
-        <f t="shared" ref="W38:W68" si="19">(F38+O38+T38)/P38</f>
+        <f t="shared" ref="W38:W68" si="18">(F38+O38+T38)/P38</f>
         <v>16.149732620320858</v>
       </c>
       <c r="X38" s="1">
-        <f t="shared" ref="X38:X68" si="20">(F38+O38)/P38</f>
+        <f t="shared" ref="X38:X68" si="19">(F38+O38)/P38</f>
         <v>16.149732620320858</v>
       </c>
       <c r="Y38" s="1">
@@ -5509,7 +5514,7 @@
         <v>94</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M39" s="1"/>
@@ -5518,7 +5523,7 @@
         <v>0</v>
       </c>
       <c r="P39" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>18.8</v>
       </c>
       <c r="Q39" s="5"/>
@@ -5526,8 +5531,8 @@
         <v>100</v>
       </c>
       <c r="S39" s="5">
-        <f t="shared" ref="S39:S40" si="21">R39*$S$1</f>
-        <v>144</v>
+        <f t="shared" si="11"/>
+        <v>100</v>
       </c>
       <c r="T39" s="5">
         <f t="shared" si="12"/>
@@ -5538,11 +5543,11 @@
       </c>
       <c r="V39" s="19"/>
       <c r="W39" s="1">
+        <f t="shared" si="18"/>
+        <v>22.393617021276594</v>
+      </c>
+      <c r="X39" s="1">
         <f t="shared" si="19"/>
-        <v>22.393617021276594</v>
-      </c>
-      <c r="X39" s="1">
-        <f t="shared" si="20"/>
         <v>16.01063829787234</v>
       </c>
       <c r="Y39" s="1">
@@ -5563,7 +5568,7 @@
       <c r="AD39" s="1"/>
       <c r="AE39" s="10">
         <f t="shared" si="6"/>
-        <v>100.8</v>
+        <v>70</v>
       </c>
       <c r="AF39" s="10">
         <v>10</v>
@@ -5635,7 +5640,7 @@
         <v>410</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>10</v>
       </c>
       <c r="M40" s="1"/>
@@ -5644,7 +5649,7 @@
         <v>0</v>
       </c>
       <c r="P40" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>84</v>
       </c>
       <c r="Q40" s="5">
@@ -5654,21 +5659,21 @@
         <v>766</v>
       </c>
       <c r="S40" s="5">
-        <f t="shared" si="21"/>
-        <v>1103.04</v>
+        <f>R40*$S$1</f>
+        <v>635.78</v>
       </c>
       <c r="T40" s="5">
         <f t="shared" si="12"/>
-        <v>1080</v>
+        <v>660</v>
       </c>
       <c r="U40" s="5"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1">
+        <f t="shared" si="18"/>
+        <v>12.738095238095237</v>
+      </c>
+      <c r="X40" s="1">
         <f t="shared" si="19"/>
-        <v>17.738095238095237</v>
-      </c>
-      <c r="X40" s="1">
-        <f t="shared" si="20"/>
         <v>4.8809523809523814</v>
       </c>
       <c r="Y40" s="1">
@@ -5689,18 +5694,18 @@
       <c r="AD40" s="1"/>
       <c r="AE40" s="10">
         <f t="shared" si="6"/>
-        <v>1103.04</v>
+        <v>635.78</v>
       </c>
       <c r="AF40" s="10">
         <v>5</v>
       </c>
       <c r="AG40" s="1">
         <f t="shared" si="13"/>
-        <v>216</v>
+        <v>132</v>
       </c>
       <c r="AH40" s="1">
         <f t="shared" si="14"/>
-        <v>1080</v>
+        <v>660</v>
       </c>
       <c r="AI40" s="1">
         <v>12</v>
@@ -5710,7 +5715,7 @@
       </c>
       <c r="AK40" s="10">
         <f t="shared" si="15"/>
-        <v>1.5</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="AL40" s="1"/>
       <c r="AM40" s="1"/>
@@ -5761,7 +5766,7 @@
         <v>261</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-6</v>
       </c>
       <c r="M41" s="1"/>
@@ -5770,12 +5775,15 @@
         <v>0</v>
       </c>
       <c r="P41" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>51</v>
       </c>
       <c r="Q41" s="5"/>
       <c r="R41" s="5"/>
-      <c r="S41" s="5"/>
+      <c r="S41" s="5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="T41" s="5">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -5783,13 +5791,13 @@
       <c r="U41" s="5"/>
       <c r="V41" s="1"/>
       <c r="W41" s="1">
+        <f t="shared" si="18"/>
+        <v>20.745098039215687</v>
+      </c>
+      <c r="X41" s="1">
         <f t="shared" si="19"/>
         <v>20.745098039215687</v>
       </c>
-      <c r="X41" s="1">
-        <f t="shared" si="20"/>
-        <v>20.745098039215687</v>
-      </c>
       <c r="Y41" s="1">
         <v>41</v>
       </c>
@@ -5807,7 +5815,7 @@
       </c>
       <c r="AD41" s="1"/>
       <c r="AE41" s="10">
-        <f t="shared" ref="AE41:AE66" si="22">G41*S41</f>
+        <f t="shared" ref="AE41:AE66" si="20">G41*S41</f>
         <v>0</v>
       </c>
       <c r="AF41" s="10">
@@ -5880,7 +5888,7 @@
         <v>680</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>4</v>
       </c>
       <c r="M42" s="1"/>
@@ -5889,7 +5897,7 @@
         <v>0</v>
       </c>
       <c r="P42" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>136.80000000000001</v>
       </c>
       <c r="Q42" s="5">
@@ -5900,22 +5908,22 @@
       </c>
       <c r="S42" s="5">
         <f>R42*$S$1</f>
-        <v>1296</v>
+        <v>747</v>
       </c>
       <c r="T42" s="5">
         <f t="shared" si="12"/>
-        <v>1320</v>
+        <v>720</v>
       </c>
       <c r="U42" s="29">
         <v>900</v>
       </c>
       <c r="V42" s="19"/>
       <c r="W42" s="1">
+        <f t="shared" si="18"/>
+        <v>13.786549707602338</v>
+      </c>
+      <c r="X42" s="1">
         <f t="shared" si="19"/>
-        <v>18.172514619883039</v>
-      </c>
-      <c r="X42" s="1">
-        <f t="shared" si="20"/>
         <v>8.523391812865496</v>
       </c>
       <c r="Y42" s="1">
@@ -5937,19 +5945,19 @@
         <v>118</v>
       </c>
       <c r="AE42" s="10">
-        <f t="shared" si="22"/>
-        <v>907.19999999999993</v>
+        <f t="shared" si="20"/>
+        <v>522.9</v>
       </c>
       <c r="AF42" s="10">
         <v>10</v>
       </c>
       <c r="AG42" s="1">
         <f t="shared" si="13"/>
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="AH42" s="1">
         <f t="shared" si="14"/>
-        <v>923.99999999999989</v>
+        <v>503.99999999999994</v>
       </c>
       <c r="AI42" s="1">
         <v>12</v>
@@ -5959,7 +5967,7 @@
       </c>
       <c r="AK42" s="10">
         <f t="shared" si="15"/>
-        <v>1.5714285714285714</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AL42" s="1"/>
       <c r="AM42" s="1"/>
@@ -6010,7 +6018,7 @@
         <v>265</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="M43" s="1"/>
@@ -6019,12 +6027,15 @@
         <v>0</v>
       </c>
       <c r="P43" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>53.2</v>
       </c>
       <c r="Q43" s="5"/>
       <c r="R43" s="5"/>
-      <c r="S43" s="5"/>
+      <c r="S43" s="5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="T43" s="5">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -6032,13 +6043,13 @@
       <c r="U43" s="5"/>
       <c r="V43" s="1"/>
       <c r="W43" s="1">
+        <f t="shared" si="18"/>
+        <v>17.443609022556391</v>
+      </c>
+      <c r="X43" s="1">
         <f t="shared" si="19"/>
         <v>17.443609022556391</v>
       </c>
-      <c r="X43" s="1">
-        <f t="shared" si="20"/>
-        <v>17.443609022556391</v>
-      </c>
       <c r="Y43" s="1">
         <v>53.8</v>
       </c>
@@ -6056,7 +6067,7 @@
       </c>
       <c r="AD43" s="1"/>
       <c r="AE43" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF43" s="10">
@@ -6131,7 +6142,7 @@
         <v>802</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>95</v>
       </c>
       <c r="M44" s="1"/>
@@ -6140,7 +6151,7 @@
         <v>720</v>
       </c>
       <c r="P44" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>179.4</v>
       </c>
       <c r="Q44" s="5">
@@ -6150,21 +6161,21 @@
         <v>1109.5999999999999</v>
       </c>
       <c r="S44" s="5">
-        <f t="shared" ref="S44:S54" si="23">R44*$S$1</f>
-        <v>1597.8239999999998</v>
+        <f>R44*$S$1</f>
+        <v>920.96799999999985</v>
       </c>
       <c r="T44" s="5">
         <f t="shared" si="12"/>
-        <v>1560</v>
+        <v>960</v>
       </c>
       <c r="U44" s="5"/>
       <c r="V44" s="1"/>
       <c r="W44" s="1">
+        <f t="shared" si="18"/>
+        <v>13.166109253065775</v>
+      </c>
+      <c r="X44" s="1">
         <f t="shared" si="19"/>
-        <v>16.510590858416943</v>
-      </c>
-      <c r="X44" s="1">
-        <f t="shared" si="20"/>
         <v>7.8149386845039013</v>
       </c>
       <c r="Y44" s="1">
@@ -6186,19 +6197,19 @@
         <v>66</v>
       </c>
       <c r="AE44" s="10">
-        <f t="shared" si="22"/>
-        <v>1118.4767999999999</v>
+        <f t="shared" si="20"/>
+        <v>644.67759999999987</v>
       </c>
       <c r="AF44" s="10">
         <v>10</v>
       </c>
       <c r="AG44" s="1">
         <f t="shared" si="13"/>
-        <v>156</v>
+        <v>96</v>
       </c>
       <c r="AH44" s="1">
         <f t="shared" si="14"/>
-        <v>1092</v>
+        <v>672</v>
       </c>
       <c r="AI44" s="1">
         <v>12</v>
@@ -6208,7 +6219,7 @@
       </c>
       <c r="AK44" s="10">
         <f t="shared" si="15"/>
-        <v>1.8571428571428572</v>
+        <v>1.1428571428571428</v>
       </c>
       <c r="AL44" s="1"/>
       <c r="AM44" s="1"/>
@@ -6259,7 +6270,7 @@
         <v>156</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="M45" s="1"/>
@@ -6268,7 +6279,7 @@
         <v>360</v>
       </c>
       <c r="P45" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>31.4</v>
       </c>
       <c r="Q45" s="5"/>
@@ -6276,8 +6287,8 @@
         <v>200</v>
       </c>
       <c r="S45" s="5">
-        <f t="shared" si="23"/>
-        <v>288</v>
+        <f t="shared" si="11"/>
+        <v>200</v>
       </c>
       <c r="T45" s="5">
         <f t="shared" si="12"/>
@@ -6288,11 +6299,11 @@
       </c>
       <c r="V45" s="19"/>
       <c r="W45" s="1">
+        <f t="shared" si="18"/>
+        <v>30.063694267515924</v>
+      </c>
+      <c r="X45" s="1">
         <f t="shared" si="19"/>
-        <v>30.063694267515924</v>
-      </c>
-      <c r="X45" s="1">
-        <f t="shared" si="20"/>
         <v>22.420382165605098</v>
       </c>
       <c r="Y45" s="1">
@@ -6314,8 +6325,8 @@
         <v>124</v>
       </c>
       <c r="AE45" s="10">
-        <f t="shared" si="22"/>
-        <v>201.6</v>
+        <f t="shared" si="20"/>
+        <v>140</v>
       </c>
       <c r="AF45" s="10">
         <v>10</v>
@@ -6387,7 +6398,7 @@
         <v>197</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-9</v>
       </c>
       <c r="M46" s="1"/>
@@ -6396,7 +6407,7 @@
         <v>720</v>
       </c>
       <c r="P46" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>37.6</v>
       </c>
       <c r="Q46" s="5"/>
@@ -6404,23 +6415,23 @@
         <v>200</v>
       </c>
       <c r="S46" s="5">
-        <f t="shared" si="23"/>
-        <v>288</v>
+        <f t="shared" si="11"/>
+        <v>200</v>
       </c>
       <c r="T46" s="5">
         <f t="shared" si="12"/>
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="U46" s="29">
         <v>200</v>
       </c>
       <c r="V46" s="19"/>
       <c r="W46" s="1">
+        <f t="shared" si="18"/>
+        <v>24.01595744680851</v>
+      </c>
+      <c r="X46" s="1">
         <f t="shared" si="19"/>
-        <v>27.207446808510639</v>
-      </c>
-      <c r="X46" s="1">
-        <f t="shared" si="20"/>
         <v>19.228723404255319</v>
       </c>
       <c r="Y46" s="1">
@@ -6440,19 +6451,19 @@
       </c>
       <c r="AD46" s="1"/>
       <c r="AE46" s="10">
-        <f t="shared" si="22"/>
-        <v>288</v>
+        <f t="shared" si="20"/>
+        <v>200</v>
       </c>
       <c r="AF46" s="10">
         <v>5</v>
       </c>
       <c r="AG46" s="1">
         <f t="shared" si="13"/>
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AH46" s="1">
         <f t="shared" si="14"/>
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="AI46" s="1">
         <v>12</v>
@@ -6462,7 +6473,7 @@
       </c>
       <c r="AK46" s="10">
         <f t="shared" si="15"/>
-        <v>0.7142857142857143</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="AL46" s="1"/>
       <c r="AM46" s="1"/>
@@ -6513,7 +6524,7 @@
         <v>167</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M47" s="1"/>
@@ -6522,7 +6533,7 @@
         <v>288</v>
       </c>
       <c r="P47" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>33.4</v>
       </c>
       <c r="Q47" s="5">
@@ -6532,23 +6543,23 @@
         <v>300</v>
       </c>
       <c r="S47" s="5">
-        <f t="shared" si="23"/>
-        <v>432</v>
+        <f t="shared" si="11"/>
+        <v>300</v>
       </c>
       <c r="T47" s="5">
         <f t="shared" si="12"/>
-        <v>480</v>
+        <v>288</v>
       </c>
       <c r="U47" s="29">
         <v>300</v>
       </c>
       <c r="V47" s="19"/>
       <c r="W47" s="1">
+        <f t="shared" si="18"/>
+        <v>17.365269461077844</v>
+      </c>
+      <c r="X47" s="1">
         <f t="shared" si="19"/>
-        <v>23.113772455089823</v>
-      </c>
-      <c r="X47" s="1">
-        <f t="shared" si="20"/>
         <v>8.7425149700598812</v>
       </c>
       <c r="Y47" s="1">
@@ -6570,19 +6581,19 @@
         <v>66</v>
       </c>
       <c r="AE47" s="10">
-        <f t="shared" si="22"/>
-        <v>388.8</v>
+        <f t="shared" si="20"/>
+        <v>270</v>
       </c>
       <c r="AF47" s="10">
         <v>8</v>
       </c>
       <c r="AG47" s="1">
         <f t="shared" si="13"/>
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AH47" s="1">
         <f t="shared" si="14"/>
-        <v>432</v>
+        <v>259.2</v>
       </c>
       <c r="AI47" s="1">
         <v>12</v>
@@ -6592,7 +6603,7 @@
       </c>
       <c r="AK47" s="10">
         <f t="shared" si="15"/>
-        <v>0.7142857142857143</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="AL47" s="1"/>
       <c r="AM47" s="1"/>
@@ -6643,7 +6654,7 @@
         <v>69</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-1</v>
       </c>
       <c r="M48" s="1"/>
@@ -6652,7 +6663,7 @@
         <v>288</v>
       </c>
       <c r="P48" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>13.6</v>
       </c>
       <c r="Q48" s="5"/>
@@ -6660,23 +6671,23 @@
         <v>192</v>
       </c>
       <c r="S48" s="5">
-        <f t="shared" si="23"/>
-        <v>276.48</v>
+        <f t="shared" si="11"/>
+        <v>192</v>
       </c>
       <c r="T48" s="5">
         <f t="shared" si="12"/>
-        <v>288</v>
+        <v>192</v>
       </c>
       <c r="U48" s="29">
         <v>192</v>
       </c>
       <c r="V48" s="19"/>
       <c r="W48" s="1">
+        <f t="shared" si="18"/>
+        <v>35.735294117647058</v>
+      </c>
+      <c r="X48" s="1">
         <f t="shared" si="19"/>
-        <v>42.794117647058826</v>
-      </c>
-      <c r="X48" s="1">
-        <f t="shared" si="20"/>
         <v>21.617647058823529</v>
       </c>
       <c r="Y48" s="1">
@@ -6696,19 +6707,19 @@
       </c>
       <c r="AD48" s="1"/>
       <c r="AE48" s="10">
-        <f t="shared" si="22"/>
-        <v>248.83200000000002</v>
+        <f t="shared" si="20"/>
+        <v>172.8</v>
       </c>
       <c r="AF48" s="10">
         <v>8</v>
       </c>
       <c r="AG48" s="1">
         <f t="shared" si="13"/>
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AH48" s="1">
         <f t="shared" si="14"/>
-        <v>259.2</v>
+        <v>172.8</v>
       </c>
       <c r="AI48" s="1">
         <v>12</v>
@@ -6718,7 +6729,7 @@
       </c>
       <c r="AK48" s="10">
         <f t="shared" si="15"/>
-        <v>0.42857142857142855</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AL48" s="1"/>
       <c r="AM48" s="1"/>
@@ -6769,7 +6780,7 @@
         <v>520</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-80</v>
       </c>
       <c r="M49" s="1"/>
@@ -6778,7 +6789,7 @@
         <v>1020</v>
       </c>
       <c r="P49" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>88</v>
       </c>
       <c r="Q49" s="5"/>
@@ -6786,23 +6797,23 @@
         <v>200</v>
       </c>
       <c r="S49" s="5">
-        <f t="shared" si="23"/>
-        <v>288</v>
+        <f t="shared" si="11"/>
+        <v>200</v>
       </c>
       <c r="T49" s="5">
         <f t="shared" si="12"/>
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="U49" s="29">
         <v>200</v>
       </c>
       <c r="V49" s="19"/>
       <c r="W49" s="1">
+        <f t="shared" si="18"/>
+        <v>23.238636363636363</v>
+      </c>
+      <c r="X49" s="1">
         <f t="shared" si="19"/>
-        <v>24.602272727272727</v>
-      </c>
-      <c r="X49" s="1">
-        <f t="shared" si="20"/>
         <v>21.193181818181817</v>
       </c>
       <c r="Y49" s="1">
@@ -6822,19 +6833,19 @@
       </c>
       <c r="AD49" s="1"/>
       <c r="AE49" s="10">
-        <f t="shared" si="22"/>
-        <v>288</v>
+        <f t="shared" si="20"/>
+        <v>200</v>
       </c>
       <c r="AF49" s="10">
         <v>5</v>
       </c>
       <c r="AG49" s="1">
         <f t="shared" si="13"/>
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AH49" s="1">
         <f t="shared" si="14"/>
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="AI49" s="1">
         <v>12</v>
@@ -6844,7 +6855,7 @@
       </c>
       <c r="AK49" s="10">
         <f t="shared" si="15"/>
-        <v>0.41666666666666669</v>
+        <v>0.25</v>
       </c>
       <c r="AL49" s="1"/>
       <c r="AM49" s="1"/>
@@ -6893,7 +6904,7 @@
         <v>136</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M50" s="1"/>
@@ -6902,7 +6913,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>27.2</v>
       </c>
       <c r="Q50" s="5">
@@ -6912,8 +6923,8 @@
         <v>92.800000000000011</v>
       </c>
       <c r="S50" s="5">
-        <f t="shared" si="23"/>
-        <v>133.63200000000001</v>
+        <f t="shared" si="11"/>
+        <v>92.800000000000011</v>
       </c>
       <c r="T50" s="5">
         <f t="shared" si="12"/>
@@ -6922,11 +6933,11 @@
       <c r="U50" s="5"/>
       <c r="V50" s="1"/>
       <c r="W50" s="1">
+        <f t="shared" si="18"/>
+        <v>15</v>
+      </c>
+      <c r="X50" s="1">
         <f t="shared" si="19"/>
-        <v>15</v>
-      </c>
-      <c r="X50" s="1">
-        <f t="shared" si="20"/>
         <v>10.588235294117647</v>
       </c>
       <c r="Y50" s="1">
@@ -6946,8 +6957,8 @@
       </c>
       <c r="AD50" s="1"/>
       <c r="AE50" s="10">
-        <f t="shared" si="22"/>
-        <v>133.63200000000001</v>
+        <f t="shared" si="20"/>
+        <v>92.800000000000011</v>
       </c>
       <c r="AF50" s="10">
         <v>5</v>
@@ -7017,7 +7028,7 @@
         <v>26.1</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="M51" s="1"/>
@@ -7026,7 +7037,7 @@
         <v>0</v>
       </c>
       <c r="P51" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>5.18</v>
       </c>
       <c r="Q51" s="5">
@@ -7036,8 +7047,8 @@
         <v>48.14</v>
       </c>
       <c r="S51" s="5">
-        <f t="shared" si="23"/>
-        <v>69.321600000000004</v>
+        <f t="shared" si="11"/>
+        <v>48.14</v>
       </c>
       <c r="T51" s="5">
         <f t="shared" si="12"/>
@@ -7046,11 +7057,11 @@
       <c r="U51" s="5"/>
       <c r="V51" s="1"/>
       <c r="W51" s="1">
+        <f t="shared" si="18"/>
+        <v>13.706563706563708</v>
+      </c>
+      <c r="X51" s="1">
         <f t="shared" si="19"/>
-        <v>13.706563706563708</v>
-      </c>
-      <c r="X51" s="1">
-        <f t="shared" si="20"/>
         <v>3.7065637065637067</v>
       </c>
       <c r="Y51" s="1">
@@ -7070,8 +7081,8 @@
       </c>
       <c r="AD51" s="1"/>
       <c r="AE51" s="10">
-        <f t="shared" si="22"/>
-        <v>69.321600000000004</v>
+        <f t="shared" si="20"/>
+        <v>48.14</v>
       </c>
       <c r="AF51" s="10">
         <v>3.7</v>
@@ -7141,7 +7152,7 @@
         <v>151</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M52" s="1"/>
@@ -7150,7 +7161,7 @@
         <v>168</v>
       </c>
       <c r="P52" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>30.2</v>
       </c>
       <c r="Q52" s="5">
@@ -7160,23 +7171,23 @@
         <v>500</v>
       </c>
       <c r="S52" s="5">
-        <f t="shared" si="23"/>
-        <v>720</v>
+        <f t="shared" ref="S52:S53" si="21">R52*$S$1</f>
+        <v>415</v>
       </c>
       <c r="T52" s="5">
         <f t="shared" si="12"/>
-        <v>756</v>
+        <v>420</v>
       </c>
       <c r="U52" s="29">
         <v>500</v>
       </c>
       <c r="V52" s="19"/>
       <c r="W52" s="1">
+        <f t="shared" si="18"/>
+        <v>21.456953642384107</v>
+      </c>
+      <c r="X52" s="1">
         <f t="shared" si="19"/>
-        <v>32.58278145695364</v>
-      </c>
-      <c r="X52" s="1">
-        <f t="shared" si="20"/>
         <v>7.5496688741721858</v>
       </c>
       <c r="Y52" s="1">
@@ -7196,19 +7207,19 @@
       </c>
       <c r="AD52" s="1"/>
       <c r="AE52" s="10">
-        <f t="shared" si="22"/>
-        <v>165.6</v>
+        <f t="shared" si="20"/>
+        <v>95.45</v>
       </c>
       <c r="AF52" s="10">
         <v>6</v>
       </c>
       <c r="AG52" s="1">
         <f t="shared" si="13"/>
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="AH52" s="1">
         <f t="shared" si="14"/>
-        <v>173.88</v>
+        <v>96.600000000000009</v>
       </c>
       <c r="AI52" s="1">
         <v>14</v>
@@ -7218,7 +7229,7 @@
       </c>
       <c r="AK52" s="10">
         <f t="shared" si="15"/>
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="AL52" s="1"/>
       <c r="AM52" s="1"/>
@@ -7269,7 +7280,7 @@
         <v>360</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>2</v>
       </c>
       <c r="M53" s="1"/>
@@ -7278,7 +7289,7 @@
         <v>336</v>
       </c>
       <c r="P53" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>72.400000000000006</v>
       </c>
       <c r="Q53" s="5">
@@ -7288,23 +7299,23 @@
         <v>750</v>
       </c>
       <c r="S53" s="5">
-        <f t="shared" si="23"/>
-        <v>1080</v>
+        <f t="shared" si="21"/>
+        <v>622.5</v>
       </c>
       <c r="T53" s="5">
         <f t="shared" si="12"/>
-        <v>1008</v>
+        <v>672</v>
       </c>
       <c r="U53" s="29">
         <v>750</v>
       </c>
       <c r="V53" s="19"/>
       <c r="W53" s="1">
+        <f t="shared" si="18"/>
+        <v>15.138121546961324</v>
+      </c>
+      <c r="X53" s="1">
         <f t="shared" si="19"/>
-        <v>19.779005524861876</v>
-      </c>
-      <c r="X53" s="1">
-        <f t="shared" si="20"/>
         <v>5.8563535911602207</v>
       </c>
       <c r="Y53" s="1">
@@ -7326,19 +7337,19 @@
         <v>66</v>
       </c>
       <c r="AE53" s="10">
-        <f t="shared" si="22"/>
-        <v>270</v>
+        <f t="shared" si="20"/>
+        <v>155.625</v>
       </c>
       <c r="AF53" s="10">
         <v>12</v>
       </c>
       <c r="AG53" s="1">
         <f t="shared" si="13"/>
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="AH53" s="1">
         <f t="shared" si="14"/>
-        <v>252</v>
+        <v>168</v>
       </c>
       <c r="AI53" s="1">
         <v>14</v>
@@ -7348,7 +7359,7 @@
       </c>
       <c r="AK53" s="10">
         <f t="shared" si="15"/>
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="AL53" s="1"/>
       <c r="AM53" s="1"/>
@@ -7399,7 +7410,7 @@
         <v>119</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-4</v>
       </c>
       <c r="M54" s="1"/>
@@ -7408,7 +7419,7 @@
         <v>336</v>
       </c>
       <c r="P54" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>23</v>
       </c>
       <c r="Q54" s="5"/>
@@ -7416,23 +7427,23 @@
         <v>200</v>
       </c>
       <c r="S54" s="5">
-        <f t="shared" si="23"/>
-        <v>288</v>
+        <f t="shared" si="11"/>
+        <v>200</v>
       </c>
       <c r="T54" s="5">
         <f t="shared" si="12"/>
-        <v>336</v>
+        <v>168</v>
       </c>
       <c r="U54" s="29">
         <v>200</v>
       </c>
       <c r="V54" s="19"/>
       <c r="W54" s="1">
+        <f t="shared" si="18"/>
+        <v>30.826086956521738</v>
+      </c>
+      <c r="X54" s="1">
         <f t="shared" si="19"/>
-        <v>38.130434782608695</v>
-      </c>
-      <c r="X54" s="1">
-        <f t="shared" si="20"/>
         <v>23.521739130434781</v>
       </c>
       <c r="Y54" s="1">
@@ -7452,19 +7463,19 @@
       </c>
       <c r="AD54" s="1"/>
       <c r="AE54" s="10">
-        <f t="shared" si="22"/>
-        <v>72</v>
+        <f t="shared" si="20"/>
+        <v>50</v>
       </c>
       <c r="AF54" s="10">
         <v>12</v>
       </c>
       <c r="AG54" s="1">
         <f t="shared" si="13"/>
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AH54" s="1">
         <f t="shared" si="14"/>
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="AI54" s="1">
         <v>14</v>
@@ -7474,7 +7485,7 @@
       </c>
       <c r="AK54" s="10">
         <f t="shared" si="15"/>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AL54" s="1"/>
       <c r="AM54" s="1"/>
@@ -7519,7 +7530,7 @@
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M55" s="1"/>
@@ -7528,12 +7539,15 @@
         <v>0</v>
       </c>
       <c r="P55" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Q55" s="5"/>
       <c r="R55" s="5"/>
-      <c r="S55" s="5"/>
+      <c r="S55" s="5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="T55" s="5">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -7541,13 +7555,13 @@
       <c r="U55" s="5"/>
       <c r="V55" s="1"/>
       <c r="W55" s="1" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X55" s="1" t="e">
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X55" s="1" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="Y55" s="1">
         <v>0</v>
       </c>
@@ -7565,7 +7579,7 @@
       </c>
       <c r="AD55" s="1"/>
       <c r="AE55" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF55" s="10">
@@ -7636,7 +7650,7 @@
         <v>10</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="M56" s="1"/>
@@ -7645,12 +7659,15 @@
         <v>0</v>
       </c>
       <c r="P56" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="Q56" s="5"/>
       <c r="R56" s="5"/>
-      <c r="S56" s="5"/>
+      <c r="S56" s="5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="T56" s="5">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -7658,13 +7675,13 @@
       <c r="U56" s="5"/>
       <c r="V56" s="1"/>
       <c r="W56" s="1">
+        <f t="shared" si="18"/>
+        <v>19.545454545454543</v>
+      </c>
+      <c r="X56" s="1">
         <f t="shared" si="19"/>
         <v>19.545454545454543</v>
       </c>
-      <c r="X56" s="1">
-        <f t="shared" si="20"/>
-        <v>19.545454545454543</v>
-      </c>
       <c r="Y56" s="1">
         <v>5.2</v>
       </c>
@@ -7684,7 +7701,7 @@
         <v>79</v>
       </c>
       <c r="AE56" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF56" s="10">
@@ -7755,7 +7772,7 @@
         <v>1</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M57" s="1"/>
@@ -7764,12 +7781,15 @@
         <v>0</v>
       </c>
       <c r="P57" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0.2</v>
       </c>
       <c r="Q57" s="5"/>
       <c r="R57" s="5"/>
-      <c r="S57" s="5"/>
+      <c r="S57" s="5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="T57" s="5">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -7777,13 +7797,13 @@
       <c r="U57" s="5"/>
       <c r="V57" s="1"/>
       <c r="W57" s="1">
+        <f t="shared" si="18"/>
+        <v>380</v>
+      </c>
+      <c r="X57" s="1">
         <f t="shared" si="19"/>
         <v>380</v>
       </c>
-      <c r="X57" s="1">
-        <f t="shared" si="20"/>
-        <v>380</v>
-      </c>
       <c r="Y57" s="1">
         <v>0.8</v>
       </c>
@@ -7803,7 +7823,7 @@
         <v>69</v>
       </c>
       <c r="AE57" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF57" s="10">
@@ -7876,7 +7896,7 @@
         <v>365</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-7</v>
       </c>
       <c r="M58" s="1"/>
@@ -7885,7 +7905,7 @@
         <v>336</v>
       </c>
       <c r="P58" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>71.599999999999994</v>
       </c>
       <c r="Q58" s="5">
@@ -7895,23 +7915,23 @@
         <v>580</v>
       </c>
       <c r="S58" s="5">
-        <f t="shared" ref="S58:S64" si="24">R58*$S$1</f>
-        <v>835.19999999999993</v>
+        <f t="shared" ref="S58:S59" si="22">R58*$S$1</f>
+        <v>481.4</v>
       </c>
       <c r="T58" s="5">
         <f t="shared" si="12"/>
-        <v>840</v>
+        <v>504</v>
       </c>
       <c r="U58" s="29">
         <v>580</v>
       </c>
       <c r="V58" s="19"/>
       <c r="W58" s="1">
+        <f t="shared" si="18"/>
+        <v>14.217877094972069</v>
+      </c>
+      <c r="X58" s="1">
         <f t="shared" si="19"/>
-        <v>18.910614525139668</v>
-      </c>
-      <c r="X58" s="1">
-        <f t="shared" si="20"/>
         <v>7.1787709497206711</v>
       </c>
       <c r="Y58" s="1">
@@ -7933,19 +7953,19 @@
         <v>66</v>
       </c>
       <c r="AE58" s="10">
-        <f t="shared" si="22"/>
-        <v>250.55999999999997</v>
+        <f t="shared" si="20"/>
+        <v>144.41999999999999</v>
       </c>
       <c r="AF58" s="10">
         <v>12</v>
       </c>
       <c r="AG58" s="1">
         <f t="shared" si="13"/>
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AH58" s="1">
         <f t="shared" si="14"/>
-        <v>252</v>
+        <v>151.19999999999999</v>
       </c>
       <c r="AI58" s="1">
         <v>14</v>
@@ -7955,7 +7975,7 @@
       </c>
       <c r="AK58" s="10">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AL58" s="1"/>
       <c r="AM58" s="1"/>
@@ -8006,7 +8026,7 @@
         <v>403</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>6</v>
       </c>
       <c r="M59" s="1"/>
@@ -8015,7 +8035,7 @@
         <v>168</v>
       </c>
       <c r="P59" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>81.8</v>
       </c>
       <c r="Q59" s="5">
@@ -8025,23 +8045,23 @@
         <v>800</v>
       </c>
       <c r="S59" s="5">
-        <f t="shared" si="24"/>
-        <v>1152</v>
+        <f t="shared" si="22"/>
+        <v>664</v>
       </c>
       <c r="T59" s="5">
         <f t="shared" si="12"/>
-        <v>1176</v>
+        <v>672</v>
       </c>
       <c r="U59" s="29">
         <v>800</v>
       </c>
       <c r="V59" s="19"/>
       <c r="W59" s="1">
+        <f t="shared" si="18"/>
+        <v>15.097799511002446</v>
+      </c>
+      <c r="X59" s="1">
         <f t="shared" si="19"/>
-        <v>21.25916870415648</v>
-      </c>
-      <c r="X59" s="1">
-        <f t="shared" si="20"/>
         <v>6.8826405867970664</v>
       </c>
       <c r="Y59" s="1">
@@ -8063,19 +8083,19 @@
         <v>66</v>
       </c>
       <c r="AE59" s="10">
-        <f t="shared" si="22"/>
-        <v>345.59999999999997</v>
+        <f t="shared" si="20"/>
+        <v>199.2</v>
       </c>
       <c r="AF59" s="10">
         <v>12</v>
       </c>
       <c r="AG59" s="1">
         <f t="shared" si="13"/>
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="AH59" s="1">
         <f t="shared" si="14"/>
-        <v>352.8</v>
+        <v>201.6</v>
       </c>
       <c r="AI59" s="1">
         <v>14</v>
@@ -8085,7 +8105,7 @@
       </c>
       <c r="AK59" s="10">
         <f t="shared" si="15"/>
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="AL59" s="1"/>
       <c r="AM59" s="1"/>
@@ -8136,7 +8156,7 @@
         <v>100</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-21</v>
       </c>
       <c r="M60" s="1"/>
@@ -8145,7 +8165,7 @@
         <v>0</v>
       </c>
       <c r="P60" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>15.8</v>
       </c>
       <c r="Q60" s="5">
@@ -8155,8 +8175,8 @@
         <v>300</v>
       </c>
       <c r="S60" s="5">
-        <f t="shared" si="24"/>
-        <v>432</v>
+        <f t="shared" si="11"/>
+        <v>300</v>
       </c>
       <c r="T60" s="5">
         <f t="shared" si="12"/>
@@ -8167,11 +8187,11 @@
       </c>
       <c r="V60" s="19"/>
       <c r="W60" s="1">
+        <f t="shared" si="18"/>
+        <v>24.683544303797468</v>
+      </c>
+      <c r="X60" s="1">
         <f t="shared" si="19"/>
-        <v>24.683544303797468</v>
-      </c>
-      <c r="X60" s="1">
-        <f t="shared" si="20"/>
         <v>-0.12658227848101264</v>
       </c>
       <c r="Y60" s="1">
@@ -8191,8 +8211,8 @@
       </c>
       <c r="AD60" s="1"/>
       <c r="AE60" s="10">
-        <f t="shared" si="22"/>
-        <v>129.6</v>
+        <f t="shared" si="20"/>
+        <v>90</v>
       </c>
       <c r="AF60" s="10">
         <v>14</v>
@@ -8264,7 +8284,7 @@
         <v>653</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-7</v>
       </c>
       <c r="M61" s="1"/>
@@ -8273,7 +8293,7 @@
         <v>336</v>
       </c>
       <c r="P61" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>129.19999999999999</v>
       </c>
       <c r="Q61" s="5">
@@ -8283,23 +8303,23 @@
         <v>700</v>
       </c>
       <c r="S61" s="5">
-        <f t="shared" si="24"/>
-        <v>1008</v>
+        <f t="shared" ref="S61:S62" si="23">R61*$S$1</f>
+        <v>581</v>
       </c>
       <c r="T61" s="5">
         <f t="shared" si="12"/>
-        <v>1008</v>
+        <v>504</v>
       </c>
       <c r="U61" s="29">
         <v>700</v>
       </c>
       <c r="V61" s="19"/>
       <c r="W61" s="1">
+        <f t="shared" si="18"/>
+        <v>13.560371517027866</v>
+      </c>
+      <c r="X61" s="1">
         <f t="shared" si="19"/>
-        <v>17.461300309597526</v>
-      </c>
-      <c r="X61" s="1">
-        <f t="shared" si="20"/>
         <v>9.6594427244582057</v>
       </c>
       <c r="Y61" s="1">
@@ -8321,19 +8341,19 @@
         <v>66</v>
       </c>
       <c r="AE61" s="10">
-        <f t="shared" si="22"/>
-        <v>252</v>
+        <f t="shared" si="20"/>
+        <v>145.25</v>
       </c>
       <c r="AF61" s="10">
         <v>12</v>
       </c>
       <c r="AG61" s="1">
         <f t="shared" si="13"/>
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="AH61" s="1">
         <f t="shared" si="14"/>
-        <v>252</v>
+        <v>126</v>
       </c>
       <c r="AI61" s="1">
         <v>14</v>
@@ -8343,7 +8363,7 @@
       </c>
       <c r="AK61" s="10">
         <f t="shared" si="15"/>
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AL61" s="1"/>
       <c r="AM61" s="1"/>
@@ -8394,7 +8414,7 @@
         <v>676</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>6</v>
       </c>
       <c r="M62" s="1"/>
@@ -8403,7 +8423,7 @@
         <v>1512</v>
       </c>
       <c r="P62" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>136.4</v>
       </c>
       <c r="Q62" s="5">
@@ -8413,23 +8433,23 @@
         <v>700</v>
       </c>
       <c r="S62" s="5">
-        <f t="shared" si="24"/>
-        <v>1008</v>
+        <f t="shared" si="23"/>
+        <v>581</v>
       </c>
       <c r="T62" s="5">
         <f t="shared" si="12"/>
-        <v>1008</v>
+        <v>504</v>
       </c>
       <c r="U62" s="29">
         <v>700</v>
       </c>
       <c r="V62" s="19"/>
       <c r="W62" s="1">
+        <f t="shared" si="18"/>
+        <v>15.227272727272727</v>
+      </c>
+      <c r="X62" s="1">
         <f t="shared" si="19"/>
-        <v>18.922287390029325</v>
-      </c>
-      <c r="X62" s="1">
-        <f t="shared" si="20"/>
         <v>11.532258064516128</v>
       </c>
       <c r="Y62" s="1">
@@ -8451,19 +8471,19 @@
         <v>66</v>
       </c>
       <c r="AE62" s="10">
-        <f t="shared" si="22"/>
-        <v>252</v>
+        <f t="shared" si="20"/>
+        <v>145.25</v>
       </c>
       <c r="AF62" s="10">
         <v>12</v>
       </c>
       <c r="AG62" s="1">
         <f t="shared" si="13"/>
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="AH62" s="1">
         <f t="shared" si="14"/>
-        <v>252</v>
+        <v>126</v>
       </c>
       <c r="AI62" s="1">
         <v>14</v>
@@ -8473,7 +8493,7 @@
       </c>
       <c r="AK62" s="10">
         <f t="shared" si="15"/>
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="AL62" s="1"/>
       <c r="AM62" s="1"/>
@@ -8522,7 +8542,7 @@
         <v>131</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>-5</v>
       </c>
       <c r="M63" s="1"/>
@@ -8531,7 +8551,7 @@
         <v>0</v>
       </c>
       <c r="P63" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>25.2</v>
       </c>
       <c r="Q63" s="5">
@@ -8541,21 +8561,21 @@
         <v>219.39999999999998</v>
       </c>
       <c r="S63" s="5">
-        <f t="shared" si="24"/>
-        <v>315.93599999999998</v>
+        <f t="shared" si="11"/>
+        <v>219.39999999999998</v>
       </c>
       <c r="T63" s="5">
         <f t="shared" si="12"/>
-        <v>336</v>
+        <v>252</v>
       </c>
       <c r="U63" s="5"/>
       <c r="V63" s="1"/>
       <c r="W63" s="1">
+        <f t="shared" si="18"/>
+        <v>13.293650793650794</v>
+      </c>
+      <c r="X63" s="1">
         <f t="shared" si="19"/>
-        <v>16.626984126984127</v>
-      </c>
-      <c r="X63" s="1">
-        <f t="shared" si="20"/>
         <v>3.2936507936507939</v>
       </c>
       <c r="Y63" s="1">
@@ -8575,19 +8595,19 @@
       </c>
       <c r="AD63" s="1"/>
       <c r="AE63" s="10">
-        <f t="shared" si="22"/>
-        <v>63.187199999999997</v>
+        <f t="shared" si="20"/>
+        <v>43.879999999999995</v>
       </c>
       <c r="AF63" s="10">
         <v>6</v>
       </c>
       <c r="AG63" s="1">
         <f t="shared" si="13"/>
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="AH63" s="1">
         <f t="shared" si="14"/>
-        <v>67.2</v>
+        <v>50.400000000000006</v>
       </c>
       <c r="AI63" s="1">
         <v>14</v>
@@ -8597,7 +8617,7 @@
       </c>
       <c r="AK63" s="10">
         <f t="shared" si="15"/>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="AL63" s="1"/>
       <c r="AM63" s="1"/>
@@ -8648,7 +8668,7 @@
         <v>233</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M64" s="1"/>
@@ -8657,7 +8677,7 @@
         <v>672</v>
       </c>
       <c r="P64" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>46.6</v>
       </c>
       <c r="Q64" s="5"/>
@@ -8665,23 +8685,23 @@
         <v>200</v>
       </c>
       <c r="S64" s="5">
-        <f t="shared" si="24"/>
-        <v>288</v>
+        <f t="shared" si="11"/>
+        <v>200</v>
       </c>
       <c r="T64" s="5">
         <f t="shared" si="12"/>
-        <v>252</v>
+        <v>168</v>
       </c>
       <c r="U64" s="29">
         <v>200</v>
       </c>
       <c r="V64" s="19"/>
       <c r="W64" s="1">
+        <f t="shared" si="18"/>
+        <v>18.047210300429185</v>
+      </c>
+      <c r="X64" s="1">
         <f t="shared" si="19"/>
-        <v>19.849785407725321</v>
-      </c>
-      <c r="X64" s="1">
-        <f t="shared" si="20"/>
         <v>14.442060085836909</v>
       </c>
       <c r="Y64" s="1">
@@ -8701,19 +8721,19 @@
       </c>
       <c r="AD64" s="1"/>
       <c r="AE64" s="10">
-        <f t="shared" si="22"/>
-        <v>66.240000000000009</v>
+        <f t="shared" si="20"/>
+        <v>46</v>
       </c>
       <c r="AF64" s="10">
         <v>6</v>
       </c>
       <c r="AG64" s="1">
         <f t="shared" si="13"/>
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AH64" s="1">
         <f t="shared" si="14"/>
-        <v>57.96</v>
+        <v>38.64</v>
       </c>
       <c r="AI64" s="1">
         <v>14</v>
@@ -8723,7 +8743,7 @@
       </c>
       <c r="AK64" s="10">
         <f t="shared" si="15"/>
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AL64" s="1"/>
       <c r="AM64" s="1"/>
@@ -8774,7 +8794,7 @@
         <v>48</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0.60000000000000142</v>
       </c>
       <c r="M65" s="1"/>
@@ -8783,12 +8803,15 @@
         <v>151.19999999999999</v>
       </c>
       <c r="P65" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>9.7200000000000006</v>
       </c>
       <c r="Q65" s="5"/>
       <c r="R65" s="5"/>
-      <c r="S65" s="5"/>
+      <c r="S65" s="5">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="T65" s="5">
         <f t="shared" si="12"/>
         <v>0</v>
@@ -8796,13 +8819,13 @@
       <c r="U65" s="5"/>
       <c r="V65" s="1"/>
       <c r="W65" s="1">
+        <f t="shared" si="18"/>
+        <v>18.888888888888886</v>
+      </c>
+      <c r="X65" s="1">
         <f t="shared" si="19"/>
         <v>18.888888888888886</v>
       </c>
-      <c r="X65" s="1">
-        <f t="shared" si="20"/>
-        <v>18.888888888888886</v>
-      </c>
       <c r="Y65" s="1">
         <v>6.48</v>
       </c>
@@ -8820,7 +8843,7 @@
       </c>
       <c r="AD65" s="1"/>
       <c r="AE65" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AF65" s="10">
@@ -8891,7 +8914,7 @@
         <v>394.5</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>28.199999999999989</v>
       </c>
       <c r="M66" s="1"/>
@@ -8900,7 +8923,7 @@
         <v>180</v>
       </c>
       <c r="P66" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>84.539999999999992</v>
       </c>
       <c r="Q66" s="5">
@@ -8911,20 +8934,20 @@
       </c>
       <c r="S66" s="5">
         <f>R66*$S$1</f>
-        <v>677.28959999999984</v>
+        <v>390.3821999999999</v>
       </c>
       <c r="T66" s="5">
         <f t="shared" si="12"/>
-        <v>660</v>
+        <v>420</v>
       </c>
       <c r="U66" s="5"/>
       <c r="V66" s="1"/>
       <c r="W66" s="1">
+        <f t="shared" si="18"/>
+        <v>10.404542228530874</v>
+      </c>
+      <c r="X66" s="1">
         <f t="shared" si="19"/>
-        <v>13.243435060326473</v>
-      </c>
-      <c r="X66" s="1">
-        <f t="shared" si="20"/>
         <v>5.4364797728885739</v>
       </c>
       <c r="Y66" s="1">
@@ -8944,19 +8967,19 @@
       </c>
       <c r="AD66" s="1"/>
       <c r="AE66" s="10">
-        <f t="shared" si="22"/>
-        <v>677.28959999999984</v>
+        <f t="shared" si="20"/>
+        <v>390.3821999999999</v>
       </c>
       <c r="AF66" s="10">
         <v>5</v>
       </c>
       <c r="AG66" s="1">
         <f t="shared" si="13"/>
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="AH66" s="1">
         <f t="shared" si="14"/>
-        <v>660</v>
+        <v>420</v>
       </c>
       <c r="AI66" s="1">
         <v>12</v>
@@ -8966,7 +8989,7 @@
       </c>
       <c r="AK66" s="10">
         <f t="shared" si="15"/>
-        <v>1.5714285714285714</v>
+        <v>1</v>
       </c>
       <c r="AL66" s="1"/>
       <c r="AM66" s="1"/>
@@ -9017,7 +9040,7 @@
         <v>12.7</v>
       </c>
       <c r="L67" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M67" s="23"/>
@@ -9026,7 +9049,7 @@
         <v>0</v>
       </c>
       <c r="P67" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>2.54</v>
       </c>
       <c r="Q67" s="25"/>
@@ -9039,11 +9062,11 @@
       <c r="U67" s="25"/>
       <c r="V67" s="23"/>
       <c r="W67" s="23">
+        <f t="shared" si="18"/>
+        <v>109.1732283464567</v>
+      </c>
+      <c r="X67" s="23">
         <f t="shared" si="19"/>
-        <v>109.1732283464567</v>
-      </c>
-      <c r="X67" s="23">
-        <f t="shared" si="20"/>
         <v>109.1732283464567</v>
       </c>
       <c r="Y67" s="23">
@@ -9116,7 +9139,7 @@
         <v>0</v>
       </c>
       <c r="P68" s="19">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Q68" s="29">
@@ -9127,11 +9150,11 @@
       </c>
       <c r="S68" s="5">
         <f>R68*$S$1</f>
-        <v>792</v>
+        <v>456.5</v>
       </c>
       <c r="T68" s="29">
         <f t="shared" si="12"/>
-        <v>792</v>
+        <v>468</v>
       </c>
       <c r="U68" s="29">
         <v>550</v>
@@ -9140,13 +9163,13 @@
         <v>169</v>
       </c>
       <c r="W68" s="19" t="e">
+        <f t="shared" si="18"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X68" s="19" t="e">
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X68" s="19" t="e">
-        <f t="shared" si="20"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="Y68" s="19">
         <v>14.4</v>
       </c>
@@ -9164,19 +9187,19 @@
       </c>
       <c r="AD68" s="19"/>
       <c r="AE68" s="19">
-        <f t="shared" ref="AE68" si="25">G68*S68</f>
-        <v>792</v>
+        <f t="shared" ref="AE68" si="24">G68*S68</f>
+        <v>456.5</v>
       </c>
       <c r="AF68" s="30">
         <v>3</v>
       </c>
       <c r="AG68" s="19">
-        <f t="shared" ref="AG68" si="26">MROUND(S68, AF68*AI68)/AF68</f>
-        <v>264</v>
+        <f t="shared" ref="AG68" si="25">MROUND(S68, AF68*AI68)/AF68</f>
+        <v>156</v>
       </c>
       <c r="AH68" s="19">
-        <f t="shared" ref="AH68" si="27">AG68*AF68*G68</f>
-        <v>792</v>
+        <f t="shared" ref="AH68" si="26">AG68*AF68*G68</f>
+        <v>468</v>
       </c>
       <c r="AI68" s="19">
         <v>12</v>
@@ -9185,8 +9208,8 @@
         <v>84</v>
       </c>
       <c r="AK68" s="30">
-        <f t="shared" ref="AK68" si="28">AG68/AJ68</f>
-        <v>3.1428571428571428</v>
+        <f t="shared" ref="AK68" si="27">AG68/AJ68</f>
+        <v>1.8571428571428572</v>
       </c>
       <c r="AL68" s="19"/>
       <c r="AM68" s="19"/>

--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/06,26/26,06,26 ПОКОМ ЗПФ/Копия дв 250626 бррсч пок зпф от Боярко.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/06,26/26,06,26 ПОКОМ ЗПФ/Копия дв 250626 бррсч пок зпф от Боярко.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\06,26\26,06,26 ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{432BB1E5-59B6-439A-9518-4DED38F60F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F3371B7-6E2A-4523-A3DE-C07088A73293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -553,7 +553,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.00_ ;[Red]\-0.00\ "/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -606,6 +606,22 @@
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
@@ -694,7 +710,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -716,9 +732,6 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="1" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
@@ -731,6 +744,16 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1050,21 +1073,23 @@
     <col min="13" max="14" width="0.85546875" customWidth="1"/>
     <col min="15" max="16" width="6" customWidth="1"/>
     <col min="17" max="17" width="7" customWidth="1"/>
-    <col min="18" max="18" width="7" style="32" customWidth="1"/>
+    <col min="18" max="18" width="7" style="31" customWidth="1"/>
     <col min="19" max="19" width="7" customWidth="1"/>
-    <col min="20" max="20" width="9.42578125" customWidth="1"/>
+    <col min="20" max="20" width="9.42578125" style="40" customWidth="1"/>
     <col min="21" max="21" width="7" customWidth="1"/>
     <col min="22" max="22" width="15" customWidth="1"/>
     <col min="23" max="24" width="5" customWidth="1"/>
     <col min="25" max="29" width="6" customWidth="1"/>
-    <col min="30" max="30" width="28.7109375" customWidth="1"/>
+    <col min="30" max="30" width="17.28515625" customWidth="1"/>
     <col min="31" max="31" width="7.7109375" style="13" customWidth="1"/>
     <col min="32" max="32" width="6" style="13" customWidth="1"/>
     <col min="33" max="33" width="7" customWidth="1"/>
     <col min="34" max="34" width="7.7109375" customWidth="1"/>
     <col min="35" max="36" width="5" customWidth="1"/>
     <col min="37" max="37" width="6" style="13" customWidth="1"/>
-    <col min="38" max="52" width="3" customWidth="1"/>
+    <col min="38" max="38" width="3" customWidth="1"/>
+    <col min="39" max="39" width="8.5703125" customWidth="1"/>
+    <col min="40" max="52" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:52" x14ac:dyDescent="0.25">
@@ -1086,10 +1111,10 @@
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
-      <c r="S1" s="33">
+      <c r="S1" s="32">
         <v>0.83</v>
       </c>
-      <c r="T1" s="1"/>
+      <c r="T1" s="33"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
@@ -1143,7 +1168,7 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
-      <c r="T2" s="21" t="s">
+      <c r="T2" s="34" t="s">
         <v>0</v>
       </c>
       <c r="U2" s="1"/>
@@ -1331,7 +1356,7 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
+      <c r="T4" s="33"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
@@ -1429,7 +1454,7 @@
         <f t="shared" si="0"/>
         <v>13619.562199999997</v>
       </c>
-      <c r="T5" s="4">
+      <c r="T5" s="35">
         <f t="shared" si="0"/>
         <v>14001.8</v>
       </c>
@@ -1481,7 +1506,10 @@
         <v>19.358730158730165</v>
       </c>
       <c r="AL5" s="1"/>
-      <c r="AM5" s="1"/>
+      <c r="AM5" s="17">
+        <f>SUM(AM6:AM498)</f>
+        <v>1133.9359999999999</v>
+      </c>
       <c r="AN5" s="1"/>
       <c r="AO5" s="1"/>
       <c r="AP5" s="1"/>
@@ -1507,10 +1535,10 @@
         <v>-27</v>
       </c>
       <c r="D6" s="6"/>
-      <c r="E6" s="22">
+      <c r="E6" s="21">
         <v>45</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="21">
         <v>-70</v>
       </c>
       <c r="G6" s="16">
@@ -1542,7 +1570,7 @@
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
+      <c r="T6" s="36"/>
       <c r="U6" s="7"/>
       <c r="V6" s="6"/>
       <c r="W6" s="6">
@@ -1603,10 +1631,10 @@
         <v>109</v>
       </c>
       <c r="D7" s="6"/>
-      <c r="E7" s="22">
+      <c r="E7" s="21">
         <v>69</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="21">
         <v>24</v>
       </c>
       <c r="G7" s="16">
@@ -1638,7 +1666,7 @@
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
+      <c r="T7" s="36"/>
       <c r="U7" s="7"/>
       <c r="V7" s="6"/>
       <c r="W7" s="6">
@@ -1701,10 +1729,10 @@
       <c r="D8" s="6">
         <v>3</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="21">
         <v>26</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="21">
         <v>32</v>
       </c>
       <c r="G8" s="16">
@@ -1736,7 +1764,7 @@
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
+      <c r="T8" s="36"/>
       <c r="U8" s="7"/>
       <c r="V8" s="6"/>
       <c r="W8" s="6">
@@ -1835,11 +1863,11 @@
         <f>R9</f>
         <v>100</v>
       </c>
-      <c r="T9" s="5">
+      <c r="T9" s="37">
         <f t="shared" ref="T9:T29" si="5">AF9*AG9</f>
         <v>168</v>
       </c>
-      <c r="U9" s="29">
+      <c r="U9" s="28">
         <v>100</v>
       </c>
       <c r="V9" s="19"/>
@@ -1893,7 +1921,10 @@
         <v>0.2</v>
       </c>
       <c r="AL9" s="1"/>
-      <c r="AM9" s="1"/>
+      <c r="AM9" s="1">
+        <f>P9*G9</f>
+        <v>2.42</v>
+      </c>
       <c r="AN9" s="1"/>
       <c r="AO9" s="1"/>
       <c r="AP9" s="1"/>
@@ -1957,11 +1988,11 @@
         <f t="shared" ref="S10:S29" si="10">R10</f>
         <v>100</v>
       </c>
-      <c r="T10" s="5">
+      <c r="T10" s="37">
         <f t="shared" si="5"/>
         <v>168</v>
       </c>
-      <c r="U10" s="29">
+      <c r="U10" s="28">
         <v>100</v>
       </c>
       <c r="V10" s="19"/>
@@ -2015,7 +2046,10 @@
         <v>0.2</v>
       </c>
       <c r="AL10" s="1"/>
-      <c r="AM10" s="1"/>
+      <c r="AM10" s="1">
+        <f t="shared" ref="AM10:AM67" si="11">P10*G10</f>
+        <v>6.06</v>
+      </c>
       <c r="AN10" s="1"/>
       <c r="AO10" s="1"/>
       <c r="AP10" s="1"/>
@@ -2083,7 +2117,7 @@
         <f>R11*$S$1</f>
         <v>543.65</v>
       </c>
-      <c r="T11" s="5">
+      <c r="T11" s="37">
         <f t="shared" si="5"/>
         <v>504</v>
       </c>
@@ -2139,7 +2173,10 @@
         <v>0.6</v>
       </c>
       <c r="AL11" s="1"/>
-      <c r="AM11" s="1"/>
+      <c r="AM11" s="1">
+        <f t="shared" si="11"/>
+        <v>20.160000000000004</v>
+      </c>
       <c r="AN11" s="1"/>
       <c r="AO11" s="1"/>
       <c r="AP11" s="1"/>
@@ -2205,11 +2242,11 @@
         <f t="shared" si="10"/>
         <v>200</v>
       </c>
-      <c r="T12" s="5">
+      <c r="T12" s="37">
         <f t="shared" si="5"/>
         <v>168</v>
       </c>
-      <c r="U12" s="29">
+      <c r="U12" s="28">
         <v>200</v>
       </c>
       <c r="V12" s="19"/>
@@ -2263,7 +2300,10 @@
         <v>0.2</v>
       </c>
       <c r="AL12" s="1"/>
-      <c r="AM12" s="1"/>
+      <c r="AM12" s="1">
+        <f t="shared" si="11"/>
+        <v>9.36</v>
+      </c>
       <c r="AN12" s="1"/>
       <c r="AO12" s="1"/>
       <c r="AP12" s="1"/>
@@ -2331,11 +2371,11 @@
         <f t="shared" si="10"/>
         <v>300</v>
       </c>
-      <c r="T13" s="5">
+      <c r="T13" s="37">
         <f t="shared" si="5"/>
         <v>336</v>
       </c>
-      <c r="U13" s="29">
+      <c r="U13" s="28">
         <v>300</v>
       </c>
       <c r="V13" s="19"/>
@@ -2389,7 +2429,10 @@
         <v>0.4</v>
       </c>
       <c r="AL13" s="1"/>
-      <c r="AM13" s="1"/>
+      <c r="AM13" s="1">
+        <f t="shared" si="11"/>
+        <v>19.343999999999998</v>
+      </c>
       <c r="AN13" s="1"/>
       <c r="AO13" s="1"/>
       <c r="AP13" s="1"/>
@@ -2457,11 +2500,11 @@
         <f t="shared" si="10"/>
         <v>300</v>
       </c>
-      <c r="T14" s="5">
+      <c r="T14" s="37">
         <f t="shared" si="5"/>
         <v>336</v>
       </c>
-      <c r="U14" s="29">
+      <c r="U14" s="28">
         <v>300</v>
       </c>
       <c r="V14" s="19"/>
@@ -2515,7 +2558,10 @@
         <v>0.4</v>
       </c>
       <c r="AL14" s="1"/>
-      <c r="AM14" s="1"/>
+      <c r="AM14" s="1">
+        <f t="shared" si="11"/>
+        <v>11.183999999999999</v>
+      </c>
       <c r="AN14" s="1"/>
       <c r="AO14" s="1"/>
       <c r="AP14" s="1"/>
@@ -2543,11 +2589,11 @@
       <c r="D15" s="1">
         <v>514</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="21">
         <f>363+E6</f>
         <v>408</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="21">
         <f>439+F6</f>
         <v>369</v>
       </c>
@@ -2585,7 +2631,7 @@
         <f>R15*$S$1</f>
         <v>363.04199999999986</v>
       </c>
-      <c r="T15" s="5">
+      <c r="T15" s="37">
         <f t="shared" si="5"/>
         <v>336</v>
       </c>
@@ -2641,7 +2687,10 @@
         <v>0.4</v>
       </c>
       <c r="AL15" s="1"/>
-      <c r="AM15" s="1"/>
+      <c r="AM15" s="1">
+        <f t="shared" si="11"/>
+        <v>19.584</v>
+      </c>
       <c r="AN15" s="1"/>
       <c r="AO15" s="1"/>
       <c r="AP15" s="1"/>
@@ -2705,11 +2754,11 @@
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="T16" s="5">
+      <c r="T16" s="37">
         <f t="shared" si="5"/>
         <v>112</v>
       </c>
-      <c r="U16" s="29">
+      <c r="U16" s="28">
         <v>100</v>
       </c>
       <c r="V16" s="19"/>
@@ -2763,7 +2812,10 @@
         <v>0.2</v>
       </c>
       <c r="AL16" s="1"/>
-      <c r="AM16" s="1"/>
+      <c r="AM16" s="1">
+        <f t="shared" si="11"/>
+        <v>1.8239999999999998</v>
+      </c>
       <c r="AN16" s="1"/>
       <c r="AO16" s="1"/>
       <c r="AP16" s="1"/>
@@ -2825,11 +2877,11 @@
         <f t="shared" si="10"/>
         <v>180</v>
       </c>
-      <c r="T17" s="5">
+      <c r="T17" s="37">
         <f t="shared" si="5"/>
         <v>336</v>
       </c>
-      <c r="U17" s="29">
+      <c r="U17" s="28">
         <v>150</v>
       </c>
       <c r="V17" s="19"/>
@@ -2883,7 +2935,10 @@
         <v>0.1111111111111111</v>
       </c>
       <c r="AL17" s="1"/>
-      <c r="AM17" s="1"/>
+      <c r="AM17" s="1">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AN17" s="1"/>
       <c r="AO17" s="1"/>
       <c r="AP17" s="1"/>
@@ -2947,7 +3002,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="T18" s="5">
+      <c r="T18" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3005,7 +3060,10 @@
         <v>0</v>
       </c>
       <c r="AL18" s="1"/>
-      <c r="AM18" s="1"/>
+      <c r="AM18" s="1">
+        <f t="shared" si="11"/>
+        <v>6.1919999999999993</v>
+      </c>
       <c r="AN18" s="1"/>
       <c r="AO18" s="1"/>
       <c r="AP18" s="1"/>
@@ -3067,7 +3125,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="T19" s="5">
+      <c r="T19" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -3125,7 +3183,10 @@
         <v>0</v>
       </c>
       <c r="AL19" s="1"/>
-      <c r="AM19" s="1"/>
+      <c r="AM19" s="1">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AN19" s="1"/>
       <c r="AO19" s="1"/>
       <c r="AP19" s="1"/>
@@ -3189,11 +3250,11 @@
         <f t="shared" si="10"/>
         <v>200</v>
       </c>
-      <c r="T20" s="5">
+      <c r="T20" s="37">
         <f t="shared" si="5"/>
         <v>168</v>
       </c>
-      <c r="U20" s="29">
+      <c r="U20" s="28">
         <v>200</v>
       </c>
       <c r="V20" s="19"/>
@@ -3247,7 +3308,10 @@
         <v>0.2</v>
       </c>
       <c r="AL20" s="1"/>
-      <c r="AM20" s="1"/>
+      <c r="AM20" s="1">
+        <f t="shared" si="11"/>
+        <v>0.32000000000000006</v>
+      </c>
       <c r="AN20" s="1"/>
       <c r="AO20" s="1"/>
       <c r="AP20" s="1"/>
@@ -3315,11 +3379,11 @@
         <f t="shared" si="10"/>
         <v>200</v>
       </c>
-      <c r="T21" s="5">
+      <c r="T21" s="37">
         <f t="shared" si="5"/>
         <v>168</v>
       </c>
-      <c r="U21" s="29">
+      <c r="U21" s="28">
         <v>200</v>
       </c>
       <c r="V21" s="19"/>
@@ -3373,7 +3437,10 @@
         <v>0.2</v>
       </c>
       <c r="AL21" s="1"/>
-      <c r="AM21" s="1"/>
+      <c r="AM21" s="1">
+        <f t="shared" si="11"/>
+        <v>5.7200000000000006</v>
+      </c>
       <c r="AN21" s="1"/>
       <c r="AO21" s="1"/>
       <c r="AP21" s="1"/>
@@ -3441,11 +3508,11 @@
         <f t="shared" si="10"/>
         <v>200</v>
       </c>
-      <c r="T22" s="5">
+      <c r="T22" s="37">
         <f t="shared" si="5"/>
         <v>168</v>
       </c>
-      <c r="U22" s="29">
+      <c r="U22" s="28">
         <v>200</v>
       </c>
       <c r="V22" s="19"/>
@@ -3499,7 +3566,10 @@
         <v>0.2</v>
       </c>
       <c r="AL22" s="1"/>
-      <c r="AM22" s="1"/>
+      <c r="AM22" s="1">
+        <f t="shared" si="11"/>
+        <v>5.2</v>
+      </c>
       <c r="AN22" s="1"/>
       <c r="AO22" s="1"/>
       <c r="AP22" s="1"/>
@@ -3563,11 +3633,11 @@
         <f t="shared" si="10"/>
         <v>70</v>
       </c>
-      <c r="T23" s="5">
+      <c r="T23" s="37">
         <f t="shared" si="5"/>
         <v>60</v>
       </c>
-      <c r="U23" s="29">
+      <c r="U23" s="28">
         <v>70</v>
       </c>
       <c r="V23" s="19"/>
@@ -3623,7 +3693,10 @@
         <v>0.14285714285714285</v>
       </c>
       <c r="AL23" s="1"/>
-      <c r="AM23" s="1"/>
+      <c r="AM23" s="1">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AN23" s="1"/>
       <c r="AO23" s="1"/>
       <c r="AP23" s="1"/>
@@ -3691,11 +3764,11 @@
         <f t="shared" si="10"/>
         <v>200</v>
       </c>
-      <c r="T24" s="5">
+      <c r="T24" s="37">
         <f t="shared" si="5"/>
         <v>210</v>
       </c>
-      <c r="U24" s="29">
+      <c r="U24" s="28">
         <v>200</v>
       </c>
       <c r="V24" s="19"/>
@@ -3749,7 +3822,10 @@
         <v>0.55555555555555558</v>
       </c>
       <c r="AL24" s="1"/>
-      <c r="AM24" s="1"/>
+      <c r="AM24" s="1">
+        <f t="shared" si="11"/>
+        <v>14.4</v>
+      </c>
       <c r="AN24" s="1"/>
       <c r="AO24" s="1"/>
       <c r="AP24" s="1"/>
@@ -3817,11 +3893,11 @@
         <f t="shared" si="10"/>
         <v>300</v>
       </c>
-      <c r="T25" s="5">
+      <c r="T25" s="37">
         <f t="shared" si="5"/>
         <v>336</v>
       </c>
-      <c r="U25" s="29">
+      <c r="U25" s="28">
         <v>300</v>
       </c>
       <c r="V25" s="19"/>
@@ -3877,7 +3953,10 @@
         <v>0.4</v>
       </c>
       <c r="AL25" s="1"/>
-      <c r="AM25" s="1"/>
+      <c r="AM25" s="1">
+        <f t="shared" si="11"/>
+        <v>18.75</v>
+      </c>
       <c r="AN25" s="1"/>
       <c r="AO25" s="1"/>
       <c r="AP25" s="1"/>
@@ -3945,11 +4024,11 @@
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="T26" s="5">
+      <c r="T26" s="37">
         <f t="shared" si="5"/>
         <v>84</v>
       </c>
-      <c r="U26" s="29">
+      <c r="U26" s="28">
         <v>100</v>
       </c>
       <c r="V26" s="19"/>
@@ -4005,7 +4084,10 @@
         <v>0.1</v>
       </c>
       <c r="AL26" s="1"/>
-      <c r="AM26" s="1"/>
+      <c r="AM26" s="1">
+        <f t="shared" si="11"/>
+        <v>3.6</v>
+      </c>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1"/>
       <c r="AP26" s="1"/>
@@ -4071,11 +4153,11 @@
         <f t="shared" si="10"/>
         <v>300</v>
       </c>
-      <c r="T27" s="5">
+      <c r="T27" s="37">
         <f t="shared" si="5"/>
         <v>336</v>
       </c>
-      <c r="U27" s="29">
+      <c r="U27" s="28">
         <v>300</v>
       </c>
       <c r="V27" s="19"/>
@@ -4129,7 +4211,10 @@
         <v>0.4</v>
       </c>
       <c r="AL27" s="1"/>
-      <c r="AM27" s="1"/>
+      <c r="AM27" s="1">
+        <f t="shared" si="11"/>
+        <v>4.6920000000000002</v>
+      </c>
       <c r="AN27" s="1"/>
       <c r="AO27" s="1"/>
       <c r="AP27" s="1"/>
@@ -4197,11 +4282,11 @@
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="T28" s="5">
+      <c r="T28" s="37">
         <f t="shared" si="5"/>
         <v>168</v>
       </c>
-      <c r="U28" s="29">
+      <c r="U28" s="28">
         <v>100</v>
       </c>
       <c r="V28" s="19"/>
@@ -4257,7 +4342,10 @@
         <v>0.2</v>
       </c>
       <c r="AL28" s="1"/>
-      <c r="AM28" s="1"/>
+      <c r="AM28" s="1">
+        <f t="shared" si="11"/>
+        <v>14.65</v>
+      </c>
       <c r="AN28" s="1"/>
       <c r="AO28" s="1"/>
       <c r="AP28" s="1"/>
@@ -4285,11 +4373,11 @@
       <c r="D29" s="1">
         <v>504</v>
       </c>
-      <c r="E29" s="22">
+      <c r="E29" s="21">
         <f>311+E30</f>
         <v>312</v>
       </c>
-      <c r="F29" s="22">
+      <c r="F29" s="21">
         <f>396+F30</f>
         <v>395</v>
       </c>
@@ -4323,7 +4411,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="T29" s="5">
+      <c r="T29" s="37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -4379,7 +4467,10 @@
         <v>0</v>
       </c>
       <c r="AL29" s="1"/>
-      <c r="AM29" s="1"/>
+      <c r="AM29" s="1">
+        <f t="shared" si="11"/>
+        <v>15.6</v>
+      </c>
       <c r="AN29" s="1"/>
       <c r="AO29" s="1"/>
       <c r="AP29" s="1"/>
@@ -4403,10 +4494,10 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
-      <c r="E30" s="22">
+      <c r="E30" s="21">
         <v>1</v>
       </c>
-      <c r="F30" s="22">
+      <c r="F30" s="21">
         <v>-1</v>
       </c>
       <c r="G30" s="16">
@@ -4436,7 +4527,7 @@
       <c r="Q30" s="7"/>
       <c r="R30" s="7"/>
       <c r="S30" s="7"/>
-      <c r="T30" s="7"/>
+      <c r="T30" s="36"/>
       <c r="U30" s="7"/>
       <c r="V30" s="6"/>
       <c r="W30" s="6">
@@ -4464,7 +4555,10 @@
       <c r="AJ30" s="6"/>
       <c r="AK30" s="12"/>
       <c r="AL30" s="1"/>
-      <c r="AM30" s="1"/>
+      <c r="AM30" s="1">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AN30" s="1"/>
       <c r="AO30" s="1"/>
       <c r="AP30" s="1"/>
@@ -4531,14 +4625,14 @@
         <v>300</v>
       </c>
       <c r="S31" s="5">
-        <f t="shared" ref="S31:S66" si="11">R31</f>
+        <f t="shared" ref="S31:S65" si="12">R31</f>
         <v>300</v>
       </c>
-      <c r="T31" s="5">
-        <f t="shared" ref="T31:T68" si="12">AF31*AG31</f>
+      <c r="T31" s="37">
+        <f t="shared" ref="T31:T68" si="13">AF31*AG31</f>
         <v>336</v>
       </c>
-      <c r="U31" s="29">
+      <c r="U31" s="28">
         <v>300</v>
       </c>
       <c r="V31" s="19"/>
@@ -4576,11 +4670,11 @@
         <v>12</v>
       </c>
       <c r="AG31" s="1">
-        <f t="shared" ref="AG31:AG66" si="13">MROUND(S31, AF31*AI31)/AF31</f>
+        <f t="shared" ref="AG31:AG66" si="14">MROUND(S31, AF31*AI31)/AF31</f>
         <v>28</v>
       </c>
       <c r="AH31" s="1">
-        <f t="shared" ref="AH31:AH66" si="14">AG31*AF31*G31</f>
+        <f t="shared" ref="AH31:AH66" si="15">AG31*AF31*G31</f>
         <v>84</v>
       </c>
       <c r="AI31" s="1">
@@ -4590,11 +4684,14 @@
         <v>70</v>
       </c>
       <c r="AK31" s="10">
-        <f t="shared" ref="AK31:AK66" si="15">AG31/AJ31</f>
+        <f t="shared" ref="AK31:AK66" si="16">AG31/AJ31</f>
         <v>0.4</v>
       </c>
       <c r="AL31" s="1"/>
-      <c r="AM31" s="1"/>
+      <c r="AM31" s="1">
+        <f t="shared" si="11"/>
+        <v>10.45</v>
+      </c>
       <c r="AN31" s="1"/>
       <c r="AO31" s="1"/>
       <c r="AP31" s="1"/>
@@ -4655,11 +4752,11 @@
       <c r="Q32" s="5"/>
       <c r="R32" s="5"/>
       <c r="S32" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="T32" s="5">
-        <f t="shared" si="12"/>
+      <c r="T32" s="37">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="U32" s="5"/>
@@ -4698,13 +4795,13 @@
         <v>12</v>
       </c>
       <c r="AG32" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AH32" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
+      <c r="AH32" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AI32" s="1">
         <v>14</v>
       </c>
@@ -4712,11 +4809,14 @@
         <v>70</v>
       </c>
       <c r="AK32" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AL32" s="1"/>
-      <c r="AM32" s="1"/>
+      <c r="AM32" s="1">
+        <f t="shared" si="11"/>
+        <v>1.1000000000000001</v>
+      </c>
       <c r="AN32" s="1"/>
       <c r="AO32" s="1"/>
       <c r="AP32" s="1"/>
@@ -4781,14 +4881,14 @@
         <v>100</v>
       </c>
       <c r="S33" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="T33" s="5">
-        <f t="shared" si="12"/>
+      <c r="T33" s="37">
+        <f t="shared" si="13"/>
         <v>96</v>
       </c>
-      <c r="U33" s="29">
+      <c r="U33" s="28">
         <v>100</v>
       </c>
       <c r="V33" s="19"/>
@@ -4824,11 +4924,11 @@
         <v>8</v>
       </c>
       <c r="AG33" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>12</v>
       </c>
       <c r="AH33" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>67.199999999999989</v>
       </c>
       <c r="AI33" s="1">
@@ -4838,11 +4938,14 @@
         <v>84</v>
       </c>
       <c r="AK33" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="AL33" s="1"/>
-      <c r="AM33" s="1"/>
+      <c r="AM33" s="1">
+        <f t="shared" si="11"/>
+        <v>12.04</v>
+      </c>
       <c r="AN33" s="1"/>
       <c r="AO33" s="1"/>
       <c r="AP33" s="1"/>
@@ -4907,14 +5010,14 @@
         <v>100</v>
       </c>
       <c r="S34" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="T34" s="5">
-        <f t="shared" si="12"/>
+      <c r="T34" s="37">
+        <f t="shared" si="13"/>
         <v>96</v>
       </c>
-      <c r="U34" s="29">
+      <c r="U34" s="28">
         <v>100</v>
       </c>
       <c r="V34" s="19"/>
@@ -4950,11 +5053,11 @@
         <v>8</v>
       </c>
       <c r="AG34" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>12</v>
       </c>
       <c r="AH34" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>67.199999999999989</v>
       </c>
       <c r="AI34" s="1">
@@ -4964,11 +5067,14 @@
         <v>84</v>
       </c>
       <c r="AK34" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="AL34" s="1"/>
-      <c r="AM34" s="1"/>
+      <c r="AM34" s="1">
+        <f t="shared" si="11"/>
+        <v>5.88</v>
+      </c>
       <c r="AN34" s="1"/>
       <c r="AO34" s="1"/>
       <c r="AP34" s="1"/>
@@ -5033,14 +5139,14 @@
         <v>100</v>
       </c>
       <c r="S35" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="T35" s="5">
-        <f t="shared" si="12"/>
+      <c r="T35" s="37">
+        <f t="shared" si="13"/>
         <v>96</v>
       </c>
-      <c r="U35" s="29">
+      <c r="U35" s="28">
         <v>100</v>
       </c>
       <c r="V35" s="19"/>
@@ -5076,11 +5182,11 @@
         <v>8</v>
       </c>
       <c r="AG35" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>12</v>
       </c>
       <c r="AH35" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>67.199999999999989</v>
       </c>
       <c r="AI35" s="1">
@@ -5090,11 +5196,14 @@
         <v>84</v>
       </c>
       <c r="AK35" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="AL35" s="1"/>
-      <c r="AM35" s="1"/>
+      <c r="AM35" s="1">
+        <f t="shared" si="11"/>
+        <v>11.899999999999999</v>
+      </c>
       <c r="AN35" s="1"/>
       <c r="AO35" s="1"/>
       <c r="AP35" s="1"/>
@@ -5164,11 +5273,11 @@
         <f>R36*$S$1</f>
         <v>415</v>
       </c>
-      <c r="T36" s="5">
-        <f t="shared" si="12"/>
+      <c r="T36" s="37">
+        <f t="shared" si="13"/>
         <v>360</v>
       </c>
-      <c r="U36" s="29">
+      <c r="U36" s="28">
         <v>500</v>
       </c>
       <c r="V36" s="19"/>
@@ -5204,11 +5313,11 @@
         <v>10</v>
       </c>
       <c r="AG36" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>36</v>
       </c>
       <c r="AH36" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>251.99999999999997</v>
       </c>
       <c r="AI36" s="1">
@@ -5218,11 +5327,14 @@
         <v>84</v>
       </c>
       <c r="AK36" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="AL36" s="1"/>
-      <c r="AM36" s="1"/>
+      <c r="AM36" s="1">
+        <f t="shared" si="11"/>
+        <v>38.92</v>
+      </c>
       <c r="AN36" s="1"/>
       <c r="AO36" s="1"/>
       <c r="AP36" s="1"/>
@@ -5285,11 +5397,11 @@
       <c r="Q37" s="5"/>
       <c r="R37" s="5"/>
       <c r="S37" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="T37" s="5">
-        <f t="shared" si="12"/>
+      <c r="T37" s="37">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="U37" s="5"/>
@@ -5326,13 +5438,13 @@
         <v>10</v>
       </c>
       <c r="AG37" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AH37" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
+      <c r="AH37" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AI37" s="1">
         <v>12</v>
       </c>
@@ -5340,11 +5452,14 @@
         <v>84</v>
       </c>
       <c r="AK37" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AL37" s="1"/>
-      <c r="AM37" s="1"/>
+      <c r="AM37" s="1">
+        <f t="shared" si="11"/>
+        <v>7.56</v>
+      </c>
       <c r="AN37" s="1"/>
       <c r="AO37" s="1"/>
       <c r="AP37" s="1"/>
@@ -5392,7 +5507,7 @@
         <v>184</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L67" si="16">E38-K38</f>
+        <f t="shared" ref="L38:L67" si="17">E38-K38</f>
         <v>3</v>
       </c>
       <c r="M38" s="1"/>
@@ -5401,27 +5516,27 @@
         <v>600</v>
       </c>
       <c r="P38" s="1">
-        <f t="shared" ref="P38:P68" si="17">E38/5</f>
+        <f t="shared" ref="P38:P68" si="18">E38/5</f>
         <v>37.4</v>
       </c>
       <c r="Q38" s="5"/>
       <c r="R38" s="5"/>
       <c r="S38" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="T38" s="5">
-        <f t="shared" si="12"/>
+      <c r="T38" s="37">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="U38" s="5"/>
       <c r="V38" s="1"/>
       <c r="W38" s="1">
-        <f t="shared" ref="W38:W68" si="18">(F38+O38+T38)/P38</f>
+        <f t="shared" ref="W38:W68" si="19">(F38+O38+T38)/P38</f>
         <v>16.149732620320858</v>
       </c>
       <c r="X38" s="1">
-        <f t="shared" ref="X38:X68" si="19">(F38+O38)/P38</f>
+        <f t="shared" ref="X38:X68" si="20">(F38+O38)/P38</f>
         <v>16.149732620320858</v>
       </c>
       <c r="Y38" s="1">
@@ -5448,13 +5563,13 @@
         <v>10</v>
       </c>
       <c r="AG38" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AH38" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
+      <c r="AH38" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AI38" s="1">
         <v>12</v>
       </c>
@@ -5462,11 +5577,14 @@
         <v>84</v>
       </c>
       <c r="AK38" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AL38" s="1"/>
-      <c r="AM38" s="1"/>
+      <c r="AM38" s="1">
+        <f t="shared" si="11"/>
+        <v>26.179999999999996</v>
+      </c>
       <c r="AN38" s="1"/>
       <c r="AO38" s="1"/>
       <c r="AP38" s="1"/>
@@ -5514,7 +5632,7 @@
         <v>94</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M39" s="1"/>
@@ -5523,7 +5641,7 @@
         <v>0</v>
       </c>
       <c r="P39" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>18.8</v>
       </c>
       <c r="Q39" s="5"/>
@@ -5531,23 +5649,23 @@
         <v>100</v>
       </c>
       <c r="S39" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="T39" s="5">
-        <f t="shared" si="12"/>
+      <c r="T39" s="37">
+        <f t="shared" si="13"/>
         <v>120</v>
       </c>
-      <c r="U39" s="29">
+      <c r="U39" s="28">
         <v>100</v>
       </c>
       <c r="V39" s="19"/>
       <c r="W39" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>22.393617021276594</v>
       </c>
       <c r="X39" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>16.01063829787234</v>
       </c>
       <c r="Y39" s="1">
@@ -5574,11 +5692,11 @@
         <v>10</v>
       </c>
       <c r="AG39" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>12</v>
       </c>
       <c r="AH39" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>84</v>
       </c>
       <c r="AI39" s="1">
@@ -5588,11 +5706,14 @@
         <v>84</v>
       </c>
       <c r="AK39" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="AL39" s="1"/>
-      <c r="AM39" s="1"/>
+      <c r="AM39" s="1">
+        <f t="shared" si="11"/>
+        <v>13.16</v>
+      </c>
       <c r="AN39" s="1"/>
       <c r="AO39" s="1"/>
       <c r="AP39" s="1"/>
@@ -5640,7 +5761,7 @@
         <v>410</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>10</v>
       </c>
       <c r="M40" s="1"/>
@@ -5649,7 +5770,7 @@
         <v>0</v>
       </c>
       <c r="P40" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>84</v>
       </c>
       <c r="Q40" s="5">
@@ -5662,18 +5783,18 @@
         <f>R40*$S$1</f>
         <v>635.78</v>
       </c>
-      <c r="T40" s="5">
-        <f t="shared" si="12"/>
+      <c r="T40" s="37">
+        <f t="shared" si="13"/>
         <v>660</v>
       </c>
       <c r="U40" s="5"/>
       <c r="V40" s="1"/>
       <c r="W40" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>12.738095238095237</v>
       </c>
       <c r="X40" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4.8809523809523814</v>
       </c>
       <c r="Y40" s="1">
@@ -5700,11 +5821,11 @@
         <v>5</v>
       </c>
       <c r="AG40" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>132</v>
       </c>
       <c r="AH40" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>660</v>
       </c>
       <c r="AI40" s="1">
@@ -5714,11 +5835,14 @@
         <v>144</v>
       </c>
       <c r="AK40" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.91666666666666663</v>
       </c>
       <c r="AL40" s="1"/>
-      <c r="AM40" s="1"/>
+      <c r="AM40" s="1">
+        <f t="shared" si="11"/>
+        <v>84</v>
+      </c>
       <c r="AN40" s="1"/>
       <c r="AO40" s="1"/>
       <c r="AP40" s="1"/>
@@ -5766,7 +5890,7 @@
         <v>261</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-6</v>
       </c>
       <c r="M41" s="1"/>
@@ -5775,29 +5899,29 @@
         <v>0</v>
       </c>
       <c r="P41" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>51</v>
       </c>
       <c r="Q41" s="5"/>
       <c r="R41" s="5"/>
       <c r="S41" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="T41" s="5">
-        <f t="shared" si="12"/>
+      <c r="T41" s="37">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="U41" s="5"/>
       <c r="V41" s="1"/>
       <c r="W41" s="1">
-        <f t="shared" si="18"/>
-        <v>20.745098039215687</v>
-      </c>
-      <c r="X41" s="1">
         <f t="shared" si="19"/>
         <v>20.745098039215687</v>
       </c>
+      <c r="X41" s="1">
+        <f t="shared" si="20"/>
+        <v>20.745098039215687</v>
+      </c>
       <c r="Y41" s="1">
         <v>41</v>
       </c>
@@ -5815,20 +5939,20 @@
       </c>
       <c r="AD41" s="1"/>
       <c r="AE41" s="10">
-        <f t="shared" ref="AE41:AE66" si="20">G41*S41</f>
+        <f t="shared" ref="AE41:AE66" si="21">G41*S41</f>
         <v>0</v>
       </c>
       <c r="AF41" s="10">
         <v>16</v>
       </c>
       <c r="AG41" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AH41" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
+      <c r="AH41" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AI41" s="1">
         <v>12</v>
       </c>
@@ -5836,11 +5960,14 @@
         <v>84</v>
       </c>
       <c r="AK41" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AL41" s="1"/>
-      <c r="AM41" s="1"/>
+      <c r="AM41" s="1">
+        <f t="shared" si="11"/>
+        <v>20.400000000000002</v>
+      </c>
       <c r="AN41" s="1"/>
       <c r="AO41" s="1"/>
       <c r="AP41" s="1"/>
@@ -5888,7 +6015,7 @@
         <v>680</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>4</v>
       </c>
       <c r="M42" s="1"/>
@@ -5897,7 +6024,7 @@
         <v>0</v>
       </c>
       <c r="P42" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>136.80000000000001</v>
       </c>
       <c r="Q42" s="5">
@@ -5910,20 +6037,20 @@
         <f>R42*$S$1</f>
         <v>747</v>
       </c>
-      <c r="T42" s="5">
-        <f t="shared" si="12"/>
+      <c r="T42" s="37">
+        <f t="shared" si="13"/>
         <v>720</v>
       </c>
-      <c r="U42" s="29">
+      <c r="U42" s="28">
         <v>900</v>
       </c>
       <c r="V42" s="19"/>
       <c r="W42" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>13.786549707602338</v>
       </c>
       <c r="X42" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8.523391812865496</v>
       </c>
       <c r="Y42" s="1">
@@ -5945,18 +6072,18 @@
         <v>118</v>
       </c>
       <c r="AE42" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>522.9</v>
       </c>
       <c r="AF42" s="10">
         <v>10</v>
       </c>
       <c r="AG42" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>72</v>
       </c>
       <c r="AH42" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>503.99999999999994</v>
       </c>
       <c r="AI42" s="1">
@@ -5966,11 +6093,14 @@
         <v>84</v>
       </c>
       <c r="AK42" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="AL42" s="1"/>
-      <c r="AM42" s="1"/>
+      <c r="AM42" s="1">
+        <f t="shared" si="11"/>
+        <v>95.76</v>
+      </c>
       <c r="AN42" s="1"/>
       <c r="AO42" s="1"/>
       <c r="AP42" s="1"/>
@@ -6018,7 +6148,7 @@
         <v>265</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="M43" s="1"/>
@@ -6027,29 +6157,29 @@
         <v>0</v>
       </c>
       <c r="P43" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>53.2</v>
       </c>
       <c r="Q43" s="5"/>
       <c r="R43" s="5"/>
       <c r="S43" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="T43" s="5">
-        <f t="shared" si="12"/>
+      <c r="T43" s="37">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="U43" s="5"/>
       <c r="V43" s="1"/>
       <c r="W43" s="1">
-        <f t="shared" si="18"/>
-        <v>17.443609022556391</v>
-      </c>
-      <c r="X43" s="1">
         <f t="shared" si="19"/>
         <v>17.443609022556391</v>
       </c>
+      <c r="X43" s="1">
+        <f t="shared" si="20"/>
+        <v>17.443609022556391</v>
+      </c>
       <c r="Y43" s="1">
         <v>53.8</v>
       </c>
@@ -6067,20 +6197,20 @@
       </c>
       <c r="AD43" s="1"/>
       <c r="AE43" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AF43" s="10">
         <v>16</v>
       </c>
       <c r="AG43" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AH43" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
+      <c r="AH43" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AI43" s="1">
         <v>12</v>
       </c>
@@ -6088,11 +6218,14 @@
         <v>84</v>
       </c>
       <c r="AK43" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AL43" s="1"/>
-      <c r="AM43" s="1"/>
+      <c r="AM43" s="1">
+        <f t="shared" si="11"/>
+        <v>21.28</v>
+      </c>
       <c r="AN43" s="1"/>
       <c r="AO43" s="1"/>
       <c r="AP43" s="1"/>
@@ -6120,11 +6253,11 @@
       <c r="D44" s="1">
         <v>724</v>
       </c>
-      <c r="E44" s="22">
+      <c r="E44" s="21">
         <f>828+E7</f>
         <v>897</v>
       </c>
-      <c r="F44" s="22">
+      <c r="F44" s="21">
         <f>658+F7</f>
         <v>682</v>
       </c>
@@ -6142,7 +6275,7 @@
         <v>802</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>95</v>
       </c>
       <c r="M44" s="1"/>
@@ -6151,7 +6284,7 @@
         <v>720</v>
       </c>
       <c r="P44" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>179.4</v>
       </c>
       <c r="Q44" s="5">
@@ -6164,18 +6297,18 @@
         <f>R44*$S$1</f>
         <v>920.96799999999985</v>
       </c>
-      <c r="T44" s="5">
-        <f t="shared" si="12"/>
+      <c r="T44" s="37">
+        <f t="shared" si="13"/>
         <v>960</v>
       </c>
       <c r="U44" s="5"/>
       <c r="V44" s="1"/>
       <c r="W44" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>13.166109253065775</v>
       </c>
       <c r="X44" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7.8149386845039013</v>
       </c>
       <c r="Y44" s="1">
@@ -6197,18 +6330,18 @@
         <v>66</v>
       </c>
       <c r="AE44" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>644.67759999999987</v>
       </c>
       <c r="AF44" s="10">
         <v>10</v>
       </c>
       <c r="AG44" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>96</v>
       </c>
       <c r="AH44" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>672</v>
       </c>
       <c r="AI44" s="1">
@@ -6218,11 +6351,14 @@
         <v>84</v>
       </c>
       <c r="AK44" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1.1428571428571428</v>
       </c>
       <c r="AL44" s="1"/>
-      <c r="AM44" s="1"/>
+      <c r="AM44" s="1">
+        <f t="shared" si="11"/>
+        <v>125.58</v>
+      </c>
       <c r="AN44" s="1"/>
       <c r="AO44" s="1"/>
       <c r="AP44" s="1"/>
@@ -6270,7 +6406,7 @@
         <v>156</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="M45" s="1"/>
@@ -6279,7 +6415,7 @@
         <v>360</v>
       </c>
       <c r="P45" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>31.4</v>
       </c>
       <c r="Q45" s="5"/>
@@ -6287,23 +6423,23 @@
         <v>200</v>
       </c>
       <c r="S45" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>200</v>
       </c>
-      <c r="T45" s="5">
-        <f t="shared" si="12"/>
+      <c r="T45" s="37">
+        <f t="shared" si="13"/>
         <v>240</v>
       </c>
-      <c r="U45" s="29">
+      <c r="U45" s="28">
         <v>200</v>
       </c>
       <c r="V45" s="19"/>
       <c r="W45" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>30.063694267515924</v>
       </c>
       <c r="X45" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>22.420382165605098</v>
       </c>
       <c r="Y45" s="1">
@@ -6325,18 +6461,18 @@
         <v>124</v>
       </c>
       <c r="AE45" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>140</v>
       </c>
       <c r="AF45" s="10">
         <v>10</v>
       </c>
       <c r="AG45" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>24</v>
       </c>
       <c r="AH45" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>168</v>
       </c>
       <c r="AI45" s="1">
@@ -6346,11 +6482,14 @@
         <v>84</v>
       </c>
       <c r="AK45" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="AL45" s="1"/>
-      <c r="AM45" s="1"/>
+      <c r="AM45" s="1">
+        <f t="shared" si="11"/>
+        <v>21.979999999999997</v>
+      </c>
       <c r="AN45" s="1"/>
       <c r="AO45" s="1"/>
       <c r="AP45" s="1"/>
@@ -6398,7 +6537,7 @@
         <v>197</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-9</v>
       </c>
       <c r="M46" s="1"/>
@@ -6407,7 +6546,7 @@
         <v>720</v>
       </c>
       <c r="P46" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>37.6</v>
       </c>
       <c r="Q46" s="5"/>
@@ -6415,23 +6554,23 @@
         <v>200</v>
       </c>
       <c r="S46" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>200</v>
       </c>
-      <c r="T46" s="5">
-        <f t="shared" si="12"/>
+      <c r="T46" s="37">
+        <f t="shared" si="13"/>
         <v>180</v>
       </c>
-      <c r="U46" s="29">
+      <c r="U46" s="28">
         <v>200</v>
       </c>
       <c r="V46" s="19"/>
       <c r="W46" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>24.01595744680851</v>
       </c>
       <c r="X46" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>19.228723404255319</v>
       </c>
       <c r="Y46" s="1">
@@ -6451,18 +6590,18 @@
       </c>
       <c r="AD46" s="1"/>
       <c r="AE46" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>200</v>
       </c>
       <c r="AF46" s="10">
         <v>5</v>
       </c>
       <c r="AG46" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>36</v>
       </c>
       <c r="AH46" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>180</v>
       </c>
       <c r="AI46" s="1">
@@ -6472,11 +6611,14 @@
         <v>84</v>
       </c>
       <c r="AK46" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="AL46" s="1"/>
-      <c r="AM46" s="1"/>
+      <c r="AM46" s="1">
+        <f t="shared" si="11"/>
+        <v>37.6</v>
+      </c>
       <c r="AN46" s="1"/>
       <c r="AO46" s="1"/>
       <c r="AP46" s="1"/>
@@ -6524,7 +6666,7 @@
         <v>167</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M47" s="1"/>
@@ -6533,7 +6675,7 @@
         <v>288</v>
       </c>
       <c r="P47" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>33.4</v>
       </c>
       <c r="Q47" s="5">
@@ -6543,23 +6685,23 @@
         <v>300</v>
       </c>
       <c r="S47" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>300</v>
       </c>
-      <c r="T47" s="5">
-        <f t="shared" si="12"/>
+      <c r="T47" s="37">
+        <f t="shared" si="13"/>
         <v>288</v>
       </c>
-      <c r="U47" s="29">
+      <c r="U47" s="28">
         <v>300</v>
       </c>
       <c r="V47" s="19"/>
       <c r="W47" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>17.365269461077844</v>
       </c>
       <c r="X47" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>8.7425149700598812</v>
       </c>
       <c r="Y47" s="1">
@@ -6581,18 +6723,18 @@
         <v>66</v>
       </c>
       <c r="AE47" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>270</v>
       </c>
       <c r="AF47" s="10">
         <v>8</v>
       </c>
       <c r="AG47" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>36</v>
       </c>
       <c r="AH47" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>259.2</v>
       </c>
       <c r="AI47" s="1">
@@ -6602,11 +6744,14 @@
         <v>84</v>
       </c>
       <c r="AK47" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="AL47" s="1"/>
-      <c r="AM47" s="1"/>
+      <c r="AM47" s="1">
+        <f t="shared" si="11"/>
+        <v>30.06</v>
+      </c>
       <c r="AN47" s="1"/>
       <c r="AO47" s="1"/>
       <c r="AP47" s="1"/>
@@ -6654,7 +6799,7 @@
         <v>69</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-1</v>
       </c>
       <c r="M48" s="1"/>
@@ -6663,7 +6808,7 @@
         <v>288</v>
       </c>
       <c r="P48" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>13.6</v>
       </c>
       <c r="Q48" s="5"/>
@@ -6671,23 +6816,23 @@
         <v>192</v>
       </c>
       <c r="S48" s="5">
-        <f t="shared" si="11"/>
-        <v>192</v>
-      </c>
-      <c r="T48" s="5">
         <f t="shared" si="12"/>
         <v>192</v>
       </c>
-      <c r="U48" s="29">
+      <c r="T48" s="37">
+        <f t="shared" si="13"/>
+        <v>192</v>
+      </c>
+      <c r="U48" s="28">
         <v>192</v>
       </c>
       <c r="V48" s="19"/>
       <c r="W48" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>35.735294117647058</v>
       </c>
       <c r="X48" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>21.617647058823529</v>
       </c>
       <c r="Y48" s="1">
@@ -6707,18 +6852,18 @@
       </c>
       <c r="AD48" s="1"/>
       <c r="AE48" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>172.8</v>
       </c>
       <c r="AF48" s="10">
         <v>8</v>
       </c>
       <c r="AG48" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>24</v>
       </c>
       <c r="AH48" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>172.8</v>
       </c>
       <c r="AI48" s="1">
@@ -6728,11 +6873,14 @@
         <v>84</v>
       </c>
       <c r="AK48" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="AL48" s="1"/>
-      <c r="AM48" s="1"/>
+      <c r="AM48" s="1">
+        <f t="shared" si="11"/>
+        <v>12.24</v>
+      </c>
       <c r="AN48" s="1"/>
       <c r="AO48" s="1"/>
       <c r="AP48" s="1"/>
@@ -6780,7 +6928,7 @@
         <v>520</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-80</v>
       </c>
       <c r="M49" s="1"/>
@@ -6789,7 +6937,7 @@
         <v>1020</v>
       </c>
       <c r="P49" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>88</v>
       </c>
       <c r="Q49" s="5"/>
@@ -6797,23 +6945,23 @@
         <v>200</v>
       </c>
       <c r="S49" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>200</v>
       </c>
-      <c r="T49" s="5">
-        <f t="shared" si="12"/>
+      <c r="T49" s="37">
+        <f t="shared" si="13"/>
         <v>180</v>
       </c>
-      <c r="U49" s="29">
+      <c r="U49" s="28">
         <v>200</v>
       </c>
       <c r="V49" s="19"/>
       <c r="W49" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>23.238636363636363</v>
       </c>
       <c r="X49" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>21.193181818181817</v>
       </c>
       <c r="Y49" s="1">
@@ -6833,18 +6981,18 @@
       </c>
       <c r="AD49" s="1"/>
       <c r="AE49" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>200</v>
       </c>
       <c r="AF49" s="10">
         <v>5</v>
       </c>
       <c r="AG49" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>36</v>
       </c>
       <c r="AH49" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>180</v>
       </c>
       <c r="AI49" s="1">
@@ -6854,11 +7002,14 @@
         <v>144</v>
       </c>
       <c r="AK49" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.25</v>
       </c>
       <c r="AL49" s="1"/>
-      <c r="AM49" s="1"/>
+      <c r="AM49" s="1">
+        <f t="shared" si="11"/>
+        <v>88</v>
+      </c>
       <c r="AN49" s="1"/>
       <c r="AO49" s="1"/>
       <c r="AP49" s="1"/>
@@ -6904,7 +7055,7 @@
         <v>136</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M50" s="1"/>
@@ -6913,7 +7064,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>27.2</v>
       </c>
       <c r="Q50" s="5">
@@ -6923,21 +7074,21 @@
         <v>92.800000000000011</v>
       </c>
       <c r="S50" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>92.800000000000011</v>
       </c>
-      <c r="T50" s="5">
-        <f t="shared" si="12"/>
+      <c r="T50" s="37">
+        <f t="shared" si="13"/>
         <v>120</v>
       </c>
       <c r="U50" s="5"/>
       <c r="V50" s="1"/>
       <c r="W50" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>15</v>
       </c>
       <c r="X50" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>10.588235294117647</v>
       </c>
       <c r="Y50" s="1">
@@ -6957,18 +7108,18 @@
       </c>
       <c r="AD50" s="1"/>
       <c r="AE50" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>92.800000000000011</v>
       </c>
       <c r="AF50" s="10">
         <v>5</v>
       </c>
       <c r="AG50" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>24</v>
       </c>
       <c r="AH50" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>120</v>
       </c>
       <c r="AI50" s="1">
@@ -6978,11 +7129,14 @@
         <v>84</v>
       </c>
       <c r="AK50" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="AL50" s="1"/>
-      <c r="AM50" s="1"/>
+      <c r="AM50" s="1">
+        <f t="shared" si="11"/>
+        <v>27.2</v>
+      </c>
       <c r="AN50" s="1"/>
       <c r="AO50" s="1"/>
       <c r="AP50" s="1"/>
@@ -7028,7 +7182,7 @@
         <v>26.1</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="M51" s="1"/>
@@ -7037,7 +7191,7 @@
         <v>0</v>
       </c>
       <c r="P51" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>5.18</v>
       </c>
       <c r="Q51" s="5">
@@ -7047,21 +7201,21 @@
         <v>48.14</v>
       </c>
       <c r="S51" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>48.14</v>
       </c>
-      <c r="T51" s="5">
-        <f t="shared" si="12"/>
+      <c r="T51" s="37">
+        <f t="shared" si="13"/>
         <v>51.800000000000004</v>
       </c>
       <c r="U51" s="5"/>
       <c r="V51" s="1"/>
       <c r="W51" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>13.706563706563708</v>
       </c>
       <c r="X51" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.7065637065637067</v>
       </c>
       <c r="Y51" s="1">
@@ -7081,18 +7235,18 @@
       </c>
       <c r="AD51" s="1"/>
       <c r="AE51" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>48.14</v>
       </c>
       <c r="AF51" s="10">
         <v>3.7</v>
       </c>
       <c r="AG51" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>14</v>
       </c>
       <c r="AH51" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>51.800000000000004</v>
       </c>
       <c r="AI51" s="1">
@@ -7102,11 +7256,14 @@
         <v>126</v>
       </c>
       <c r="AK51" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.1111111111111111</v>
       </c>
       <c r="AL51" s="1"/>
-      <c r="AM51" s="1"/>
+      <c r="AM51" s="1">
+        <f t="shared" si="11"/>
+        <v>5.18</v>
+      </c>
       <c r="AN51" s="1"/>
       <c r="AO51" s="1"/>
       <c r="AP51" s="1"/>
@@ -7152,7 +7309,7 @@
         <v>151</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M52" s="1"/>
@@ -7161,7 +7318,7 @@
         <v>168</v>
       </c>
       <c r="P52" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>30.2</v>
       </c>
       <c r="Q52" s="5">
@@ -7171,23 +7328,23 @@
         <v>500</v>
       </c>
       <c r="S52" s="5">
-        <f t="shared" ref="S52:S53" si="21">R52*$S$1</f>
+        <f t="shared" ref="S52:S53" si="22">R52*$S$1</f>
         <v>415</v>
       </c>
-      <c r="T52" s="5">
-        <f t="shared" si="12"/>
+      <c r="T52" s="37">
+        <f t="shared" si="13"/>
         <v>420</v>
       </c>
-      <c r="U52" s="29">
+      <c r="U52" s="28">
         <v>500</v>
       </c>
       <c r="V52" s="19"/>
       <c r="W52" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>21.456953642384107</v>
       </c>
       <c r="X52" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7.5496688741721858</v>
       </c>
       <c r="Y52" s="1">
@@ -7207,18 +7364,18 @@
       </c>
       <c r="AD52" s="1"/>
       <c r="AE52" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>95.45</v>
       </c>
       <c r="AF52" s="10">
         <v>6</v>
       </c>
       <c r="AG52" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>70</v>
       </c>
       <c r="AH52" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>96.600000000000009</v>
       </c>
       <c r="AI52" s="1">
@@ -7228,11 +7385,14 @@
         <v>140</v>
       </c>
       <c r="AK52" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.5</v>
       </c>
       <c r="AL52" s="1"/>
-      <c r="AM52" s="1"/>
+      <c r="AM52" s="1">
+        <f t="shared" si="11"/>
+        <v>6.9459999999999997</v>
+      </c>
       <c r="AN52" s="1"/>
       <c r="AO52" s="1"/>
       <c r="AP52" s="1"/>
@@ -7280,7 +7440,7 @@
         <v>360</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2</v>
       </c>
       <c r="M53" s="1"/>
@@ -7289,7 +7449,7 @@
         <v>336</v>
       </c>
       <c r="P53" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>72.400000000000006</v>
       </c>
       <c r="Q53" s="5">
@@ -7299,23 +7459,23 @@
         <v>750</v>
       </c>
       <c r="S53" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>622.5</v>
       </c>
-      <c r="T53" s="5">
-        <f t="shared" si="12"/>
+      <c r="T53" s="37">
+        <f t="shared" si="13"/>
         <v>672</v>
       </c>
-      <c r="U53" s="29">
+      <c r="U53" s="28">
         <v>750</v>
       </c>
       <c r="V53" s="19"/>
       <c r="W53" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>15.138121546961324</v>
       </c>
       <c r="X53" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>5.8563535911602207</v>
       </c>
       <c r="Y53" s="1">
@@ -7337,18 +7497,18 @@
         <v>66</v>
       </c>
       <c r="AE53" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>155.625</v>
       </c>
       <c r="AF53" s="10">
         <v>12</v>
       </c>
       <c r="AG53" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>56</v>
       </c>
       <c r="AH53" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>168</v>
       </c>
       <c r="AI53" s="1">
@@ -7358,11 +7518,14 @@
         <v>70</v>
       </c>
       <c r="AK53" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.8</v>
       </c>
       <c r="AL53" s="1"/>
-      <c r="AM53" s="1"/>
+      <c r="AM53" s="1">
+        <f t="shared" si="11"/>
+        <v>18.100000000000001</v>
+      </c>
       <c r="AN53" s="1"/>
       <c r="AO53" s="1"/>
       <c r="AP53" s="1"/>
@@ -7410,7 +7573,7 @@
         <v>119</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-4</v>
       </c>
       <c r="M54" s="1"/>
@@ -7419,7 +7582,7 @@
         <v>336</v>
       </c>
       <c r="P54" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>23</v>
       </c>
       <c r="Q54" s="5"/>
@@ -7427,23 +7590,23 @@
         <v>200</v>
       </c>
       <c r="S54" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>200</v>
       </c>
-      <c r="T54" s="5">
-        <f t="shared" si="12"/>
+      <c r="T54" s="37">
+        <f t="shared" si="13"/>
         <v>168</v>
       </c>
-      <c r="U54" s="29">
+      <c r="U54" s="28">
         <v>200</v>
       </c>
       <c r="V54" s="19"/>
       <c r="W54" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>30.826086956521738</v>
       </c>
       <c r="X54" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>23.521739130434781</v>
       </c>
       <c r="Y54" s="1">
@@ -7463,18 +7626,18 @@
       </c>
       <c r="AD54" s="1"/>
       <c r="AE54" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>50</v>
       </c>
       <c r="AF54" s="10">
         <v>12</v>
       </c>
       <c r="AG54" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>14</v>
       </c>
       <c r="AH54" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>42</v>
       </c>
       <c r="AI54" s="1">
@@ -7484,11 +7647,14 @@
         <v>70</v>
       </c>
       <c r="AK54" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.2</v>
       </c>
       <c r="AL54" s="1"/>
-      <c r="AM54" s="1"/>
+      <c r="AM54" s="1">
+        <f t="shared" si="11"/>
+        <v>5.75</v>
+      </c>
       <c r="AN54" s="1"/>
       <c r="AO54" s="1"/>
       <c r="AP54" s="1"/>
@@ -7530,7 +7696,7 @@
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M55" s="1"/>
@@ -7539,29 +7705,29 @@
         <v>0</v>
       </c>
       <c r="P55" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Q55" s="5"/>
       <c r="R55" s="5"/>
       <c r="S55" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="T55" s="5">
-        <f t="shared" si="12"/>
+      <c r="T55" s="37">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="U55" s="5"/>
       <c r="V55" s="1"/>
       <c r="W55" s="1" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X55" s="1" t="e">
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="X55" s="1" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Y55" s="1">
         <v>0</v>
       </c>
@@ -7579,20 +7745,20 @@
       </c>
       <c r="AD55" s="1"/>
       <c r="AE55" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AF55" s="10">
         <v>6</v>
       </c>
       <c r="AG55" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AH55" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
+      <c r="AH55" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AI55" s="1">
         <v>14</v>
       </c>
@@ -7600,11 +7766,14 @@
         <v>140</v>
       </c>
       <c r="AK55" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AL55" s="1"/>
-      <c r="AM55" s="1"/>
+      <c r="AM55" s="1">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AN55" s="1"/>
       <c r="AO55" s="1"/>
       <c r="AP55" s="1"/>
@@ -7650,7 +7819,7 @@
         <v>10</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="M56" s="1"/>
@@ -7659,29 +7828,29 @@
         <v>0</v>
       </c>
       <c r="P56" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="Q56" s="5"/>
       <c r="R56" s="5"/>
       <c r="S56" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="T56" s="5">
-        <f t="shared" si="12"/>
+      <c r="T56" s="37">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="U56" s="5"/>
       <c r="V56" s="1"/>
       <c r="W56" s="1">
-        <f t="shared" si="18"/>
-        <v>19.545454545454543</v>
-      </c>
-      <c r="X56" s="1">
         <f t="shared" si="19"/>
         <v>19.545454545454543</v>
       </c>
+      <c r="X56" s="1">
+        <f t="shared" si="20"/>
+        <v>19.545454545454543</v>
+      </c>
       <c r="Y56" s="1">
         <v>5.2</v>
       </c>
@@ -7701,20 +7870,20 @@
         <v>79</v>
       </c>
       <c r="AE56" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AF56" s="10">
         <v>6</v>
       </c>
       <c r="AG56" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AH56" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
+      <c r="AH56" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AI56" s="1">
         <v>14</v>
       </c>
@@ -7722,11 +7891,14 @@
         <v>140</v>
       </c>
       <c r="AK56" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AL56" s="1"/>
-      <c r="AM56" s="1"/>
+      <c r="AM56" s="1">
+        <f t="shared" si="11"/>
+        <v>0.39600000000000002</v>
+      </c>
       <c r="AN56" s="1"/>
       <c r="AO56" s="1"/>
       <c r="AP56" s="1"/>
@@ -7772,7 +7944,7 @@
         <v>1</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M57" s="1"/>
@@ -7781,29 +7953,29 @@
         <v>0</v>
       </c>
       <c r="P57" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.2</v>
       </c>
       <c r="Q57" s="5"/>
       <c r="R57" s="5"/>
       <c r="S57" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="T57" s="5">
-        <f t="shared" si="12"/>
+      <c r="T57" s="37">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="U57" s="5"/>
       <c r="V57" s="1"/>
       <c r="W57" s="1">
-        <f t="shared" si="18"/>
-        <v>380</v>
-      </c>
-      <c r="X57" s="1">
         <f t="shared" si="19"/>
         <v>380</v>
       </c>
+      <c r="X57" s="1">
+        <f t="shared" si="20"/>
+        <v>380</v>
+      </c>
       <c r="Y57" s="1">
         <v>0.8</v>
       </c>
@@ -7823,20 +7995,20 @@
         <v>69</v>
       </c>
       <c r="AE57" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AF57" s="10">
         <v>6</v>
       </c>
       <c r="AG57" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AH57" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
+      <c r="AH57" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AI57" s="1">
         <v>14</v>
       </c>
@@ -7844,11 +8016,14 @@
         <v>140</v>
       </c>
       <c r="AK57" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AL57" s="1"/>
-      <c r="AM57" s="1"/>
+      <c r="AM57" s="1">
+        <f t="shared" si="11"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
       <c r="AN57" s="1"/>
       <c r="AO57" s="1"/>
       <c r="AP57" s="1"/>
@@ -7896,7 +8071,7 @@
         <v>365</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-7</v>
       </c>
       <c r="M58" s="1"/>
@@ -7905,7 +8080,7 @@
         <v>336</v>
       </c>
       <c r="P58" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>71.599999999999994</v>
       </c>
       <c r="Q58" s="5">
@@ -7915,23 +8090,23 @@
         <v>580</v>
       </c>
       <c r="S58" s="5">
-        <f t="shared" ref="S58:S59" si="22">R58*$S$1</f>
+        <f t="shared" ref="S58:S59" si="23">R58*$S$1</f>
         <v>481.4</v>
       </c>
-      <c r="T58" s="5">
-        <f t="shared" si="12"/>
+      <c r="T58" s="37">
+        <f t="shared" si="13"/>
         <v>504</v>
       </c>
-      <c r="U58" s="29">
+      <c r="U58" s="28">
         <v>580</v>
       </c>
       <c r="V58" s="19"/>
       <c r="W58" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>14.217877094972069</v>
       </c>
       <c r="X58" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>7.1787709497206711</v>
       </c>
       <c r="Y58" s="1">
@@ -7953,18 +8128,18 @@
         <v>66</v>
       </c>
       <c r="AE58" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>144.41999999999999</v>
       </c>
       <c r="AF58" s="10">
         <v>12</v>
       </c>
       <c r="AG58" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>42</v>
       </c>
       <c r="AH58" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>151.19999999999999</v>
       </c>
       <c r="AI58" s="1">
@@ -7974,11 +8149,14 @@
         <v>70</v>
       </c>
       <c r="AK58" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.6</v>
       </c>
       <c r="AL58" s="1"/>
-      <c r="AM58" s="1"/>
+      <c r="AM58" s="1">
+        <f t="shared" si="11"/>
+        <v>21.479999999999997</v>
+      </c>
       <c r="AN58" s="1"/>
       <c r="AO58" s="1"/>
       <c r="AP58" s="1"/>
@@ -8026,7 +8204,7 @@
         <v>403</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>6</v>
       </c>
       <c r="M59" s="1"/>
@@ -8035,7 +8213,7 @@
         <v>168</v>
       </c>
       <c r="P59" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>81.8</v>
       </c>
       <c r="Q59" s="5">
@@ -8045,23 +8223,23 @@
         <v>800</v>
       </c>
       <c r="S59" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>664</v>
       </c>
-      <c r="T59" s="5">
-        <f t="shared" si="12"/>
+      <c r="T59" s="37">
+        <f t="shared" si="13"/>
         <v>672</v>
       </c>
-      <c r="U59" s="29">
+      <c r="U59" s="28">
         <v>800</v>
       </c>
       <c r="V59" s="19"/>
       <c r="W59" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>15.097799511002446</v>
       </c>
       <c r="X59" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>6.8826405867970664</v>
       </c>
       <c r="Y59" s="1">
@@ -8083,18 +8261,18 @@
         <v>66</v>
       </c>
       <c r="AE59" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>199.2</v>
       </c>
       <c r="AF59" s="10">
         <v>12</v>
       </c>
       <c r="AG59" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>56</v>
       </c>
       <c r="AH59" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>201.6</v>
       </c>
       <c r="AI59" s="1">
@@ -8104,11 +8282,14 @@
         <v>70</v>
       </c>
       <c r="AK59" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.8</v>
       </c>
       <c r="AL59" s="1"/>
-      <c r="AM59" s="1"/>
+      <c r="AM59" s="1">
+        <f t="shared" si="11"/>
+        <v>24.54</v>
+      </c>
       <c r="AN59" s="1"/>
       <c r="AO59" s="1"/>
       <c r="AP59" s="1"/>
@@ -8156,7 +8337,7 @@
         <v>100</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-21</v>
       </c>
       <c r="M60" s="1"/>
@@ -8165,7 +8346,7 @@
         <v>0</v>
       </c>
       <c r="P60" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>15.8</v>
       </c>
       <c r="Q60" s="5">
@@ -8175,23 +8356,23 @@
         <v>300</v>
       </c>
       <c r="S60" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>300</v>
       </c>
-      <c r="T60" s="5">
-        <f t="shared" si="12"/>
+      <c r="T60" s="37">
+        <f t="shared" si="13"/>
         <v>392</v>
       </c>
-      <c r="U60" s="29">
+      <c r="U60" s="28">
         <v>300</v>
       </c>
       <c r="V60" s="19"/>
       <c r="W60" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>24.683544303797468</v>
       </c>
       <c r="X60" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>-0.12658227848101264</v>
       </c>
       <c r="Y60" s="1">
@@ -8211,18 +8392,18 @@
       </c>
       <c r="AD60" s="1"/>
       <c r="AE60" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>90</v>
       </c>
       <c r="AF60" s="10">
         <v>14</v>
       </c>
       <c r="AG60" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>28</v>
       </c>
       <c r="AH60" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>117.6</v>
       </c>
       <c r="AI60" s="1">
@@ -8232,11 +8413,14 @@
         <v>70</v>
       </c>
       <c r="AK60" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.4</v>
       </c>
       <c r="AL60" s="1"/>
-      <c r="AM60" s="1"/>
+      <c r="AM60" s="1">
+        <f t="shared" si="11"/>
+        <v>4.74</v>
+      </c>
       <c r="AN60" s="1"/>
       <c r="AO60" s="1"/>
       <c r="AP60" s="1"/>
@@ -8284,7 +8468,7 @@
         <v>653</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-7</v>
       </c>
       <c r="M61" s="1"/>
@@ -8293,7 +8477,7 @@
         <v>336</v>
       </c>
       <c r="P61" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>129.19999999999999</v>
       </c>
       <c r="Q61" s="5">
@@ -8303,23 +8487,23 @@
         <v>700</v>
       </c>
       <c r="S61" s="5">
-        <f t="shared" ref="S61:S62" si="23">R61*$S$1</f>
+        <f t="shared" ref="S61:S62" si="24">R61*$S$1</f>
         <v>581</v>
       </c>
-      <c r="T61" s="5">
-        <f t="shared" si="12"/>
+      <c r="T61" s="37">
+        <f t="shared" si="13"/>
         <v>504</v>
       </c>
-      <c r="U61" s="29">
+      <c r="U61" s="28">
         <v>700</v>
       </c>
       <c r="V61" s="19"/>
       <c r="W61" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>13.560371517027866</v>
       </c>
       <c r="X61" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>9.6594427244582057</v>
       </c>
       <c r="Y61" s="1">
@@ -8341,18 +8525,18 @@
         <v>66</v>
       </c>
       <c r="AE61" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>145.25</v>
       </c>
       <c r="AF61" s="10">
         <v>12</v>
       </c>
       <c r="AG61" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>42</v>
       </c>
       <c r="AH61" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>126</v>
       </c>
       <c r="AI61" s="1">
@@ -8362,11 +8546,14 @@
         <v>70</v>
       </c>
       <c r="AK61" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.6</v>
       </c>
       <c r="AL61" s="1"/>
-      <c r="AM61" s="1"/>
+      <c r="AM61" s="1">
+        <f t="shared" si="11"/>
+        <v>32.299999999999997</v>
+      </c>
       <c r="AN61" s="1"/>
       <c r="AO61" s="1"/>
       <c r="AP61" s="1"/>
@@ -8394,11 +8581,11 @@
       <c r="D62" s="1">
         <v>360</v>
       </c>
-      <c r="E62" s="22">
+      <c r="E62" s="21">
         <f>656+E8</f>
         <v>682</v>
       </c>
-      <c r="F62" s="22">
+      <c r="F62" s="21">
         <f>29+F8</f>
         <v>61</v>
       </c>
@@ -8414,7 +8601,7 @@
         <v>676</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>6</v>
       </c>
       <c r="M62" s="1"/>
@@ -8423,7 +8610,7 @@
         <v>1512</v>
       </c>
       <c r="P62" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>136.4</v>
       </c>
       <c r="Q62" s="5">
@@ -8433,23 +8620,23 @@
         <v>700</v>
       </c>
       <c r="S62" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>581</v>
       </c>
-      <c r="T62" s="5">
-        <f t="shared" si="12"/>
+      <c r="T62" s="37">
+        <f t="shared" si="13"/>
         <v>504</v>
       </c>
-      <c r="U62" s="29">
+      <c r="U62" s="28">
         <v>700</v>
       </c>
       <c r="V62" s="19"/>
       <c r="W62" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>15.227272727272727</v>
       </c>
       <c r="X62" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>11.532258064516128</v>
       </c>
       <c r="Y62" s="1">
@@ -8471,18 +8658,18 @@
         <v>66</v>
       </c>
       <c r="AE62" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>145.25</v>
       </c>
       <c r="AF62" s="10">
         <v>12</v>
       </c>
       <c r="AG62" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>42</v>
       </c>
       <c r="AH62" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>126</v>
       </c>
       <c r="AI62" s="1">
@@ -8492,11 +8679,14 @@
         <v>70</v>
       </c>
       <c r="AK62" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.6</v>
       </c>
       <c r="AL62" s="1"/>
-      <c r="AM62" s="1"/>
+      <c r="AM62" s="1">
+        <f t="shared" si="11"/>
+        <v>34.1</v>
+      </c>
       <c r="AN62" s="1"/>
       <c r="AO62" s="1"/>
       <c r="AP62" s="1"/>
@@ -8542,7 +8732,7 @@
         <v>131</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>-5</v>
       </c>
       <c r="M63" s="1"/>
@@ -8551,7 +8741,7 @@
         <v>0</v>
       </c>
       <c r="P63" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>25.2</v>
       </c>
       <c r="Q63" s="5">
@@ -8561,21 +8751,21 @@
         <v>219.39999999999998</v>
       </c>
       <c r="S63" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>219.39999999999998</v>
       </c>
-      <c r="T63" s="5">
-        <f t="shared" si="12"/>
+      <c r="T63" s="37">
+        <f t="shared" si="13"/>
         <v>252</v>
       </c>
       <c r="U63" s="5"/>
       <c r="V63" s="1"/>
       <c r="W63" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>13.293650793650794</v>
       </c>
       <c r="X63" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.2936507936507939</v>
       </c>
       <c r="Y63" s="1">
@@ -8595,18 +8785,18 @@
       </c>
       <c r="AD63" s="1"/>
       <c r="AE63" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>43.879999999999995</v>
       </c>
       <c r="AF63" s="10">
         <v>6</v>
       </c>
       <c r="AG63" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>42</v>
       </c>
       <c r="AH63" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>50.400000000000006</v>
       </c>
       <c r="AI63" s="1">
@@ -8616,11 +8806,14 @@
         <v>140</v>
       </c>
       <c r="AK63" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.3</v>
       </c>
       <c r="AL63" s="1"/>
-      <c r="AM63" s="1"/>
+      <c r="AM63" s="1">
+        <f t="shared" si="11"/>
+        <v>5.04</v>
+      </c>
       <c r="AN63" s="1"/>
       <c r="AO63" s="1"/>
       <c r="AP63" s="1"/>
@@ -8668,7 +8861,7 @@
         <v>233</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M64" s="1"/>
@@ -8677,7 +8870,7 @@
         <v>672</v>
       </c>
       <c r="P64" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>46.6</v>
       </c>
       <c r="Q64" s="5"/>
@@ -8685,23 +8878,23 @@
         <v>200</v>
       </c>
       <c r="S64" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>200</v>
       </c>
-      <c r="T64" s="5">
-        <f t="shared" si="12"/>
+      <c r="T64" s="37">
+        <f t="shared" si="13"/>
         <v>168</v>
       </c>
-      <c r="U64" s="29">
+      <c r="U64" s="28">
         <v>200</v>
       </c>
       <c r="V64" s="19"/>
       <c r="W64" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>18.047210300429185</v>
       </c>
       <c r="X64" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>14.442060085836909</v>
       </c>
       <c r="Y64" s="1">
@@ -8721,18 +8914,18 @@
       </c>
       <c r="AD64" s="1"/>
       <c r="AE64" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>46</v>
       </c>
       <c r="AF64" s="10">
         <v>6</v>
       </c>
       <c r="AG64" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>28</v>
       </c>
       <c r="AH64" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>38.64</v>
       </c>
       <c r="AI64" s="1">
@@ -8742,11 +8935,14 @@
         <v>140</v>
       </c>
       <c r="AK64" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0.2</v>
       </c>
       <c r="AL64" s="1"/>
-      <c r="AM64" s="1"/>
+      <c r="AM64" s="1">
+        <f t="shared" si="11"/>
+        <v>10.718</v>
+      </c>
       <c r="AN64" s="1"/>
       <c r="AO64" s="1"/>
       <c r="AP64" s="1"/>
@@ -8794,7 +8990,7 @@
         <v>48</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0.60000000000000142</v>
       </c>
       <c r="M65" s="1"/>
@@ -8803,29 +8999,29 @@
         <v>151.19999999999999</v>
       </c>
       <c r="P65" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>9.7200000000000006</v>
       </c>
       <c r="Q65" s="5"/>
       <c r="R65" s="5"/>
       <c r="S65" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="T65" s="5">
-        <f t="shared" si="12"/>
+      <c r="T65" s="37">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="U65" s="5"/>
       <c r="V65" s="1"/>
       <c r="W65" s="1">
-        <f t="shared" si="18"/>
-        <v>18.888888888888886</v>
-      </c>
-      <c r="X65" s="1">
         <f t="shared" si="19"/>
         <v>18.888888888888886</v>
       </c>
+      <c r="X65" s="1">
+        <f t="shared" si="20"/>
+        <v>18.888888888888886</v>
+      </c>
       <c r="Y65" s="1">
         <v>6.48</v>
       </c>
@@ -8843,20 +9039,20 @@
       </c>
       <c r="AD65" s="1"/>
       <c r="AE65" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AF65" s="10">
         <v>2.7</v>
       </c>
       <c r="AG65" s="1">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AH65" s="1">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
+      <c r="AH65" s="1">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="AI65" s="1">
         <v>14</v>
       </c>
@@ -8864,11 +9060,14 @@
         <v>126</v>
       </c>
       <c r="AK65" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AL65" s="1"/>
-      <c r="AM65" s="1"/>
+      <c r="AM65" s="1">
+        <f t="shared" si="11"/>
+        <v>9.7200000000000006</v>
+      </c>
       <c r="AN65" s="1"/>
       <c r="AO65" s="1"/>
       <c r="AP65" s="1"/>
@@ -8894,11 +9093,11 @@
         <v>487.3</v>
       </c>
       <c r="D66" s="1"/>
-      <c r="E66" s="27">
+      <c r="E66" s="26">
         <f>410+E67</f>
         <v>422.7</v>
       </c>
-      <c r="F66" s="27">
+      <c r="F66" s="26">
         <f>2.3+F67</f>
         <v>279.60000000000002</v>
       </c>
@@ -8914,7 +9113,7 @@
         <v>394.5</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>28.199999999999989</v>
       </c>
       <c r="M66" s="1"/>
@@ -8923,7 +9122,7 @@
         <v>180</v>
       </c>
       <c r="P66" s="1">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>84.539999999999992</v>
       </c>
       <c r="Q66" s="5">
@@ -8936,18 +9135,18 @@
         <f>R66*$S$1</f>
         <v>390.3821999999999</v>
       </c>
-      <c r="T66" s="5">
-        <f t="shared" si="12"/>
+      <c r="T66" s="37">
+        <f t="shared" si="13"/>
         <v>420</v>
       </c>
       <c r="U66" s="5"/>
       <c r="V66" s="1"/>
       <c r="W66" s="1">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>10.404542228530874</v>
       </c>
       <c r="X66" s="1">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>5.4364797728885739</v>
       </c>
       <c r="Y66" s="1">
@@ -8967,18 +9166,18 @@
       </c>
       <c r="AD66" s="1"/>
       <c r="AE66" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>390.3821999999999</v>
       </c>
       <c r="AF66" s="10">
         <v>5</v>
       </c>
       <c r="AG66" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>84</v>
       </c>
       <c r="AH66" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>420</v>
       </c>
       <c r="AI66" s="1">
@@ -8988,11 +9187,14 @@
         <v>84</v>
       </c>
       <c r="AK66" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="AL66" s="1"/>
-      <c r="AM66" s="1"/>
+      <c r="AM66" s="1">
+        <f t="shared" si="11"/>
+        <v>84.539999999999992</v>
+      </c>
       <c r="AN66" s="1"/>
       <c r="AO66" s="1"/>
       <c r="AP66" s="1"/>
@@ -9008,92 +9210,95 @@
       <c r="AZ66" s="1"/>
     </row>
     <row r="67" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A67" s="23" t="s">
+      <c r="A67" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="B67" s="23" t="s">
+      <c r="B67" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="C67" s="23">
+      <c r="C67" s="22">
         <v>-5</v>
       </c>
-      <c r="D67" s="23">
+      <c r="D67" s="22">
         <v>300</v>
       </c>
-      <c r="E67" s="27">
+      <c r="E67" s="26">
         <v>12.7</v>
       </c>
-      <c r="F67" s="27">
+      <c r="F67" s="26">
         <v>277.3</v>
       </c>
-      <c r="G67" s="24">
+      <c r="G67" s="23">
         <v>0</v>
       </c>
-      <c r="H67" s="23"/>
-      <c r="I67" s="23" t="s">
+      <c r="H67" s="22"/>
+      <c r="I67" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="J67" s="23" t="s">
+      <c r="J67" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="K67" s="23">
+      <c r="K67" s="22">
         <v>12.7</v>
       </c>
-      <c r="L67" s="23">
-        <f t="shared" si="16"/>
+      <c r="L67" s="22">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="M67" s="23"/>
-      <c r="N67" s="23"/>
-      <c r="O67" s="23">
+      <c r="M67" s="22"/>
+      <c r="N67" s="22"/>
+      <c r="O67" s="22">
         <v>0</v>
       </c>
-      <c r="P67" s="23">
-        <f t="shared" si="17"/>
+      <c r="P67" s="22">
+        <f t="shared" si="18"/>
         <v>2.54</v>
       </c>
-      <c r="Q67" s="25"/>
-      <c r="R67" s="25"/>
-      <c r="S67" s="25"/>
-      <c r="T67" s="25">
-        <f t="shared" si="12"/>
+      <c r="Q67" s="24"/>
+      <c r="R67" s="24"/>
+      <c r="S67" s="24"/>
+      <c r="T67" s="38">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="U67" s="25"/>
-      <c r="V67" s="23"/>
-      <c r="W67" s="23">
-        <f t="shared" si="18"/>
-        <v>109.1732283464567</v>
-      </c>
-      <c r="X67" s="23">
+      <c r="U67" s="24"/>
+      <c r="V67" s="22"/>
+      <c r="W67" s="22">
         <f t="shared" si="19"/>
         <v>109.1732283464567</v>
       </c>
-      <c r="Y67" s="23">
+      <c r="X67" s="22">
+        <f t="shared" si="20"/>
+        <v>109.1732283464567</v>
+      </c>
+      <c r="Y67" s="22">
         <v>1</v>
       </c>
-      <c r="Z67" s="23">
+      <c r="Z67" s="22">
         <v>0</v>
       </c>
-      <c r="AA67" s="23">
+      <c r="AA67" s="22">
         <v>0</v>
       </c>
-      <c r="AB67" s="23">
+      <c r="AB67" s="22">
         <v>0</v>
       </c>
-      <c r="AC67" s="23">
+      <c r="AC67" s="22">
         <v>0</v>
       </c>
-      <c r="AD67" s="23"/>
-      <c r="AE67" s="26"/>
-      <c r="AF67" s="26"/>
-      <c r="AG67" s="23"/>
-      <c r="AH67" s="23"/>
-      <c r="AI67" s="23"/>
-      <c r="AJ67" s="23"/>
-      <c r="AK67" s="26"/>
+      <c r="AD67" s="22"/>
+      <c r="AE67" s="25"/>
+      <c r="AF67" s="25"/>
+      <c r="AG67" s="22"/>
+      <c r="AH67" s="22"/>
+      <c r="AI67" s="22"/>
+      <c r="AJ67" s="22"/>
+      <c r="AK67" s="25"/>
       <c r="AL67" s="1"/>
-      <c r="AM67" s="1"/>
+      <c r="AM67" s="1">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
       <c r="AN67" s="1"/>
       <c r="AO67" s="1"/>
       <c r="AP67" s="1"/>
@@ -9108,7 +9313,7 @@
       <c r="AY67" s="1"/>
       <c r="AZ67" s="1"/>
     </row>
-    <row r="68" spans="1:53" s="31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:53" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="19" t="s">
         <v>167</v>
       </c>
@@ -9121,7 +9326,7 @@
       <c r="D68" s="19"/>
       <c r="E68" s="19"/>
       <c r="F68" s="19"/>
-      <c r="G68" s="28">
+      <c r="G68" s="27">
         <v>1</v>
       </c>
       <c r="H68" s="19">
@@ -9139,37 +9344,37 @@
         <v>0</v>
       </c>
       <c r="P68" s="19">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q68" s="29">
+      <c r="Q68" s="28">
         <v>0</v>
       </c>
-      <c r="R68" s="29">
+      <c r="R68" s="28">
         <v>550</v>
       </c>
       <c r="S68" s="5">
         <f>R68*$S$1</f>
         <v>456.5</v>
       </c>
-      <c r="T68" s="29">
-        <f t="shared" si="12"/>
+      <c r="T68" s="39">
+        <f t="shared" si="13"/>
         <v>468</v>
       </c>
-      <c r="U68" s="29">
+      <c r="U68" s="28">
         <v>550</v>
       </c>
       <c r="V68" s="19" t="s">
         <v>169</v>
       </c>
       <c r="W68" s="19" t="e">
-        <f t="shared" si="18"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X68" s="19" t="e">
         <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="X68" s="19" t="e">
+        <f t="shared" si="20"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="Y68" s="19">
         <v>14.4</v>
       </c>
@@ -9187,18 +9392,18 @@
       </c>
       <c r="AD68" s="19"/>
       <c r="AE68" s="19">
-        <f t="shared" ref="AE68" si="24">G68*S68</f>
+        <f t="shared" ref="AE68" si="25">G68*S68</f>
         <v>456.5</v>
       </c>
-      <c r="AF68" s="30">
+      <c r="AF68" s="29">
         <v>3</v>
       </c>
       <c r="AG68" s="19">
-        <f t="shared" ref="AG68" si="25">MROUND(S68, AF68*AI68)/AF68</f>
+        <f t="shared" ref="AG68" si="26">MROUND(S68, AF68*AI68)/AF68</f>
         <v>156</v>
       </c>
       <c r="AH68" s="19">
-        <f t="shared" ref="AH68" si="26">AG68*AF68*G68</f>
+        <f t="shared" ref="AH68" si="27">AG68*AF68*G68</f>
         <v>468</v>
       </c>
       <c r="AI68" s="19">
@@ -9207,8 +9412,8 @@
       <c r="AJ68" s="19">
         <v>84</v>
       </c>
-      <c r="AK68" s="30">
-        <f t="shared" ref="AK68" si="27">AG68/AJ68</f>
+      <c r="AK68" s="29">
+        <f t="shared" ref="AK68" si="28">AG68/AJ68</f>
         <v>1.8571428571428572</v>
       </c>
       <c r="AL68" s="19"/>
@@ -9248,7 +9453,7 @@
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
       <c r="S69" s="1"/>
-      <c r="T69" s="1"/>
+      <c r="T69" s="33"/>
       <c r="U69" s="1"/>
       <c r="V69" s="1"/>
       <c r="W69" s="1"/>
@@ -9302,7 +9507,7 @@
       <c r="Q70" s="1"/>
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
-      <c r="T70" s="1"/>
+      <c r="T70" s="33"/>
       <c r="U70" s="1"/>
       <c r="V70" s="1"/>
       <c r="W70" s="1"/>
@@ -9356,7 +9561,7 @@
       <c r="Q71" s="1"/>
       <c r="R71" s="1"/>
       <c r="S71" s="1"/>
-      <c r="T71" s="1"/>
+      <c r="T71" s="33"/>
       <c r="U71" s="1"/>
       <c r="V71" s="1"/>
       <c r="W71" s="1"/>
@@ -9410,7 +9615,7 @@
       <c r="Q72" s="1"/>
       <c r="R72" s="1"/>
       <c r="S72" s="1"/>
-      <c r="T72" s="1"/>
+      <c r="T72" s="33"/>
       <c r="U72" s="1"/>
       <c r="V72" s="1"/>
       <c r="W72" s="1"/>
@@ -9464,7 +9669,7 @@
       <c r="Q73" s="1"/>
       <c r="R73" s="1"/>
       <c r="S73" s="1"/>
-      <c r="T73" s="1"/>
+      <c r="T73" s="33"/>
       <c r="U73" s="1"/>
       <c r="V73" s="1"/>
       <c r="W73" s="1"/>
@@ -9518,7 +9723,7 @@
       <c r="Q74" s="1"/>
       <c r="R74" s="1"/>
       <c r="S74" s="1"/>
-      <c r="T74" s="1"/>
+      <c r="T74" s="33"/>
       <c r="U74" s="1"/>
       <c r="V74" s="1"/>
       <c r="W74" s="1"/>
@@ -9572,7 +9777,7 @@
       <c r="Q75" s="1"/>
       <c r="R75" s="1"/>
       <c r="S75" s="1"/>
-      <c r="T75" s="1"/>
+      <c r="T75" s="33"/>
       <c r="U75" s="1"/>
       <c r="V75" s="1"/>
       <c r="W75" s="1"/>
@@ -9626,7 +9831,7 @@
       <c r="Q76" s="1"/>
       <c r="R76" s="1"/>
       <c r="S76" s="1"/>
-      <c r="T76" s="1"/>
+      <c r="T76" s="33"/>
       <c r="U76" s="1"/>
       <c r="V76" s="1"/>
       <c r="W76" s="1"/>
@@ -9680,7 +9885,7 @@
       <c r="Q77" s="1"/>
       <c r="R77" s="1"/>
       <c r="S77" s="1"/>
-      <c r="T77" s="1"/>
+      <c r="T77" s="33"/>
       <c r="U77" s="1"/>
       <c r="V77" s="1"/>
       <c r="W77" s="1"/>
@@ -9734,7 +9939,7 @@
       <c r="Q78" s="1"/>
       <c r="R78" s="1"/>
       <c r="S78" s="1"/>
-      <c r="T78" s="1"/>
+      <c r="T78" s="33"/>
       <c r="U78" s="1"/>
       <c r="V78" s="1"/>
       <c r="W78" s="1"/>
@@ -9788,7 +9993,7 @@
       <c r="Q79" s="1"/>
       <c r="R79" s="1"/>
       <c r="S79" s="1"/>
-      <c r="T79" s="1"/>
+      <c r="T79" s="33"/>
       <c r="U79" s="1"/>
       <c r="V79" s="1"/>
       <c r="W79" s="1"/>
@@ -9842,7 +10047,7 @@
       <c r="Q80" s="1"/>
       <c r="R80" s="1"/>
       <c r="S80" s="1"/>
-      <c r="T80" s="1"/>
+      <c r="T80" s="33"/>
       <c r="U80" s="1"/>
       <c r="V80" s="1"/>
       <c r="W80" s="1"/>
@@ -9896,7 +10101,7 @@
       <c r="Q81" s="1"/>
       <c r="R81" s="1"/>
       <c r="S81" s="1"/>
-      <c r="T81" s="1"/>
+      <c r="T81" s="33"/>
       <c r="U81" s="1"/>
       <c r="V81" s="1"/>
       <c r="W81" s="1"/>
@@ -9950,7 +10155,7 @@
       <c r="Q82" s="1"/>
       <c r="R82" s="1"/>
       <c r="S82" s="1"/>
-      <c r="T82" s="1"/>
+      <c r="T82" s="33"/>
       <c r="U82" s="1"/>
       <c r="V82" s="1"/>
       <c r="W82" s="1"/>
@@ -10004,7 +10209,7 @@
       <c r="Q83" s="1"/>
       <c r="R83" s="1"/>
       <c r="S83" s="1"/>
-      <c r="T83" s="1"/>
+      <c r="T83" s="33"/>
       <c r="U83" s="1"/>
       <c r="V83" s="1"/>
       <c r="W83" s="1"/>
@@ -10058,7 +10263,7 @@
       <c r="Q84" s="1"/>
       <c r="R84" s="1"/>
       <c r="S84" s="1"/>
-      <c r="T84" s="1"/>
+      <c r="T84" s="33"/>
       <c r="U84" s="1"/>
       <c r="V84" s="1"/>
       <c r="W84" s="1"/>
@@ -10112,7 +10317,7 @@
       <c r="Q85" s="1"/>
       <c r="R85" s="1"/>
       <c r="S85" s="1"/>
-      <c r="T85" s="1"/>
+      <c r="T85" s="33"/>
       <c r="U85" s="1"/>
       <c r="V85" s="1"/>
       <c r="W85" s="1"/>
@@ -10166,7 +10371,7 @@
       <c r="Q86" s="1"/>
       <c r="R86" s="1"/>
       <c r="S86" s="1"/>
-      <c r="T86" s="1"/>
+      <c r="T86" s="33"/>
       <c r="U86" s="1"/>
       <c r="V86" s="1"/>
       <c r="W86" s="1"/>
@@ -10220,7 +10425,7 @@
       <c r="Q87" s="1"/>
       <c r="R87" s="1"/>
       <c r="S87" s="1"/>
-      <c r="T87" s="1"/>
+      <c r="T87" s="33"/>
       <c r="U87" s="1"/>
       <c r="V87" s="1"/>
       <c r="W87" s="1"/>
@@ -10274,7 +10479,7 @@
       <c r="Q88" s="1"/>
       <c r="R88" s="1"/>
       <c r="S88" s="1"/>
-      <c r="T88" s="1"/>
+      <c r="T88" s="33"/>
       <c r="U88" s="1"/>
       <c r="V88" s="1"/>
       <c r="W88" s="1"/>
@@ -10328,7 +10533,7 @@
       <c r="Q89" s="1"/>
       <c r="R89" s="1"/>
       <c r="S89" s="1"/>
-      <c r="T89" s="1"/>
+      <c r="T89" s="33"/>
       <c r="U89" s="1"/>
       <c r="V89" s="1"/>
       <c r="W89" s="1"/>
@@ -10382,7 +10587,7 @@
       <c r="Q90" s="1"/>
       <c r="R90" s="1"/>
       <c r="S90" s="1"/>
-      <c r="T90" s="1"/>
+      <c r="T90" s="33"/>
       <c r="U90" s="1"/>
       <c r="V90" s="1"/>
       <c r="W90" s="1"/>
@@ -10436,7 +10641,7 @@
       <c r="Q91" s="1"/>
       <c r="R91" s="1"/>
       <c r="S91" s="1"/>
-      <c r="T91" s="1"/>
+      <c r="T91" s="33"/>
       <c r="U91" s="1"/>
       <c r="V91" s="1"/>
       <c r="W91" s="1"/>
@@ -10490,7 +10695,7 @@
       <c r="Q92" s="1"/>
       <c r="R92" s="1"/>
       <c r="S92" s="1"/>
-      <c r="T92" s="1"/>
+      <c r="T92" s="33"/>
       <c r="U92" s="1"/>
       <c r="V92" s="1"/>
       <c r="W92" s="1"/>
@@ -10544,7 +10749,7 @@
       <c r="Q93" s="1"/>
       <c r="R93" s="1"/>
       <c r="S93" s="1"/>
-      <c r="T93" s="1"/>
+      <c r="T93" s="33"/>
       <c r="U93" s="1"/>
       <c r="V93" s="1"/>
       <c r="W93" s="1"/>
@@ -10598,7 +10803,7 @@
       <c r="Q94" s="1"/>
       <c r="R94" s="1"/>
       <c r="S94" s="1"/>
-      <c r="T94" s="1"/>
+      <c r="T94" s="33"/>
       <c r="U94" s="1"/>
       <c r="V94" s="1"/>
       <c r="W94" s="1"/>
@@ -10652,7 +10857,7 @@
       <c r="Q95" s="1"/>
       <c r="R95" s="1"/>
       <c r="S95" s="1"/>
-      <c r="T95" s="1"/>
+      <c r="T95" s="33"/>
       <c r="U95" s="1"/>
       <c r="V95" s="1"/>
       <c r="W95" s="1"/>
@@ -10706,7 +10911,7 @@
       <c r="Q96" s="1"/>
       <c r="R96" s="1"/>
       <c r="S96" s="1"/>
-      <c r="T96" s="1"/>
+      <c r="T96" s="33"/>
       <c r="U96" s="1"/>
       <c r="V96" s="1"/>
       <c r="W96" s="1"/>
@@ -10760,7 +10965,7 @@
       <c r="Q97" s="1"/>
       <c r="R97" s="1"/>
       <c r="S97" s="1"/>
-      <c r="T97" s="1"/>
+      <c r="T97" s="33"/>
       <c r="U97" s="1"/>
       <c r="V97" s="1"/>
       <c r="W97" s="1"/>
@@ -10814,7 +11019,7 @@
       <c r="Q98" s="1"/>
       <c r="R98" s="1"/>
       <c r="S98" s="1"/>
-      <c r="T98" s="1"/>
+      <c r="T98" s="33"/>
       <c r="U98" s="1"/>
       <c r="V98" s="1"/>
       <c r="W98" s="1"/>
@@ -10868,7 +11073,7 @@
       <c r="Q99" s="1"/>
       <c r="R99" s="1"/>
       <c r="S99" s="1"/>
-      <c r="T99" s="1"/>
+      <c r="T99" s="33"/>
       <c r="U99" s="1"/>
       <c r="V99" s="1"/>
       <c r="W99" s="1"/>
@@ -10922,7 +11127,7 @@
       <c r="Q100" s="1"/>
       <c r="R100" s="1"/>
       <c r="S100" s="1"/>
-      <c r="T100" s="1"/>
+      <c r="T100" s="33"/>
       <c r="U100" s="1"/>
       <c r="V100" s="1"/>
       <c r="W100" s="1"/>
@@ -10976,7 +11181,7 @@
       <c r="Q101" s="1"/>
       <c r="R101" s="1"/>
       <c r="S101" s="1"/>
-      <c r="T101" s="1"/>
+      <c r="T101" s="33"/>
       <c r="U101" s="1"/>
       <c r="V101" s="1"/>
       <c r="W101" s="1"/>
@@ -11030,7 +11235,7 @@
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
       <c r="S102" s="1"/>
-      <c r="T102" s="1"/>
+      <c r="T102" s="33"/>
       <c r="U102" s="1"/>
       <c r="V102" s="1"/>
       <c r="W102" s="1"/>
@@ -11084,7 +11289,7 @@
       <c r="Q103" s="1"/>
       <c r="R103" s="1"/>
       <c r="S103" s="1"/>
-      <c r="T103" s="1"/>
+      <c r="T103" s="33"/>
       <c r="U103" s="1"/>
       <c r="V103" s="1"/>
       <c r="W103" s="1"/>
@@ -11138,7 +11343,7 @@
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
       <c r="S104" s="1"/>
-      <c r="T104" s="1"/>
+      <c r="T104" s="33"/>
       <c r="U104" s="1"/>
       <c r="V104" s="1"/>
       <c r="W104" s="1"/>
@@ -11192,7 +11397,7 @@
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
       <c r="S105" s="1"/>
-      <c r="T105" s="1"/>
+      <c r="T105" s="33"/>
       <c r="U105" s="1"/>
       <c r="V105" s="1"/>
       <c r="W105" s="1"/>
@@ -11246,7 +11451,7 @@
       <c r="Q106" s="1"/>
       <c r="R106" s="1"/>
       <c r="S106" s="1"/>
-      <c r="T106" s="1"/>
+      <c r="T106" s="33"/>
       <c r="U106" s="1"/>
       <c r="V106" s="1"/>
       <c r="W106" s="1"/>
@@ -11300,7 +11505,7 @@
       <c r="Q107" s="1"/>
       <c r="R107" s="1"/>
       <c r="S107" s="1"/>
-      <c r="T107" s="1"/>
+      <c r="T107" s="33"/>
       <c r="U107" s="1"/>
       <c r="V107" s="1"/>
       <c r="W107" s="1"/>
@@ -11354,7 +11559,7 @@
       <c r="Q108" s="1"/>
       <c r="R108" s="1"/>
       <c r="S108" s="1"/>
-      <c r="T108" s="1"/>
+      <c r="T108" s="33"/>
       <c r="U108" s="1"/>
       <c r="V108" s="1"/>
       <c r="W108" s="1"/>
@@ -11408,7 +11613,7 @@
       <c r="Q109" s="1"/>
       <c r="R109" s="1"/>
       <c r="S109" s="1"/>
-      <c r="T109" s="1"/>
+      <c r="T109" s="33"/>
       <c r="U109" s="1"/>
       <c r="V109" s="1"/>
       <c r="W109" s="1"/>
@@ -11462,7 +11667,7 @@
       <c r="Q110" s="1"/>
       <c r="R110" s="1"/>
       <c r="S110" s="1"/>
-      <c r="T110" s="1"/>
+      <c r="T110" s="33"/>
       <c r="U110" s="1"/>
       <c r="V110" s="1"/>
       <c r="W110" s="1"/>
@@ -11516,7 +11721,7 @@
       <c r="Q111" s="1"/>
       <c r="R111" s="1"/>
       <c r="S111" s="1"/>
-      <c r="T111" s="1"/>
+      <c r="T111" s="33"/>
       <c r="U111" s="1"/>
       <c r="V111" s="1"/>
       <c r="W111" s="1"/>
@@ -11570,7 +11775,7 @@
       <c r="Q112" s="1"/>
       <c r="R112" s="1"/>
       <c r="S112" s="1"/>
-      <c r="T112" s="1"/>
+      <c r="T112" s="33"/>
       <c r="U112" s="1"/>
       <c r="V112" s="1"/>
       <c r="W112" s="1"/>
@@ -11624,7 +11829,7 @@
       <c r="Q113" s="1"/>
       <c r="R113" s="1"/>
       <c r="S113" s="1"/>
-      <c r="T113" s="1"/>
+      <c r="T113" s="33"/>
       <c r="U113" s="1"/>
       <c r="V113" s="1"/>
       <c r="W113" s="1"/>
@@ -11678,7 +11883,7 @@
       <c r="Q114" s="1"/>
       <c r="R114" s="1"/>
       <c r="S114" s="1"/>
-      <c r="T114" s="1"/>
+      <c r="T114" s="33"/>
       <c r="U114" s="1"/>
       <c r="V114" s="1"/>
       <c r="W114" s="1"/>
@@ -11732,7 +11937,7 @@
       <c r="Q115" s="1"/>
       <c r="R115" s="1"/>
       <c r="S115" s="1"/>
-      <c r="T115" s="1"/>
+      <c r="T115" s="33"/>
       <c r="U115" s="1"/>
       <c r="V115" s="1"/>
       <c r="W115" s="1"/>
@@ -11786,7 +11991,7 @@
       <c r="Q116" s="1"/>
       <c r="R116" s="1"/>
       <c r="S116" s="1"/>
-      <c r="T116" s="1"/>
+      <c r="T116" s="33"/>
       <c r="U116" s="1"/>
       <c r="V116" s="1"/>
       <c r="W116" s="1"/>
@@ -11840,7 +12045,7 @@
       <c r="Q117" s="1"/>
       <c r="R117" s="1"/>
       <c r="S117" s="1"/>
-      <c r="T117" s="1"/>
+      <c r="T117" s="33"/>
       <c r="U117" s="1"/>
       <c r="V117" s="1"/>
       <c r="W117" s="1"/>
@@ -11894,7 +12099,7 @@
       <c r="Q118" s="1"/>
       <c r="R118" s="1"/>
       <c r="S118" s="1"/>
-      <c r="T118" s="1"/>
+      <c r="T118" s="33"/>
       <c r="U118" s="1"/>
       <c r="V118" s="1"/>
       <c r="W118" s="1"/>
@@ -11948,7 +12153,7 @@
       <c r="Q119" s="1"/>
       <c r="R119" s="1"/>
       <c r="S119" s="1"/>
-      <c r="T119" s="1"/>
+      <c r="T119" s="33"/>
       <c r="U119" s="1"/>
       <c r="V119" s="1"/>
       <c r="W119" s="1"/>
@@ -12002,7 +12207,7 @@
       <c r="Q120" s="1"/>
       <c r="R120" s="1"/>
       <c r="S120" s="1"/>
-      <c r="T120" s="1"/>
+      <c r="T120" s="33"/>
       <c r="U120" s="1"/>
       <c r="V120" s="1"/>
       <c r="W120" s="1"/>
@@ -12056,7 +12261,7 @@
       <c r="Q121" s="1"/>
       <c r="R121" s="1"/>
       <c r="S121" s="1"/>
-      <c r="T121" s="1"/>
+      <c r="T121" s="33"/>
       <c r="U121" s="1"/>
       <c r="V121" s="1"/>
       <c r="W121" s="1"/>
@@ -12110,7 +12315,7 @@
       <c r="Q122" s="1"/>
       <c r="R122" s="1"/>
       <c r="S122" s="1"/>
-      <c r="T122" s="1"/>
+      <c r="T122" s="33"/>
       <c r="U122" s="1"/>
       <c r="V122" s="1"/>
       <c r="W122" s="1"/>
@@ -12164,7 +12369,7 @@
       <c r="Q123" s="1"/>
       <c r="R123" s="1"/>
       <c r="S123" s="1"/>
-      <c r="T123" s="1"/>
+      <c r="T123" s="33"/>
       <c r="U123" s="1"/>
       <c r="V123" s="1"/>
       <c r="W123" s="1"/>
@@ -12218,7 +12423,7 @@
       <c r="Q124" s="1"/>
       <c r="R124" s="1"/>
       <c r="S124" s="1"/>
-      <c r="T124" s="1"/>
+      <c r="T124" s="33"/>
       <c r="U124" s="1"/>
       <c r="V124" s="1"/>
       <c r="W124" s="1"/>
@@ -12272,7 +12477,7 @@
       <c r="Q125" s="1"/>
       <c r="R125" s="1"/>
       <c r="S125" s="1"/>
-      <c r="T125" s="1"/>
+      <c r="T125" s="33"/>
       <c r="U125" s="1"/>
       <c r="V125" s="1"/>
       <c r="W125" s="1"/>
@@ -12326,7 +12531,7 @@
       <c r="Q126" s="1"/>
       <c r="R126" s="1"/>
       <c r="S126" s="1"/>
-      <c r="T126" s="1"/>
+      <c r="T126" s="33"/>
       <c r="U126" s="1"/>
       <c r="V126" s="1"/>
       <c r="W126" s="1"/>
@@ -12380,7 +12585,7 @@
       <c r="Q127" s="1"/>
       <c r="R127" s="1"/>
       <c r="S127" s="1"/>
-      <c r="T127" s="1"/>
+      <c r="T127" s="33"/>
       <c r="U127" s="1"/>
       <c r="V127" s="1"/>
       <c r="W127" s="1"/>
@@ -12434,7 +12639,7 @@
       <c r="Q128" s="1"/>
       <c r="R128" s="1"/>
       <c r="S128" s="1"/>
-      <c r="T128" s="1"/>
+      <c r="T128" s="33"/>
       <c r="U128" s="1"/>
       <c r="V128" s="1"/>
       <c r="W128" s="1"/>
@@ -12488,7 +12693,7 @@
       <c r="Q129" s="1"/>
       <c r="R129" s="1"/>
       <c r="S129" s="1"/>
-      <c r="T129" s="1"/>
+      <c r="T129" s="33"/>
       <c r="U129" s="1"/>
       <c r="V129" s="1"/>
       <c r="W129" s="1"/>
@@ -12542,7 +12747,7 @@
       <c r="Q130" s="1"/>
       <c r="R130" s="1"/>
       <c r="S130" s="1"/>
-      <c r="T130" s="1"/>
+      <c r="T130" s="33"/>
       <c r="U130" s="1"/>
       <c r="V130" s="1"/>
       <c r="W130" s="1"/>
@@ -12596,7 +12801,7 @@
       <c r="Q131" s="1"/>
       <c r="R131" s="1"/>
       <c r="S131" s="1"/>
-      <c r="T131" s="1"/>
+      <c r="T131" s="33"/>
       <c r="U131" s="1"/>
       <c r="V131" s="1"/>
       <c r="W131" s="1"/>
@@ -12650,7 +12855,7 @@
       <c r="Q132" s="1"/>
       <c r="R132" s="1"/>
       <c r="S132" s="1"/>
-      <c r="T132" s="1"/>
+      <c r="T132" s="33"/>
       <c r="U132" s="1"/>
       <c r="V132" s="1"/>
       <c r="W132" s="1"/>
@@ -12704,7 +12909,7 @@
       <c r="Q133" s="1"/>
       <c r="R133" s="1"/>
       <c r="S133" s="1"/>
-      <c r="T133" s="1"/>
+      <c r="T133" s="33"/>
       <c r="U133" s="1"/>
       <c r="V133" s="1"/>
       <c r="W133" s="1"/>
@@ -12758,7 +12963,7 @@
       <c r="Q134" s="1"/>
       <c r="R134" s="1"/>
       <c r="S134" s="1"/>
-      <c r="T134" s="1"/>
+      <c r="T134" s="33"/>
       <c r="U134" s="1"/>
       <c r="V134" s="1"/>
       <c r="W134" s="1"/>
@@ -12812,7 +13017,7 @@
       <c r="Q135" s="1"/>
       <c r="R135" s="1"/>
       <c r="S135" s="1"/>
-      <c r="T135" s="1"/>
+      <c r="T135" s="33"/>
       <c r="U135" s="1"/>
       <c r="V135" s="1"/>
       <c r="W135" s="1"/>
@@ -12866,7 +13071,7 @@
       <c r="Q136" s="1"/>
       <c r="R136" s="1"/>
       <c r="S136" s="1"/>
-      <c r="T136" s="1"/>
+      <c r="T136" s="33"/>
       <c r="U136" s="1"/>
       <c r="V136" s="1"/>
       <c r="W136" s="1"/>
@@ -12920,7 +13125,7 @@
       <c r="Q137" s="1"/>
       <c r="R137" s="1"/>
       <c r="S137" s="1"/>
-      <c r="T137" s="1"/>
+      <c r="T137" s="33"/>
       <c r="U137" s="1"/>
       <c r="V137" s="1"/>
       <c r="W137" s="1"/>
@@ -12974,7 +13179,7 @@
       <c r="Q138" s="1"/>
       <c r="R138" s="1"/>
       <c r="S138" s="1"/>
-      <c r="T138" s="1"/>
+      <c r="T138" s="33"/>
       <c r="U138" s="1"/>
       <c r="V138" s="1"/>
       <c r="W138" s="1"/>
@@ -13028,7 +13233,7 @@
       <c r="Q139" s="1"/>
       <c r="R139" s="1"/>
       <c r="S139" s="1"/>
-      <c r="T139" s="1"/>
+      <c r="T139" s="33"/>
       <c r="U139" s="1"/>
       <c r="V139" s="1"/>
       <c r="W139" s="1"/>
@@ -13082,7 +13287,7 @@
       <c r="Q140" s="1"/>
       <c r="R140" s="1"/>
       <c r="S140" s="1"/>
-      <c r="T140" s="1"/>
+      <c r="T140" s="33"/>
       <c r="U140" s="1"/>
       <c r="V140" s="1"/>
       <c r="W140" s="1"/>
@@ -13136,7 +13341,7 @@
       <c r="Q141" s="1"/>
       <c r="R141" s="1"/>
       <c r="S141" s="1"/>
-      <c r="T141" s="1"/>
+      <c r="T141" s="33"/>
       <c r="U141" s="1"/>
       <c r="V141" s="1"/>
       <c r="W141" s="1"/>
@@ -13190,7 +13395,7 @@
       <c r="Q142" s="1"/>
       <c r="R142" s="1"/>
       <c r="S142" s="1"/>
-      <c r="T142" s="1"/>
+      <c r="T142" s="33"/>
       <c r="U142" s="1"/>
       <c r="V142" s="1"/>
       <c r="W142" s="1"/>
@@ -13244,7 +13449,7 @@
       <c r="Q143" s="1"/>
       <c r="R143" s="1"/>
       <c r="S143" s="1"/>
-      <c r="T143" s="1"/>
+      <c r="T143" s="33"/>
       <c r="U143" s="1"/>
       <c r="V143" s="1"/>
       <c r="W143" s="1"/>
@@ -13298,7 +13503,7 @@
       <c r="Q144" s="1"/>
       <c r="R144" s="1"/>
       <c r="S144" s="1"/>
-      <c r="T144" s="1"/>
+      <c r="T144" s="33"/>
       <c r="U144" s="1"/>
       <c r="V144" s="1"/>
       <c r="W144" s="1"/>
@@ -13352,7 +13557,7 @@
       <c r="Q145" s="1"/>
       <c r="R145" s="1"/>
       <c r="S145" s="1"/>
-      <c r="T145" s="1"/>
+      <c r="T145" s="33"/>
       <c r="U145" s="1"/>
       <c r="V145" s="1"/>
       <c r="W145" s="1"/>
@@ -13406,7 +13611,7 @@
       <c r="Q146" s="1"/>
       <c r="R146" s="1"/>
       <c r="S146" s="1"/>
-      <c r="T146" s="1"/>
+      <c r="T146" s="33"/>
       <c r="U146" s="1"/>
       <c r="V146" s="1"/>
       <c r="W146" s="1"/>
@@ -13460,7 +13665,7 @@
       <c r="Q147" s="1"/>
       <c r="R147" s="1"/>
       <c r="S147" s="1"/>
-      <c r="T147" s="1"/>
+      <c r="T147" s="33"/>
       <c r="U147" s="1"/>
       <c r="V147" s="1"/>
       <c r="W147" s="1"/>
@@ -13514,7 +13719,7 @@
       <c r="Q148" s="1"/>
       <c r="R148" s="1"/>
       <c r="S148" s="1"/>
-      <c r="T148" s="1"/>
+      <c r="T148" s="33"/>
       <c r="U148" s="1"/>
       <c r="V148" s="1"/>
       <c r="W148" s="1"/>
@@ -13568,7 +13773,7 @@
       <c r="Q149" s="1"/>
       <c r="R149" s="1"/>
       <c r="S149" s="1"/>
-      <c r="T149" s="1"/>
+      <c r="T149" s="33"/>
       <c r="U149" s="1"/>
       <c r="V149" s="1"/>
       <c r="W149" s="1"/>
@@ -13622,7 +13827,7 @@
       <c r="Q150" s="1"/>
       <c r="R150" s="1"/>
       <c r="S150" s="1"/>
-      <c r="T150" s="1"/>
+      <c r="T150" s="33"/>
       <c r="U150" s="1"/>
       <c r="V150" s="1"/>
       <c r="W150" s="1"/>
@@ -13676,7 +13881,7 @@
       <c r="Q151" s="1"/>
       <c r="R151" s="1"/>
       <c r="S151" s="1"/>
-      <c r="T151" s="1"/>
+      <c r="T151" s="33"/>
       <c r="U151" s="1"/>
       <c r="V151" s="1"/>
       <c r="W151" s="1"/>
@@ -13730,7 +13935,7 @@
       <c r="Q152" s="1"/>
       <c r="R152" s="1"/>
       <c r="S152" s="1"/>
-      <c r="T152" s="1"/>
+      <c r="T152" s="33"/>
       <c r="U152" s="1"/>
       <c r="V152" s="1"/>
       <c r="W152" s="1"/>
@@ -13784,7 +13989,7 @@
       <c r="Q153" s="1"/>
       <c r="R153" s="1"/>
       <c r="S153" s="1"/>
-      <c r="T153" s="1"/>
+      <c r="T153" s="33"/>
       <c r="U153" s="1"/>
       <c r="V153" s="1"/>
       <c r="W153" s="1"/>
@@ -13838,7 +14043,7 @@
       <c r="Q154" s="1"/>
       <c r="R154" s="1"/>
       <c r="S154" s="1"/>
-      <c r="T154" s="1"/>
+      <c r="T154" s="33"/>
       <c r="U154" s="1"/>
       <c r="V154" s="1"/>
       <c r="W154" s="1"/>
@@ -13892,7 +14097,7 @@
       <c r="Q155" s="1"/>
       <c r="R155" s="1"/>
       <c r="S155" s="1"/>
-      <c r="T155" s="1"/>
+      <c r="T155" s="33"/>
       <c r="U155" s="1"/>
       <c r="V155" s="1"/>
       <c r="W155" s="1"/>
@@ -13946,7 +14151,7 @@
       <c r="Q156" s="1"/>
       <c r="R156" s="1"/>
       <c r="S156" s="1"/>
-      <c r="T156" s="1"/>
+      <c r="T156" s="33"/>
       <c r="U156" s="1"/>
       <c r="V156" s="1"/>
       <c r="W156" s="1"/>
@@ -14000,7 +14205,7 @@
       <c r="Q157" s="1"/>
       <c r="R157" s="1"/>
       <c r="S157" s="1"/>
-      <c r="T157" s="1"/>
+      <c r="T157" s="33"/>
       <c r="U157" s="1"/>
       <c r="V157" s="1"/>
       <c r="W157" s="1"/>
@@ -14054,7 +14259,7 @@
       <c r="Q158" s="1"/>
       <c r="R158" s="1"/>
       <c r="S158" s="1"/>
-      <c r="T158" s="1"/>
+      <c r="T158" s="33"/>
       <c r="U158" s="1"/>
       <c r="V158" s="1"/>
       <c r="W158" s="1"/>
@@ -14108,7 +14313,7 @@
       <c r="Q159" s="1"/>
       <c r="R159" s="1"/>
       <c r="S159" s="1"/>
-      <c r="T159" s="1"/>
+      <c r="T159" s="33"/>
       <c r="U159" s="1"/>
       <c r="V159" s="1"/>
       <c r="W159" s="1"/>
@@ -14162,7 +14367,7 @@
       <c r="Q160" s="1"/>
       <c r="R160" s="1"/>
       <c r="S160" s="1"/>
-      <c r="T160" s="1"/>
+      <c r="T160" s="33"/>
       <c r="U160" s="1"/>
       <c r="V160" s="1"/>
       <c r="W160" s="1"/>
@@ -14216,7 +14421,7 @@
       <c r="Q161" s="1"/>
       <c r="R161" s="1"/>
       <c r="S161" s="1"/>
-      <c r="T161" s="1"/>
+      <c r="T161" s="33"/>
       <c r="U161" s="1"/>
       <c r="V161" s="1"/>
       <c r="W161" s="1"/>
@@ -14270,7 +14475,7 @@
       <c r="Q162" s="1"/>
       <c r="R162" s="1"/>
       <c r="S162" s="1"/>
-      <c r="T162" s="1"/>
+      <c r="T162" s="33"/>
       <c r="U162" s="1"/>
       <c r="V162" s="1"/>
       <c r="W162" s="1"/>
@@ -14324,7 +14529,7 @@
       <c r="Q163" s="1"/>
       <c r="R163" s="1"/>
       <c r="S163" s="1"/>
-      <c r="T163" s="1"/>
+      <c r="T163" s="33"/>
       <c r="U163" s="1"/>
       <c r="V163" s="1"/>
       <c r="W163" s="1"/>
@@ -14378,7 +14583,7 @@
       <c r="Q164" s="1"/>
       <c r="R164" s="1"/>
       <c r="S164" s="1"/>
-      <c r="T164" s="1"/>
+      <c r="T164" s="33"/>
       <c r="U164" s="1"/>
       <c r="V164" s="1"/>
       <c r="W164" s="1"/>
@@ -14432,7 +14637,7 @@
       <c r="Q165" s="1"/>
       <c r="R165" s="1"/>
       <c r="S165" s="1"/>
-      <c r="T165" s="1"/>
+      <c r="T165" s="33"/>
       <c r="U165" s="1"/>
       <c r="V165" s="1"/>
       <c r="W165" s="1"/>
@@ -14486,7 +14691,7 @@
       <c r="Q166" s="1"/>
       <c r="R166" s="1"/>
       <c r="S166" s="1"/>
-      <c r="T166" s="1"/>
+      <c r="T166" s="33"/>
       <c r="U166" s="1"/>
       <c r="V166" s="1"/>
       <c r="W166" s="1"/>
@@ -14540,7 +14745,7 @@
       <c r="Q167" s="1"/>
       <c r="R167" s="1"/>
       <c r="S167" s="1"/>
-      <c r="T167" s="1"/>
+      <c r="T167" s="33"/>
       <c r="U167" s="1"/>
       <c r="V167" s="1"/>
       <c r="W167" s="1"/>
@@ -14594,7 +14799,7 @@
       <c r="Q168" s="1"/>
       <c r="R168" s="1"/>
       <c r="S168" s="1"/>
-      <c r="T168" s="1"/>
+      <c r="T168" s="33"/>
       <c r="U168" s="1"/>
       <c r="V168" s="1"/>
       <c r="W168" s="1"/>
@@ -14648,7 +14853,7 @@
       <c r="Q169" s="1"/>
       <c r="R169" s="1"/>
       <c r="S169" s="1"/>
-      <c r="T169" s="1"/>
+      <c r="T169" s="33"/>
       <c r="U169" s="1"/>
       <c r="V169" s="1"/>
       <c r="W169" s="1"/>
@@ -14702,7 +14907,7 @@
       <c r="Q170" s="1"/>
       <c r="R170" s="1"/>
       <c r="S170" s="1"/>
-      <c r="T170" s="1"/>
+      <c r="T170" s="33"/>
       <c r="U170" s="1"/>
       <c r="V170" s="1"/>
       <c r="W170" s="1"/>
@@ -14756,7 +14961,7 @@
       <c r="Q171" s="1"/>
       <c r="R171" s="1"/>
       <c r="S171" s="1"/>
-      <c r="T171" s="1"/>
+      <c r="T171" s="33"/>
       <c r="U171" s="1"/>
       <c r="V171" s="1"/>
       <c r="W171" s="1"/>
@@ -14810,7 +15015,7 @@
       <c r="Q172" s="1"/>
       <c r="R172" s="1"/>
       <c r="S172" s="1"/>
-      <c r="T172" s="1"/>
+      <c r="T172" s="33"/>
       <c r="U172" s="1"/>
       <c r="V172" s="1"/>
       <c r="W172" s="1"/>
@@ -14864,7 +15069,7 @@
       <c r="Q173" s="1"/>
       <c r="R173" s="1"/>
       <c r="S173" s="1"/>
-      <c r="T173" s="1"/>
+      <c r="T173" s="33"/>
       <c r="U173" s="1"/>
       <c r="V173" s="1"/>
       <c r="W173" s="1"/>
@@ -14918,7 +15123,7 @@
       <c r="Q174" s="1"/>
       <c r="R174" s="1"/>
       <c r="S174" s="1"/>
-      <c r="T174" s="1"/>
+      <c r="T174" s="33"/>
       <c r="U174" s="1"/>
       <c r="V174" s="1"/>
       <c r="W174" s="1"/>
@@ -14972,7 +15177,7 @@
       <c r="Q175" s="1"/>
       <c r="R175" s="1"/>
       <c r="S175" s="1"/>
-      <c r="T175" s="1"/>
+      <c r="T175" s="33"/>
       <c r="U175" s="1"/>
       <c r="V175" s="1"/>
       <c r="W175" s="1"/>
@@ -15026,7 +15231,7 @@
       <c r="Q176" s="1"/>
       <c r="R176" s="1"/>
       <c r="S176" s="1"/>
-      <c r="T176" s="1"/>
+      <c r="T176" s="33"/>
       <c r="U176" s="1"/>
       <c r="V176" s="1"/>
       <c r="W176" s="1"/>
@@ -15080,7 +15285,7 @@
       <c r="Q177" s="1"/>
       <c r="R177" s="1"/>
       <c r="S177" s="1"/>
-      <c r="T177" s="1"/>
+      <c r="T177" s="33"/>
       <c r="U177" s="1"/>
       <c r="V177" s="1"/>
       <c r="W177" s="1"/>
@@ -15134,7 +15339,7 @@
       <c r="Q178" s="1"/>
       <c r="R178" s="1"/>
       <c r="S178" s="1"/>
-      <c r="T178" s="1"/>
+      <c r="T178" s="33"/>
       <c r="U178" s="1"/>
       <c r="V178" s="1"/>
       <c r="W178" s="1"/>
@@ -15188,7 +15393,7 @@
       <c r="Q179" s="1"/>
       <c r="R179" s="1"/>
       <c r="S179" s="1"/>
-      <c r="T179" s="1"/>
+      <c r="T179" s="33"/>
       <c r="U179" s="1"/>
       <c r="V179" s="1"/>
       <c r="W179" s="1"/>
@@ -15242,7 +15447,7 @@
       <c r="Q180" s="1"/>
       <c r="R180" s="1"/>
       <c r="S180" s="1"/>
-      <c r="T180" s="1"/>
+      <c r="T180" s="33"/>
       <c r="U180" s="1"/>
       <c r="V180" s="1"/>
       <c r="W180" s="1"/>
@@ -15296,7 +15501,7 @@
       <c r="Q181" s="1"/>
       <c r="R181" s="1"/>
       <c r="S181" s="1"/>
-      <c r="T181" s="1"/>
+      <c r="T181" s="33"/>
       <c r="U181" s="1"/>
       <c r="V181" s="1"/>
       <c r="W181" s="1"/>
@@ -15350,7 +15555,7 @@
       <c r="Q182" s="1"/>
       <c r="R182" s="1"/>
       <c r="S182" s="1"/>
-      <c r="T182" s="1"/>
+      <c r="T182" s="33"/>
       <c r="U182" s="1"/>
       <c r="V182" s="1"/>
       <c r="W182" s="1"/>
@@ -15404,7 +15609,7 @@
       <c r="Q183" s="1"/>
       <c r="R183" s="1"/>
       <c r="S183" s="1"/>
-      <c r="T183" s="1"/>
+      <c r="T183" s="33"/>
       <c r="U183" s="1"/>
       <c r="V183" s="1"/>
       <c r="W183" s="1"/>
@@ -15458,7 +15663,7 @@
       <c r="Q184" s="1"/>
       <c r="R184" s="1"/>
       <c r="S184" s="1"/>
-      <c r="T184" s="1"/>
+      <c r="T184" s="33"/>
       <c r="U184" s="1"/>
       <c r="V184" s="1"/>
       <c r="W184" s="1"/>
@@ -15512,7 +15717,7 @@
       <c r="Q185" s="1"/>
       <c r="R185" s="1"/>
       <c r="S185" s="1"/>
-      <c r="T185" s="1"/>
+      <c r="T185" s="33"/>
       <c r="U185" s="1"/>
       <c r="V185" s="1"/>
       <c r="W185" s="1"/>
@@ -15566,7 +15771,7 @@
       <c r="Q186" s="1"/>
       <c r="R186" s="1"/>
       <c r="S186" s="1"/>
-      <c r="T186" s="1"/>
+      <c r="T186" s="33"/>
       <c r="U186" s="1"/>
       <c r="V186" s="1"/>
       <c r="W186" s="1"/>
@@ -15620,7 +15825,7 @@
       <c r="Q187" s="1"/>
       <c r="R187" s="1"/>
       <c r="S187" s="1"/>
-      <c r="T187" s="1"/>
+      <c r="T187" s="33"/>
       <c r="U187" s="1"/>
       <c r="V187" s="1"/>
       <c r="W187" s="1"/>
@@ -15674,7 +15879,7 @@
       <c r="Q188" s="1"/>
       <c r="R188" s="1"/>
       <c r="S188" s="1"/>
-      <c r="T188" s="1"/>
+      <c r="T188" s="33"/>
       <c r="U188" s="1"/>
       <c r="V188" s="1"/>
       <c r="W188" s="1"/>
@@ -15728,7 +15933,7 @@
       <c r="Q189" s="1"/>
       <c r="R189" s="1"/>
       <c r="S189" s="1"/>
-      <c r="T189" s="1"/>
+      <c r="T189" s="33"/>
       <c r="U189" s="1"/>
       <c r="V189" s="1"/>
       <c r="W189" s="1"/>
@@ -15782,7 +15987,7 @@
       <c r="Q190" s="1"/>
       <c r="R190" s="1"/>
       <c r="S190" s="1"/>
-      <c r="T190" s="1"/>
+      <c r="T190" s="33"/>
       <c r="U190" s="1"/>
       <c r="V190" s="1"/>
       <c r="W190" s="1"/>
@@ -15836,7 +16041,7 @@
       <c r="Q191" s="1"/>
       <c r="R191" s="1"/>
       <c r="S191" s="1"/>
-      <c r="T191" s="1"/>
+      <c r="T191" s="33"/>
       <c r="U191" s="1"/>
       <c r="V191" s="1"/>
       <c r="W191" s="1"/>
@@ -15890,7 +16095,7 @@
       <c r="Q192" s="1"/>
       <c r="R192" s="1"/>
       <c r="S192" s="1"/>
-      <c r="T192" s="1"/>
+      <c r="T192" s="33"/>
       <c r="U192" s="1"/>
       <c r="V192" s="1"/>
       <c r="W192" s="1"/>
@@ -15944,7 +16149,7 @@
       <c r="Q193" s="1"/>
       <c r="R193" s="1"/>
       <c r="S193" s="1"/>
-      <c r="T193" s="1"/>
+      <c r="T193" s="33"/>
       <c r="U193" s="1"/>
       <c r="V193" s="1"/>
       <c r="W193" s="1"/>
@@ -15998,7 +16203,7 @@
       <c r="Q194" s="1"/>
       <c r="R194" s="1"/>
       <c r="S194" s="1"/>
-      <c r="T194" s="1"/>
+      <c r="T194" s="33"/>
       <c r="U194" s="1"/>
       <c r="V194" s="1"/>
       <c r="W194" s="1"/>
@@ -16052,7 +16257,7 @@
       <c r="Q195" s="1"/>
       <c r="R195" s="1"/>
       <c r="S195" s="1"/>
-      <c r="T195" s="1"/>
+      <c r="T195" s="33"/>
       <c r="U195" s="1"/>
       <c r="V195" s="1"/>
       <c r="W195" s="1"/>
@@ -16106,7 +16311,7 @@
       <c r="Q196" s="1"/>
       <c r="R196" s="1"/>
       <c r="S196" s="1"/>
-      <c r="T196" s="1"/>
+      <c r="T196" s="33"/>
       <c r="U196" s="1"/>
       <c r="V196" s="1"/>
       <c r="W196" s="1"/>
@@ -16160,7 +16365,7 @@
       <c r="Q197" s="1"/>
       <c r="R197" s="1"/>
       <c r="S197" s="1"/>
-      <c r="T197" s="1"/>
+      <c r="T197" s="33"/>
       <c r="U197" s="1"/>
       <c r="V197" s="1"/>
       <c r="W197" s="1"/>
@@ -16214,7 +16419,7 @@
       <c r="Q198" s="1"/>
       <c r="R198" s="1"/>
       <c r="S198" s="1"/>
-      <c r="T198" s="1"/>
+      <c r="T198" s="33"/>
       <c r="U198" s="1"/>
       <c r="V198" s="1"/>
       <c r="W198" s="1"/>
@@ -16268,7 +16473,7 @@
       <c r="Q199" s="1"/>
       <c r="R199" s="1"/>
       <c r="S199" s="1"/>
-      <c r="T199" s="1"/>
+      <c r="T199" s="33"/>
       <c r="U199" s="1"/>
       <c r="V199" s="1"/>
       <c r="W199" s="1"/>
@@ -16322,7 +16527,7 @@
       <c r="Q200" s="1"/>
       <c r="R200" s="1"/>
       <c r="S200" s="1"/>
-      <c r="T200" s="1"/>
+      <c r="T200" s="33"/>
       <c r="U200" s="1"/>
       <c r="V200" s="1"/>
       <c r="W200" s="1"/>
@@ -16376,7 +16581,7 @@
       <c r="Q201" s="1"/>
       <c r="R201" s="1"/>
       <c r="S201" s="1"/>
-      <c r="T201" s="1"/>
+      <c r="T201" s="33"/>
       <c r="U201" s="1"/>
       <c r="V201" s="1"/>
       <c r="W201" s="1"/>
@@ -16430,7 +16635,7 @@
       <c r="Q202" s="1"/>
       <c r="R202" s="1"/>
       <c r="S202" s="1"/>
-      <c r="T202" s="1"/>
+      <c r="T202" s="33"/>
       <c r="U202" s="1"/>
       <c r="V202" s="1"/>
       <c r="W202" s="1"/>
@@ -16484,7 +16689,7 @@
       <c r="Q203" s="1"/>
       <c r="R203" s="1"/>
       <c r="S203" s="1"/>
-      <c r="T203" s="1"/>
+      <c r="T203" s="33"/>
       <c r="U203" s="1"/>
       <c r="V203" s="1"/>
       <c r="W203" s="1"/>
@@ -16538,7 +16743,7 @@
       <c r="Q204" s="1"/>
       <c r="R204" s="1"/>
       <c r="S204" s="1"/>
-      <c r="T204" s="1"/>
+      <c r="T204" s="33"/>
       <c r="U204" s="1"/>
       <c r="V204" s="1"/>
       <c r="W204" s="1"/>
@@ -16592,7 +16797,7 @@
       <c r="Q205" s="1"/>
       <c r="R205" s="1"/>
       <c r="S205" s="1"/>
-      <c r="T205" s="1"/>
+      <c r="T205" s="33"/>
       <c r="U205" s="1"/>
       <c r="V205" s="1"/>
       <c r="W205" s="1"/>
@@ -16646,7 +16851,7 @@
       <c r="Q206" s="1"/>
       <c r="R206" s="1"/>
       <c r="S206" s="1"/>
-      <c r="T206" s="1"/>
+      <c r="T206" s="33"/>
       <c r="U206" s="1"/>
       <c r="V206" s="1"/>
       <c r="W206" s="1"/>
@@ -16700,7 +16905,7 @@
       <c r="Q207" s="1"/>
       <c r="R207" s="1"/>
       <c r="S207" s="1"/>
-      <c r="T207" s="1"/>
+      <c r="T207" s="33"/>
       <c r="U207" s="1"/>
       <c r="V207" s="1"/>
       <c r="W207" s="1"/>
@@ -16754,7 +16959,7 @@
       <c r="Q208" s="1"/>
       <c r="R208" s="1"/>
       <c r="S208" s="1"/>
-      <c r="T208" s="1"/>
+      <c r="T208" s="33"/>
       <c r="U208" s="1"/>
       <c r="V208" s="1"/>
       <c r="W208" s="1"/>
@@ -16808,7 +17013,7 @@
       <c r="Q209" s="1"/>
       <c r="R209" s="1"/>
       <c r="S209" s="1"/>
-      <c r="T209" s="1"/>
+      <c r="T209" s="33"/>
       <c r="U209" s="1"/>
       <c r="V209" s="1"/>
       <c r="W209" s="1"/>
@@ -16862,7 +17067,7 @@
       <c r="Q210" s="1"/>
       <c r="R210" s="1"/>
       <c r="S210" s="1"/>
-      <c r="T210" s="1"/>
+      <c r="T210" s="33"/>
       <c r="U210" s="1"/>
       <c r="V210" s="1"/>
       <c r="W210" s="1"/>
@@ -16916,7 +17121,7 @@
       <c r="Q211" s="1"/>
       <c r="R211" s="1"/>
       <c r="S211" s="1"/>
-      <c r="T211" s="1"/>
+      <c r="T211" s="33"/>
       <c r="U211" s="1"/>
       <c r="V211" s="1"/>
       <c r="W211" s="1"/>
@@ -16970,7 +17175,7 @@
       <c r="Q212" s="1"/>
       <c r="R212" s="1"/>
       <c r="S212" s="1"/>
-      <c r="T212" s="1"/>
+      <c r="T212" s="33"/>
       <c r="U212" s="1"/>
       <c r="V212" s="1"/>
       <c r="W212" s="1"/>
@@ -17024,7 +17229,7 @@
       <c r="Q213" s="1"/>
       <c r="R213" s="1"/>
       <c r="S213" s="1"/>
-      <c r="T213" s="1"/>
+      <c r="T213" s="33"/>
       <c r="U213" s="1"/>
       <c r="V213" s="1"/>
       <c r="W213" s="1"/>
@@ -17078,7 +17283,7 @@
       <c r="Q214" s="1"/>
       <c r="R214" s="1"/>
       <c r="S214" s="1"/>
-      <c r="T214" s="1"/>
+      <c r="T214" s="33"/>
       <c r="U214" s="1"/>
       <c r="V214" s="1"/>
       <c r="W214" s="1"/>
@@ -17132,7 +17337,7 @@
       <c r="Q215" s="1"/>
       <c r="R215" s="1"/>
       <c r="S215" s="1"/>
-      <c r="T215" s="1"/>
+      <c r="T215" s="33"/>
       <c r="U215" s="1"/>
       <c r="V215" s="1"/>
       <c r="W215" s="1"/>
@@ -17186,7 +17391,7 @@
       <c r="Q216" s="1"/>
       <c r="R216" s="1"/>
       <c r="S216" s="1"/>
-      <c r="T216" s="1"/>
+      <c r="T216" s="33"/>
       <c r="U216" s="1"/>
       <c r="V216" s="1"/>
       <c r="W216" s="1"/>
@@ -17240,7 +17445,7 @@
       <c r="Q217" s="1"/>
       <c r="R217" s="1"/>
       <c r="S217" s="1"/>
-      <c r="T217" s="1"/>
+      <c r="T217" s="33"/>
       <c r="U217" s="1"/>
       <c r="V217" s="1"/>
       <c r="W217" s="1"/>
@@ -17294,7 +17499,7 @@
       <c r="Q218" s="1"/>
       <c r="R218" s="1"/>
       <c r="S218" s="1"/>
-      <c r="T218" s="1"/>
+      <c r="T218" s="33"/>
       <c r="U218" s="1"/>
       <c r="V218" s="1"/>
       <c r="W218" s="1"/>
@@ -17348,7 +17553,7 @@
       <c r="Q219" s="1"/>
       <c r="R219" s="1"/>
       <c r="S219" s="1"/>
-      <c r="T219" s="1"/>
+      <c r="T219" s="33"/>
       <c r="U219" s="1"/>
       <c r="V219" s="1"/>
       <c r="W219" s="1"/>
@@ -17402,7 +17607,7 @@
       <c r="Q220" s="1"/>
       <c r="R220" s="1"/>
       <c r="S220" s="1"/>
-      <c r="T220" s="1"/>
+      <c r="T220" s="33"/>
       <c r="U220" s="1"/>
       <c r="V220" s="1"/>
       <c r="W220" s="1"/>
@@ -17456,7 +17661,7 @@
       <c r="Q221" s="1"/>
       <c r="R221" s="1"/>
       <c r="S221" s="1"/>
-      <c r="T221" s="1"/>
+      <c r="T221" s="33"/>
       <c r="U221" s="1"/>
       <c r="V221" s="1"/>
       <c r="W221" s="1"/>
@@ -17510,7 +17715,7 @@
       <c r="Q222" s="1"/>
       <c r="R222" s="1"/>
       <c r="S222" s="1"/>
-      <c r="T222" s="1"/>
+      <c r="T222" s="33"/>
       <c r="U222" s="1"/>
       <c r="V222" s="1"/>
       <c r="W222" s="1"/>
@@ -17564,7 +17769,7 @@
       <c r="Q223" s="1"/>
       <c r="R223" s="1"/>
       <c r="S223" s="1"/>
-      <c r="T223" s="1"/>
+      <c r="T223" s="33"/>
       <c r="U223" s="1"/>
       <c r="V223" s="1"/>
       <c r="W223" s="1"/>
@@ -17618,7 +17823,7 @@
       <c r="Q224" s="1"/>
       <c r="R224" s="1"/>
       <c r="S224" s="1"/>
-      <c r="T224" s="1"/>
+      <c r="T224" s="33"/>
       <c r="U224" s="1"/>
       <c r="V224" s="1"/>
       <c r="W224" s="1"/>
@@ -17672,7 +17877,7 @@
       <c r="Q225" s="1"/>
       <c r="R225" s="1"/>
       <c r="S225" s="1"/>
-      <c r="T225" s="1"/>
+      <c r="T225" s="33"/>
       <c r="U225" s="1"/>
       <c r="V225" s="1"/>
       <c r="W225" s="1"/>
@@ -17726,7 +17931,7 @@
       <c r="Q226" s="1"/>
       <c r="R226" s="1"/>
       <c r="S226" s="1"/>
-      <c r="T226" s="1"/>
+      <c r="T226" s="33"/>
       <c r="U226" s="1"/>
       <c r="V226" s="1"/>
       <c r="W226" s="1"/>
@@ -17780,7 +17985,7 @@
       <c r="Q227" s="1"/>
       <c r="R227" s="1"/>
       <c r="S227" s="1"/>
-      <c r="T227" s="1"/>
+      <c r="T227" s="33"/>
       <c r="U227" s="1"/>
       <c r="V227" s="1"/>
       <c r="W227" s="1"/>
@@ -17834,7 +18039,7 @@
       <c r="Q228" s="1"/>
       <c r="R228" s="1"/>
       <c r="S228" s="1"/>
-      <c r="T228" s="1"/>
+      <c r="T228" s="33"/>
       <c r="U228" s="1"/>
       <c r="V228" s="1"/>
       <c r="W228" s="1"/>
@@ -17888,7 +18093,7 @@
       <c r="Q229" s="1"/>
       <c r="R229" s="1"/>
       <c r="S229" s="1"/>
-      <c r="T229" s="1"/>
+      <c r="T229" s="33"/>
       <c r="U229" s="1"/>
       <c r="V229" s="1"/>
       <c r="W229" s="1"/>
@@ -17942,7 +18147,7 @@
       <c r="Q230" s="1"/>
       <c r="R230" s="1"/>
       <c r="S230" s="1"/>
-      <c r="T230" s="1"/>
+      <c r="T230" s="33"/>
       <c r="U230" s="1"/>
       <c r="V230" s="1"/>
       <c r="W230" s="1"/>
@@ -17996,7 +18201,7 @@
       <c r="Q231" s="1"/>
       <c r="R231" s="1"/>
       <c r="S231" s="1"/>
-      <c r="T231" s="1"/>
+      <c r="T231" s="33"/>
       <c r="U231" s="1"/>
       <c r="V231" s="1"/>
       <c r="W231" s="1"/>
@@ -18050,7 +18255,7 @@
       <c r="Q232" s="1"/>
       <c r="R232" s="1"/>
       <c r="S232" s="1"/>
-      <c r="T232" s="1"/>
+      <c r="T232" s="33"/>
       <c r="U232" s="1"/>
       <c r="V232" s="1"/>
       <c r="W232" s="1"/>
@@ -18104,7 +18309,7 @@
       <c r="Q233" s="1"/>
       <c r="R233" s="1"/>
       <c r="S233" s="1"/>
-      <c r="T233" s="1"/>
+      <c r="T233" s="33"/>
       <c r="U233" s="1"/>
       <c r="V233" s="1"/>
       <c r="W233" s="1"/>
@@ -18158,7 +18363,7 @@
       <c r="Q234" s="1"/>
       <c r="R234" s="1"/>
       <c r="S234" s="1"/>
-      <c r="T234" s="1"/>
+      <c r="T234" s="33"/>
       <c r="U234" s="1"/>
       <c r="V234" s="1"/>
       <c r="W234" s="1"/>
@@ -18212,7 +18417,7 @@
       <c r="Q235" s="1"/>
       <c r="R235" s="1"/>
       <c r="S235" s="1"/>
-      <c r="T235" s="1"/>
+      <c r="T235" s="33"/>
       <c r="U235" s="1"/>
       <c r="V235" s="1"/>
       <c r="W235" s="1"/>
@@ -18266,7 +18471,7 @@
       <c r="Q236" s="1"/>
       <c r="R236" s="1"/>
       <c r="S236" s="1"/>
-      <c r="T236" s="1"/>
+      <c r="T236" s="33"/>
       <c r="U236" s="1"/>
       <c r="V236" s="1"/>
       <c r="W236" s="1"/>
@@ -18320,7 +18525,7 @@
       <c r="Q237" s="1"/>
       <c r="R237" s="1"/>
       <c r="S237" s="1"/>
-      <c r="T237" s="1"/>
+      <c r="T237" s="33"/>
       <c r="U237" s="1"/>
       <c r="V237" s="1"/>
       <c r="W237" s="1"/>
@@ -18374,7 +18579,7 @@
       <c r="Q238" s="1"/>
       <c r="R238" s="1"/>
       <c r="S238" s="1"/>
-      <c r="T238" s="1"/>
+      <c r="T238" s="33"/>
       <c r="U238" s="1"/>
       <c r="V238" s="1"/>
       <c r="W238" s="1"/>
@@ -18428,7 +18633,7 @@
       <c r="Q239" s="1"/>
       <c r="R239" s="1"/>
       <c r="S239" s="1"/>
-      <c r="T239" s="1"/>
+      <c r="T239" s="33"/>
       <c r="U239" s="1"/>
       <c r="V239" s="1"/>
       <c r="W239" s="1"/>
@@ -18482,7 +18687,7 @@
       <c r="Q240" s="1"/>
       <c r="R240" s="1"/>
       <c r="S240" s="1"/>
-      <c r="T240" s="1"/>
+      <c r="T240" s="33"/>
       <c r="U240" s="1"/>
       <c r="V240" s="1"/>
       <c r="W240" s="1"/>
@@ -18536,7 +18741,7 @@
       <c r="Q241" s="1"/>
       <c r="R241" s="1"/>
       <c r="S241" s="1"/>
-      <c r="T241" s="1"/>
+      <c r="T241" s="33"/>
       <c r="U241" s="1"/>
       <c r="V241" s="1"/>
       <c r="W241" s="1"/>
@@ -18590,7 +18795,7 @@
       <c r="Q242" s="1"/>
       <c r="R242" s="1"/>
       <c r="S242" s="1"/>
-      <c r="T242" s="1"/>
+      <c r="T242" s="33"/>
       <c r="U242" s="1"/>
       <c r="V242" s="1"/>
       <c r="W242" s="1"/>
@@ -18644,7 +18849,7 @@
       <c r="Q243" s="1"/>
       <c r="R243" s="1"/>
       <c r="S243" s="1"/>
-      <c r="T243" s="1"/>
+      <c r="T243" s="33"/>
       <c r="U243" s="1"/>
       <c r="V243" s="1"/>
       <c r="W243" s="1"/>
@@ -18698,7 +18903,7 @@
       <c r="Q244" s="1"/>
       <c r="R244" s="1"/>
       <c r="S244" s="1"/>
-      <c r="T244" s="1"/>
+      <c r="T244" s="33"/>
       <c r="U244" s="1"/>
       <c r="V244" s="1"/>
       <c r="W244" s="1"/>
@@ -18752,7 +18957,7 @@
       <c r="Q245" s="1"/>
       <c r="R245" s="1"/>
       <c r="S245" s="1"/>
-      <c r="T245" s="1"/>
+      <c r="T245" s="33"/>
       <c r="U245" s="1"/>
       <c r="V245" s="1"/>
       <c r="W245" s="1"/>
@@ -18806,7 +19011,7 @@
       <c r="Q246" s="1"/>
       <c r="R246" s="1"/>
       <c r="S246" s="1"/>
-      <c r="T246" s="1"/>
+      <c r="T246" s="33"/>
       <c r="U246" s="1"/>
       <c r="V246" s="1"/>
       <c r="W246" s="1"/>
@@ -18860,7 +19065,7 @@
       <c r="Q247" s="1"/>
       <c r="R247" s="1"/>
       <c r="S247" s="1"/>
-      <c r="T247" s="1"/>
+      <c r="T247" s="33"/>
       <c r="U247" s="1"/>
       <c r="V247" s="1"/>
       <c r="W247" s="1"/>
@@ -18914,7 +19119,7 @@
       <c r="Q248" s="1"/>
       <c r="R248" s="1"/>
       <c r="S248" s="1"/>
-      <c r="T248" s="1"/>
+      <c r="T248" s="33"/>
       <c r="U248" s="1"/>
       <c r="V248" s="1"/>
       <c r="W248" s="1"/>
@@ -18968,7 +19173,7 @@
       <c r="Q249" s="1"/>
       <c r="R249" s="1"/>
       <c r="S249" s="1"/>
-      <c r="T249" s="1"/>
+      <c r="T249" s="33"/>
       <c r="U249" s="1"/>
       <c r="V249" s="1"/>
       <c r="W249" s="1"/>
@@ -19022,7 +19227,7 @@
       <c r="Q250" s="1"/>
       <c r="R250" s="1"/>
       <c r="S250" s="1"/>
-      <c r="T250" s="1"/>
+      <c r="T250" s="33"/>
       <c r="U250" s="1"/>
       <c r="V250" s="1"/>
       <c r="W250" s="1"/>
@@ -19076,7 +19281,7 @@
       <c r="Q251" s="1"/>
       <c r="R251" s="1"/>
       <c r="S251" s="1"/>
-      <c r="T251" s="1"/>
+      <c r="T251" s="33"/>
       <c r="U251" s="1"/>
       <c r="V251" s="1"/>
       <c r="W251" s="1"/>
@@ -19130,7 +19335,7 @@
       <c r="Q252" s="1"/>
       <c r="R252" s="1"/>
       <c r="S252" s="1"/>
-      <c r="T252" s="1"/>
+      <c r="T252" s="33"/>
       <c r="U252" s="1"/>
       <c r="V252" s="1"/>
       <c r="W252" s="1"/>
@@ -19184,7 +19389,7 @@
       <c r="Q253" s="1"/>
       <c r="R253" s="1"/>
       <c r="S253" s="1"/>
-      <c r="T253" s="1"/>
+      <c r="T253" s="33"/>
       <c r="U253" s="1"/>
       <c r="V253" s="1"/>
       <c r="W253" s="1"/>
@@ -19238,7 +19443,7 @@
       <c r="Q254" s="1"/>
       <c r="R254" s="1"/>
       <c r="S254" s="1"/>
-      <c r="T254" s="1"/>
+      <c r="T254" s="33"/>
       <c r="U254" s="1"/>
       <c r="V254" s="1"/>
       <c r="W254" s="1"/>
@@ -19292,7 +19497,7 @@
       <c r="Q255" s="1"/>
       <c r="R255" s="1"/>
       <c r="S255" s="1"/>
-      <c r="T255" s="1"/>
+      <c r="T255" s="33"/>
       <c r="U255" s="1"/>
       <c r="V255" s="1"/>
       <c r="W255" s="1"/>
@@ -19346,7 +19551,7 @@
       <c r="Q256" s="1"/>
       <c r="R256" s="1"/>
       <c r="S256" s="1"/>
-      <c r="T256" s="1"/>
+      <c r="T256" s="33"/>
       <c r="U256" s="1"/>
       <c r="V256" s="1"/>
       <c r="W256" s="1"/>
@@ -19400,7 +19605,7 @@
       <c r="Q257" s="1"/>
       <c r="R257" s="1"/>
       <c r="S257" s="1"/>
-      <c r="T257" s="1"/>
+      <c r="T257" s="33"/>
       <c r="U257" s="1"/>
       <c r="V257" s="1"/>
       <c r="W257" s="1"/>
@@ -19454,7 +19659,7 @@
       <c r="Q258" s="1"/>
       <c r="R258" s="1"/>
       <c r="S258" s="1"/>
-      <c r="T258" s="1"/>
+      <c r="T258" s="33"/>
       <c r="U258" s="1"/>
       <c r="V258" s="1"/>
       <c r="W258" s="1"/>
@@ -19508,7 +19713,7 @@
       <c r="Q259" s="1"/>
       <c r="R259" s="1"/>
       <c r="S259" s="1"/>
-      <c r="T259" s="1"/>
+      <c r="T259" s="33"/>
       <c r="U259" s="1"/>
       <c r="V259" s="1"/>
       <c r="W259" s="1"/>
@@ -19562,7 +19767,7 @@
       <c r="Q260" s="1"/>
       <c r="R260" s="1"/>
       <c r="S260" s="1"/>
-      <c r="T260" s="1"/>
+      <c r="T260" s="33"/>
       <c r="U260" s="1"/>
       <c r="V260" s="1"/>
       <c r="W260" s="1"/>
@@ -19616,7 +19821,7 @@
       <c r="Q261" s="1"/>
       <c r="R261" s="1"/>
       <c r="S261" s="1"/>
-      <c r="T261" s="1"/>
+      <c r="T261" s="33"/>
       <c r="U261" s="1"/>
       <c r="V261" s="1"/>
       <c r="W261" s="1"/>
@@ -19670,7 +19875,7 @@
       <c r="Q262" s="1"/>
       <c r="R262" s="1"/>
       <c r="S262" s="1"/>
-      <c r="T262" s="1"/>
+      <c r="T262" s="33"/>
       <c r="U262" s="1"/>
       <c r="V262" s="1"/>
       <c r="W262" s="1"/>
@@ -19724,7 +19929,7 @@
       <c r="Q263" s="1"/>
       <c r="R263" s="1"/>
       <c r="S263" s="1"/>
-      <c r="T263" s="1"/>
+      <c r="T263" s="33"/>
       <c r="U263" s="1"/>
       <c r="V263" s="1"/>
       <c r="W263" s="1"/>
@@ -19778,7 +19983,7 @@
       <c r="Q264" s="1"/>
       <c r="R264" s="1"/>
       <c r="S264" s="1"/>
-      <c r="T264" s="1"/>
+      <c r="T264" s="33"/>
       <c r="U264" s="1"/>
       <c r="V264" s="1"/>
       <c r="W264" s="1"/>
@@ -19832,7 +20037,7 @@
       <c r="Q265" s="1"/>
       <c r="R265" s="1"/>
       <c r="S265" s="1"/>
-      <c r="T265" s="1"/>
+      <c r="T265" s="33"/>
       <c r="U265" s="1"/>
       <c r="V265" s="1"/>
       <c r="W265" s="1"/>
@@ -19886,7 +20091,7 @@
       <c r="Q266" s="1"/>
       <c r="R266" s="1"/>
       <c r="S266" s="1"/>
-      <c r="T266" s="1"/>
+      <c r="T266" s="33"/>
       <c r="U266" s="1"/>
       <c r="V266" s="1"/>
       <c r="W266" s="1"/>
@@ -19940,7 +20145,7 @@
       <c r="Q267" s="1"/>
       <c r="R267" s="1"/>
       <c r="S267" s="1"/>
-      <c r="T267" s="1"/>
+      <c r="T267" s="33"/>
       <c r="U267" s="1"/>
       <c r="V267" s="1"/>
       <c r="W267" s="1"/>
@@ -19994,7 +20199,7 @@
       <c r="Q268" s="1"/>
       <c r="R268" s="1"/>
       <c r="S268" s="1"/>
-      <c r="T268" s="1"/>
+      <c r="T268" s="33"/>
       <c r="U268" s="1"/>
       <c r="V268" s="1"/>
       <c r="W268" s="1"/>
@@ -20048,7 +20253,7 @@
       <c r="Q269" s="1"/>
       <c r="R269" s="1"/>
       <c r="S269" s="1"/>
-      <c r="T269" s="1"/>
+      <c r="T269" s="33"/>
       <c r="U269" s="1"/>
       <c r="V269" s="1"/>
       <c r="W269" s="1"/>
@@ -20102,7 +20307,7 @@
       <c r="Q270" s="1"/>
       <c r="R270" s="1"/>
       <c r="S270" s="1"/>
-      <c r="T270" s="1"/>
+      <c r="T270" s="33"/>
       <c r="U270" s="1"/>
       <c r="V270" s="1"/>
       <c r="W270" s="1"/>
@@ -20156,7 +20361,7 @@
       <c r="Q271" s="1"/>
       <c r="R271" s="1"/>
       <c r="S271" s="1"/>
-      <c r="T271" s="1"/>
+      <c r="T271" s="33"/>
       <c r="U271" s="1"/>
       <c r="V271" s="1"/>
       <c r="W271" s="1"/>
@@ -20210,7 +20415,7 @@
       <c r="Q272" s="1"/>
       <c r="R272" s="1"/>
       <c r="S272" s="1"/>
-      <c r="T272" s="1"/>
+      <c r="T272" s="33"/>
       <c r="U272" s="1"/>
       <c r="V272" s="1"/>
       <c r="W272" s="1"/>
@@ -20264,7 +20469,7 @@
       <c r="Q273" s="1"/>
       <c r="R273" s="1"/>
       <c r="S273" s="1"/>
-      <c r="T273" s="1"/>
+      <c r="T273" s="33"/>
       <c r="U273" s="1"/>
       <c r="V273" s="1"/>
       <c r="W273" s="1"/>
@@ -20318,7 +20523,7 @@
       <c r="Q274" s="1"/>
       <c r="R274" s="1"/>
       <c r="S274" s="1"/>
-      <c r="T274" s="1"/>
+      <c r="T274" s="33"/>
       <c r="U274" s="1"/>
       <c r="V274" s="1"/>
       <c r="W274" s="1"/>
@@ -20372,7 +20577,7 @@
       <c r="Q275" s="1"/>
       <c r="R275" s="1"/>
       <c r="S275" s="1"/>
-      <c r="T275" s="1"/>
+      <c r="T275" s="33"/>
       <c r="U275" s="1"/>
       <c r="V275" s="1"/>
       <c r="W275" s="1"/>
@@ -20426,7 +20631,7 @@
       <c r="Q276" s="1"/>
       <c r="R276" s="1"/>
       <c r="S276" s="1"/>
-      <c r="T276" s="1"/>
+      <c r="T276" s="33"/>
       <c r="U276" s="1"/>
       <c r="V276" s="1"/>
       <c r="W276" s="1"/>
@@ -20480,7 +20685,7 @@
       <c r="Q277" s="1"/>
       <c r="R277" s="1"/>
       <c r="S277" s="1"/>
-      <c r="T277" s="1"/>
+      <c r="T277" s="33"/>
       <c r="U277" s="1"/>
       <c r="V277" s="1"/>
       <c r="W277" s="1"/>
@@ -20534,7 +20739,7 @@
       <c r="Q278" s="1"/>
       <c r="R278" s="1"/>
       <c r="S278" s="1"/>
-      <c r="T278" s="1"/>
+      <c r="T278" s="33"/>
       <c r="U278" s="1"/>
       <c r="V278" s="1"/>
       <c r="W278" s="1"/>
@@ -20588,7 +20793,7 @@
       <c r="Q279" s="1"/>
       <c r="R279" s="1"/>
       <c r="S279" s="1"/>
-      <c r="T279" s="1"/>
+      <c r="T279" s="33"/>
       <c r="U279" s="1"/>
       <c r="V279" s="1"/>
       <c r="W279" s="1"/>
@@ -20642,7 +20847,7 @@
       <c r="Q280" s="1"/>
       <c r="R280" s="1"/>
       <c r="S280" s="1"/>
-      <c r="T280" s="1"/>
+      <c r="T280" s="33"/>
       <c r="U280" s="1"/>
       <c r="V280" s="1"/>
       <c r="W280" s="1"/>
@@ -20696,7 +20901,7 @@
       <c r="Q281" s="1"/>
       <c r="R281" s="1"/>
       <c r="S281" s="1"/>
-      <c r="T281" s="1"/>
+      <c r="T281" s="33"/>
       <c r="U281" s="1"/>
       <c r="V281" s="1"/>
       <c r="W281" s="1"/>
@@ -20750,7 +20955,7 @@
       <c r="Q282" s="1"/>
       <c r="R282" s="1"/>
       <c r="S282" s="1"/>
-      <c r="T282" s="1"/>
+      <c r="T282" s="33"/>
       <c r="U282" s="1"/>
       <c r="V282" s="1"/>
       <c r="W282" s="1"/>
@@ -20804,7 +21009,7 @@
       <c r="Q283" s="1"/>
       <c r="R283" s="1"/>
       <c r="S283" s="1"/>
-      <c r="T283" s="1"/>
+      <c r="T283" s="33"/>
       <c r="U283" s="1"/>
       <c r="V283" s="1"/>
       <c r="W283" s="1"/>
@@ -20858,7 +21063,7 @@
       <c r="Q284" s="1"/>
       <c r="R284" s="1"/>
       <c r="S284" s="1"/>
-      <c r="T284" s="1"/>
+      <c r="T284" s="33"/>
       <c r="U284" s="1"/>
       <c r="V284" s="1"/>
       <c r="W284" s="1"/>
@@ -20912,7 +21117,7 @@
       <c r="Q285" s="1"/>
       <c r="R285" s="1"/>
       <c r="S285" s="1"/>
-      <c r="T285" s="1"/>
+      <c r="T285" s="33"/>
       <c r="U285" s="1"/>
       <c r="V285" s="1"/>
       <c r="W285" s="1"/>
@@ -20966,7 +21171,7 @@
       <c r="Q286" s="1"/>
       <c r="R286" s="1"/>
       <c r="S286" s="1"/>
-      <c r="T286" s="1"/>
+      <c r="T286" s="33"/>
       <c r="U286" s="1"/>
       <c r="V286" s="1"/>
       <c r="W286" s="1"/>
@@ -21020,7 +21225,7 @@
       <c r="Q287" s="1"/>
       <c r="R287" s="1"/>
       <c r="S287" s="1"/>
-      <c r="T287" s="1"/>
+      <c r="T287" s="33"/>
       <c r="U287" s="1"/>
       <c r="V287" s="1"/>
       <c r="W287" s="1"/>
@@ -21074,7 +21279,7 @@
       <c r="Q288" s="1"/>
       <c r="R288" s="1"/>
       <c r="S288" s="1"/>
-      <c r="T288" s="1"/>
+      <c r="T288" s="33"/>
       <c r="U288" s="1"/>
       <c r="V288" s="1"/>
       <c r="W288" s="1"/>
@@ -21128,7 +21333,7 @@
       <c r="Q289" s="1"/>
       <c r="R289" s="1"/>
       <c r="S289" s="1"/>
-      <c r="T289" s="1"/>
+      <c r="T289" s="33"/>
       <c r="U289" s="1"/>
       <c r="V289" s="1"/>
       <c r="W289" s="1"/>
@@ -21182,7 +21387,7 @@
       <c r="Q290" s="1"/>
       <c r="R290" s="1"/>
       <c r="S290" s="1"/>
-      <c r="T290" s="1"/>
+      <c r="T290" s="33"/>
       <c r="U290" s="1"/>
       <c r="V290" s="1"/>
       <c r="W290" s="1"/>
@@ -21236,7 +21441,7 @@
       <c r="Q291" s="1"/>
       <c r="R291" s="1"/>
       <c r="S291" s="1"/>
-      <c r="T291" s="1"/>
+      <c r="T291" s="33"/>
       <c r="U291" s="1"/>
       <c r="V291" s="1"/>
       <c r="W291" s="1"/>
@@ -21290,7 +21495,7 @@
       <c r="Q292" s="1"/>
       <c r="R292" s="1"/>
       <c r="S292" s="1"/>
-      <c r="T292" s="1"/>
+      <c r="T292" s="33"/>
       <c r="U292" s="1"/>
       <c r="V292" s="1"/>
       <c r="W292" s="1"/>
@@ -21344,7 +21549,7 @@
       <c r="Q293" s="1"/>
       <c r="R293" s="1"/>
       <c r="S293" s="1"/>
-      <c r="T293" s="1"/>
+      <c r="T293" s="33"/>
       <c r="U293" s="1"/>
       <c r="V293" s="1"/>
       <c r="W293" s="1"/>
@@ -21398,7 +21603,7 @@
       <c r="Q294" s="1"/>
       <c r="R294" s="1"/>
       <c r="S294" s="1"/>
-      <c r="T294" s="1"/>
+      <c r="T294" s="33"/>
       <c r="U294" s="1"/>
       <c r="V294" s="1"/>
       <c r="W294" s="1"/>
@@ -21452,7 +21657,7 @@
       <c r="Q295" s="1"/>
       <c r="R295" s="1"/>
       <c r="S295" s="1"/>
-      <c r="T295" s="1"/>
+      <c r="T295" s="33"/>
       <c r="U295" s="1"/>
       <c r="V295" s="1"/>
       <c r="W295" s="1"/>
@@ -21506,7 +21711,7 @@
       <c r="Q296" s="1"/>
       <c r="R296" s="1"/>
       <c r="S296" s="1"/>
-      <c r="T296" s="1"/>
+      <c r="T296" s="33"/>
       <c r="U296" s="1"/>
       <c r="V296" s="1"/>
       <c r="W296" s="1"/>
@@ -21560,7 +21765,7 @@
       <c r="Q297" s="1"/>
       <c r="R297" s="1"/>
       <c r="S297" s="1"/>
-      <c r="T297" s="1"/>
+      <c r="T297" s="33"/>
       <c r="U297" s="1"/>
       <c r="V297" s="1"/>
       <c r="W297" s="1"/>
@@ -21614,7 +21819,7 @@
       <c r="Q298" s="1"/>
       <c r="R298" s="1"/>
       <c r="S298" s="1"/>
-      <c r="T298" s="1"/>
+      <c r="T298" s="33"/>
       <c r="U298" s="1"/>
       <c r="V298" s="1"/>
       <c r="W298" s="1"/>
@@ -21668,7 +21873,7 @@
       <c r="Q299" s="1"/>
       <c r="R299" s="1"/>
       <c r="S299" s="1"/>
-      <c r="T299" s="1"/>
+      <c r="T299" s="33"/>
       <c r="U299" s="1"/>
       <c r="V299" s="1"/>
       <c r="W299" s="1"/>
@@ -21722,7 +21927,7 @@
       <c r="Q300" s="1"/>
       <c r="R300" s="1"/>
       <c r="S300" s="1"/>
-      <c r="T300" s="1"/>
+      <c r="T300" s="33"/>
       <c r="U300" s="1"/>
       <c r="V300" s="1"/>
       <c r="W300" s="1"/>
@@ -21776,7 +21981,7 @@
       <c r="Q301" s="1"/>
       <c r="R301" s="1"/>
       <c r="S301" s="1"/>
-      <c r="T301" s="1"/>
+      <c r="T301" s="33"/>
       <c r="U301" s="1"/>
       <c r="V301" s="1"/>
       <c r="W301" s="1"/>
@@ -21830,7 +22035,7 @@
       <c r="Q302" s="1"/>
       <c r="R302" s="1"/>
       <c r="S302" s="1"/>
-      <c r="T302" s="1"/>
+      <c r="T302" s="33"/>
       <c r="U302" s="1"/>
       <c r="V302" s="1"/>
       <c r="W302" s="1"/>
@@ -21884,7 +22089,7 @@
       <c r="Q303" s="1"/>
       <c r="R303" s="1"/>
       <c r="S303" s="1"/>
-      <c r="T303" s="1"/>
+      <c r="T303" s="33"/>
       <c r="U303" s="1"/>
       <c r="V303" s="1"/>
       <c r="W303" s="1"/>
@@ -21938,7 +22143,7 @@
       <c r="Q304" s="1"/>
       <c r="R304" s="1"/>
       <c r="S304" s="1"/>
-      <c r="T304" s="1"/>
+      <c r="T304" s="33"/>
       <c r="U304" s="1"/>
       <c r="V304" s="1"/>
       <c r="W304" s="1"/>
@@ -21992,7 +22197,7 @@
       <c r="Q305" s="1"/>
       <c r="R305" s="1"/>
       <c r="S305" s="1"/>
-      <c r="T305" s="1"/>
+      <c r="T305" s="33"/>
       <c r="U305" s="1"/>
       <c r="V305" s="1"/>
       <c r="W305" s="1"/>
@@ -22046,7 +22251,7 @@
       <c r="Q306" s="1"/>
       <c r="R306" s="1"/>
       <c r="S306" s="1"/>
-      <c r="T306" s="1"/>
+      <c r="T306" s="33"/>
       <c r="U306" s="1"/>
       <c r="V306" s="1"/>
       <c r="W306" s="1"/>
@@ -22100,7 +22305,7 @@
       <c r="Q307" s="1"/>
       <c r="R307" s="1"/>
       <c r="S307" s="1"/>
-      <c r="T307" s="1"/>
+      <c r="T307" s="33"/>
       <c r="U307" s="1"/>
       <c r="V307" s="1"/>
       <c r="W307" s="1"/>
@@ -22154,7 +22359,7 @@
       <c r="Q308" s="1"/>
       <c r="R308" s="1"/>
       <c r="S308" s="1"/>
-      <c r="T308" s="1"/>
+      <c r="T308" s="33"/>
       <c r="U308" s="1"/>
       <c r="V308" s="1"/>
       <c r="W308" s="1"/>
@@ -22208,7 +22413,7 @@
       <c r="Q309" s="1"/>
       <c r="R309" s="1"/>
       <c r="S309" s="1"/>
-      <c r="T309" s="1"/>
+      <c r="T309" s="33"/>
       <c r="U309" s="1"/>
       <c r="V309" s="1"/>
       <c r="W309" s="1"/>
@@ -22262,7 +22467,7 @@
       <c r="Q310" s="1"/>
       <c r="R310" s="1"/>
       <c r="S310" s="1"/>
-      <c r="T310" s="1"/>
+      <c r="T310" s="33"/>
       <c r="U310" s="1"/>
       <c r="V310" s="1"/>
       <c r="W310" s="1"/>
@@ -22316,7 +22521,7 @@
       <c r="Q311" s="1"/>
       <c r="R311" s="1"/>
       <c r="S311" s="1"/>
-      <c r="T311" s="1"/>
+      <c r="T311" s="33"/>
       <c r="U311" s="1"/>
       <c r="V311" s="1"/>
       <c r="W311" s="1"/>
@@ -22370,7 +22575,7 @@
       <c r="Q312" s="1"/>
       <c r="R312" s="1"/>
       <c r="S312" s="1"/>
-      <c r="T312" s="1"/>
+      <c r="T312" s="33"/>
       <c r="U312" s="1"/>
       <c r="V312" s="1"/>
       <c r="W312" s="1"/>
@@ -22424,7 +22629,7 @@
       <c r="Q313" s="1"/>
       <c r="R313" s="1"/>
       <c r="S313" s="1"/>
-      <c r="T313" s="1"/>
+      <c r="T313" s="33"/>
       <c r="U313" s="1"/>
       <c r="V313" s="1"/>
       <c r="W313" s="1"/>
@@ -22478,7 +22683,7 @@
       <c r="Q314" s="1"/>
       <c r="R314" s="1"/>
       <c r="S314" s="1"/>
-      <c r="T314" s="1"/>
+      <c r="T314" s="33"/>
       <c r="U314" s="1"/>
       <c r="V314" s="1"/>
       <c r="W314" s="1"/>
@@ -22532,7 +22737,7 @@
       <c r="Q315" s="1"/>
       <c r="R315" s="1"/>
       <c r="S315" s="1"/>
-      <c r="T315" s="1"/>
+      <c r="T315" s="33"/>
       <c r="U315" s="1"/>
       <c r="V315" s="1"/>
       <c r="W315" s="1"/>
@@ -22586,7 +22791,7 @@
       <c r="Q316" s="1"/>
       <c r="R316" s="1"/>
       <c r="S316" s="1"/>
-      <c r="T316" s="1"/>
+      <c r="T316" s="33"/>
       <c r="U316" s="1"/>
       <c r="V316" s="1"/>
       <c r="W316" s="1"/>
@@ -22640,7 +22845,7 @@
       <c r="Q317" s="1"/>
       <c r="R317" s="1"/>
       <c r="S317" s="1"/>
-      <c r="T317" s="1"/>
+      <c r="T317" s="33"/>
       <c r="U317" s="1"/>
       <c r="V317" s="1"/>
       <c r="W317" s="1"/>
@@ -22694,7 +22899,7 @@
       <c r="Q318" s="1"/>
       <c r="R318" s="1"/>
       <c r="S318" s="1"/>
-      <c r="T318" s="1"/>
+      <c r="T318" s="33"/>
       <c r="U318" s="1"/>
       <c r="V318" s="1"/>
       <c r="W318" s="1"/>
@@ -22748,7 +22953,7 @@
       <c r="Q319" s="1"/>
       <c r="R319" s="1"/>
       <c r="S319" s="1"/>
-      <c r="T319" s="1"/>
+      <c r="T319" s="33"/>
       <c r="U319" s="1"/>
       <c r="V319" s="1"/>
       <c r="W319" s="1"/>
@@ -22802,7 +23007,7 @@
       <c r="Q320" s="1"/>
       <c r="R320" s="1"/>
       <c r="S320" s="1"/>
-      <c r="T320" s="1"/>
+      <c r="T320" s="33"/>
       <c r="U320" s="1"/>
       <c r="V320" s="1"/>
       <c r="W320" s="1"/>
@@ -22856,7 +23061,7 @@
       <c r="Q321" s="1"/>
       <c r="R321" s="1"/>
       <c r="S321" s="1"/>
-      <c r="T321" s="1"/>
+      <c r="T321" s="33"/>
       <c r="U321" s="1"/>
       <c r="V321" s="1"/>
       <c r="W321" s="1"/>
@@ -22910,7 +23115,7 @@
       <c r="Q322" s="1"/>
       <c r="R322" s="1"/>
       <c r="S322" s="1"/>
-      <c r="T322" s="1"/>
+      <c r="T322" s="33"/>
       <c r="U322" s="1"/>
       <c r="V322" s="1"/>
       <c r="W322" s="1"/>
@@ -22964,7 +23169,7 @@
       <c r="Q323" s="1"/>
       <c r="R323" s="1"/>
       <c r="S323" s="1"/>
-      <c r="T323" s="1"/>
+      <c r="T323" s="33"/>
       <c r="U323" s="1"/>
       <c r="V323" s="1"/>
       <c r="W323" s="1"/>
@@ -23018,7 +23223,7 @@
       <c r="Q324" s="1"/>
       <c r="R324" s="1"/>
       <c r="S324" s="1"/>
-      <c r="T324" s="1"/>
+      <c r="T324" s="33"/>
       <c r="U324" s="1"/>
       <c r="V324" s="1"/>
       <c r="W324" s="1"/>
@@ -23072,7 +23277,7 @@
       <c r="Q325" s="1"/>
       <c r="R325" s="1"/>
       <c r="S325" s="1"/>
-      <c r="T325" s="1"/>
+      <c r="T325" s="33"/>
       <c r="U325" s="1"/>
       <c r="V325" s="1"/>
       <c r="W325" s="1"/>
@@ -23126,7 +23331,7 @@
       <c r="Q326" s="1"/>
       <c r="R326" s="1"/>
       <c r="S326" s="1"/>
-      <c r="T326" s="1"/>
+      <c r="T326" s="33"/>
       <c r="U326" s="1"/>
       <c r="V326" s="1"/>
       <c r="W326" s="1"/>
@@ -23180,7 +23385,7 @@
       <c r="Q327" s="1"/>
       <c r="R327" s="1"/>
       <c r="S327" s="1"/>
-      <c r="T327" s="1"/>
+      <c r="T327" s="33"/>
       <c r="U327" s="1"/>
       <c r="V327" s="1"/>
       <c r="W327" s="1"/>
@@ -23234,7 +23439,7 @@
       <c r="Q328" s="1"/>
       <c r="R328" s="1"/>
       <c r="S328" s="1"/>
-      <c r="T328" s="1"/>
+      <c r="T328" s="33"/>
       <c r="U328" s="1"/>
       <c r="V328" s="1"/>
       <c r="W328" s="1"/>
@@ -23288,7 +23493,7 @@
       <c r="Q329" s="1"/>
       <c r="R329" s="1"/>
       <c r="S329" s="1"/>
-      <c r="T329" s="1"/>
+      <c r="T329" s="33"/>
       <c r="U329" s="1"/>
       <c r="V329" s="1"/>
       <c r="W329" s="1"/>
@@ -23342,7 +23547,7 @@
       <c r="Q330" s="1"/>
       <c r="R330" s="1"/>
       <c r="S330" s="1"/>
-      <c r="T330" s="1"/>
+      <c r="T330" s="33"/>
       <c r="U330" s="1"/>
       <c r="V330" s="1"/>
       <c r="W330" s="1"/>
@@ -23396,7 +23601,7 @@
       <c r="Q331" s="1"/>
       <c r="R331" s="1"/>
       <c r="S331" s="1"/>
-      <c r="T331" s="1"/>
+      <c r="T331" s="33"/>
       <c r="U331" s="1"/>
       <c r="V331" s="1"/>
       <c r="W331" s="1"/>
@@ -23450,7 +23655,7 @@
       <c r="Q332" s="1"/>
       <c r="R332" s="1"/>
       <c r="S332" s="1"/>
-      <c r="T332" s="1"/>
+      <c r="T332" s="33"/>
       <c r="U332" s="1"/>
       <c r="V332" s="1"/>
       <c r="W332" s="1"/>
@@ -23504,7 +23709,7 @@
       <c r="Q333" s="1"/>
       <c r="R333" s="1"/>
       <c r="S333" s="1"/>
-      <c r="T333" s="1"/>
+      <c r="T333" s="33"/>
       <c r="U333" s="1"/>
       <c r="V333" s="1"/>
       <c r="W333" s="1"/>
@@ -23558,7 +23763,7 @@
       <c r="Q334" s="1"/>
       <c r="R334" s="1"/>
       <c r="S334" s="1"/>
-      <c r="T334" s="1"/>
+      <c r="T334" s="33"/>
       <c r="U334" s="1"/>
       <c r="V334" s="1"/>
       <c r="W334" s="1"/>
@@ -23612,7 +23817,7 @@
       <c r="Q335" s="1"/>
       <c r="R335" s="1"/>
       <c r="S335" s="1"/>
-      <c r="T335" s="1"/>
+      <c r="T335" s="33"/>
       <c r="U335" s="1"/>
       <c r="V335" s="1"/>
       <c r="W335" s="1"/>
@@ -23666,7 +23871,7 @@
       <c r="Q336" s="1"/>
       <c r="R336" s="1"/>
       <c r="S336" s="1"/>
-      <c r="T336" s="1"/>
+      <c r="T336" s="33"/>
       <c r="U336" s="1"/>
       <c r="V336" s="1"/>
       <c r="W336" s="1"/>
@@ -23720,7 +23925,7 @@
       <c r="Q337" s="1"/>
       <c r="R337" s="1"/>
       <c r="S337" s="1"/>
-      <c r="T337" s="1"/>
+      <c r="T337" s="33"/>
       <c r="U337" s="1"/>
       <c r="V337" s="1"/>
       <c r="W337" s="1"/>
@@ -23774,7 +23979,7 @@
       <c r="Q338" s="1"/>
       <c r="R338" s="1"/>
       <c r="S338" s="1"/>
-      <c r="T338" s="1"/>
+      <c r="T338" s="33"/>
       <c r="U338" s="1"/>
       <c r="V338" s="1"/>
       <c r="W338" s="1"/>
@@ -23828,7 +24033,7 @@
       <c r="Q339" s="1"/>
       <c r="R339" s="1"/>
       <c r="S339" s="1"/>
-      <c r="T339" s="1"/>
+      <c r="T339" s="33"/>
       <c r="U339" s="1"/>
       <c r="V339" s="1"/>
       <c r="W339" s="1"/>
@@ -23882,7 +24087,7 @@
       <c r="Q340" s="1"/>
       <c r="R340" s="1"/>
       <c r="S340" s="1"/>
-      <c r="T340" s="1"/>
+      <c r="T340" s="33"/>
       <c r="U340" s="1"/>
       <c r="V340" s="1"/>
       <c r="W340" s="1"/>
@@ -23936,7 +24141,7 @@
       <c r="Q341" s="1"/>
       <c r="R341" s="1"/>
       <c r="S341" s="1"/>
-      <c r="T341" s="1"/>
+      <c r="T341" s="33"/>
       <c r="U341" s="1"/>
       <c r="V341" s="1"/>
       <c r="W341" s="1"/>
@@ -23990,7 +24195,7 @@
       <c r="Q342" s="1"/>
       <c r="R342" s="1"/>
       <c r="S342" s="1"/>
-      <c r="T342" s="1"/>
+      <c r="T342" s="33"/>
       <c r="U342" s="1"/>
       <c r="V342" s="1"/>
       <c r="W342" s="1"/>
@@ -24044,7 +24249,7 @@
       <c r="Q343" s="1"/>
       <c r="R343" s="1"/>
       <c r="S343" s="1"/>
-      <c r="T343" s="1"/>
+      <c r="T343" s="33"/>
       <c r="U343" s="1"/>
       <c r="V343" s="1"/>
       <c r="W343" s="1"/>
@@ -24098,7 +24303,7 @@
       <c r="Q344" s="1"/>
       <c r="R344" s="1"/>
       <c r="S344" s="1"/>
-      <c r="T344" s="1"/>
+      <c r="T344" s="33"/>
       <c r="U344" s="1"/>
       <c r="V344" s="1"/>
       <c r="W344" s="1"/>
@@ -24152,7 +24357,7 @@
       <c r="Q345" s="1"/>
       <c r="R345" s="1"/>
       <c r="S345" s="1"/>
-      <c r="T345" s="1"/>
+      <c r="T345" s="33"/>
       <c r="U345" s="1"/>
       <c r="V345" s="1"/>
       <c r="W345" s="1"/>
@@ -24206,7 +24411,7 @@
       <c r="Q346" s="1"/>
       <c r="R346" s="1"/>
       <c r="S346" s="1"/>
-      <c r="T346" s="1"/>
+      <c r="T346" s="33"/>
       <c r="U346" s="1"/>
       <c r="V346" s="1"/>
       <c r="W346" s="1"/>
@@ -24260,7 +24465,7 @@
       <c r="Q347" s="1"/>
       <c r="R347" s="1"/>
       <c r="S347" s="1"/>
-      <c r="T347" s="1"/>
+      <c r="T347" s="33"/>
       <c r="U347" s="1"/>
       <c r="V347" s="1"/>
       <c r="W347" s="1"/>
@@ -24314,7 +24519,7 @@
       <c r="Q348" s="1"/>
       <c r="R348" s="1"/>
       <c r="S348" s="1"/>
-      <c r="T348" s="1"/>
+      <c r="T348" s="33"/>
       <c r="U348" s="1"/>
       <c r="V348" s="1"/>
       <c r="W348" s="1"/>
@@ -24368,7 +24573,7 @@
       <c r="Q349" s="1"/>
       <c r="R349" s="1"/>
       <c r="S349" s="1"/>
-      <c r="T349" s="1"/>
+      <c r="T349" s="33"/>
       <c r="U349" s="1"/>
       <c r="V349" s="1"/>
       <c r="W349" s="1"/>
@@ -24422,7 +24627,7 @@
       <c r="Q350" s="1"/>
       <c r="R350" s="1"/>
       <c r="S350" s="1"/>
-      <c r="T350" s="1"/>
+      <c r="T350" s="33"/>
       <c r="U350" s="1"/>
       <c r="V350" s="1"/>
       <c r="W350" s="1"/>
@@ -24476,7 +24681,7 @@
       <c r="Q351" s="1"/>
       <c r="R351" s="1"/>
       <c r="S351" s="1"/>
-      <c r="T351" s="1"/>
+      <c r="T351" s="33"/>
       <c r="U351" s="1"/>
       <c r="V351" s="1"/>
       <c r="W351" s="1"/>
@@ -24530,7 +24735,7 @@
       <c r="Q352" s="1"/>
       <c r="R352" s="1"/>
       <c r="S352" s="1"/>
-      <c r="T352" s="1"/>
+      <c r="T352" s="33"/>
       <c r="U352" s="1"/>
       <c r="V352" s="1"/>
       <c r="W352" s="1"/>
@@ -24584,7 +24789,7 @@
       <c r="Q353" s="1"/>
       <c r="R353" s="1"/>
       <c r="S353" s="1"/>
-      <c r="T353" s="1"/>
+      <c r="T353" s="33"/>
       <c r="U353" s="1"/>
       <c r="V353" s="1"/>
       <c r="W353" s="1"/>
@@ -24638,7 +24843,7 @@
       <c r="Q354" s="1"/>
       <c r="R354" s="1"/>
       <c r="S354" s="1"/>
-      <c r="T354" s="1"/>
+      <c r="T354" s="33"/>
       <c r="U354" s="1"/>
       <c r="V354" s="1"/>
       <c r="W354" s="1"/>
@@ -24692,7 +24897,7 @@
       <c r="Q355" s="1"/>
       <c r="R355" s="1"/>
       <c r="S355" s="1"/>
-      <c r="T355" s="1"/>
+      <c r="T355" s="33"/>
       <c r="U355" s="1"/>
       <c r="V355" s="1"/>
       <c r="W355" s="1"/>
@@ -24746,7 +24951,7 @@
       <c r="Q356" s="1"/>
       <c r="R356" s="1"/>
       <c r="S356" s="1"/>
-      <c r="T356" s="1"/>
+      <c r="T356" s="33"/>
       <c r="U356" s="1"/>
       <c r="V356" s="1"/>
       <c r="W356" s="1"/>
@@ -24800,7 +25005,7 @@
       <c r="Q357" s="1"/>
       <c r="R357" s="1"/>
       <c r="S357" s="1"/>
-      <c r="T357" s="1"/>
+      <c r="T357" s="33"/>
       <c r="U357" s="1"/>
       <c r="V357" s="1"/>
       <c r="W357" s="1"/>
@@ -24854,7 +25059,7 @@
       <c r="Q358" s="1"/>
       <c r="R358" s="1"/>
       <c r="S358" s="1"/>
-      <c r="T358" s="1"/>
+      <c r="T358" s="33"/>
       <c r="U358" s="1"/>
       <c r="V358" s="1"/>
       <c r="W358" s="1"/>
@@ -24908,7 +25113,7 @@
       <c r="Q359" s="1"/>
       <c r="R359" s="1"/>
       <c r="S359" s="1"/>
-      <c r="T359" s="1"/>
+      <c r="T359" s="33"/>
       <c r="U359" s="1"/>
       <c r="V359" s="1"/>
       <c r="W359" s="1"/>
@@ -24962,7 +25167,7 @@
       <c r="Q360" s="1"/>
       <c r="R360" s="1"/>
       <c r="S360" s="1"/>
-      <c r="T360" s="1"/>
+      <c r="T360" s="33"/>
       <c r="U360" s="1"/>
       <c r="V360" s="1"/>
       <c r="W360" s="1"/>
@@ -25016,7 +25221,7 @@
       <c r="Q361" s="1"/>
       <c r="R361" s="1"/>
       <c r="S361" s="1"/>
-      <c r="T361" s="1"/>
+      <c r="T361" s="33"/>
       <c r="U361" s="1"/>
       <c r="V361" s="1"/>
       <c r="W361" s="1"/>
@@ -25070,7 +25275,7 @@
       <c r="Q362" s="1"/>
       <c r="R362" s="1"/>
       <c r="S362" s="1"/>
-      <c r="T362" s="1"/>
+      <c r="T362" s="33"/>
       <c r="U362" s="1"/>
       <c r="V362" s="1"/>
       <c r="W362" s="1"/>
@@ -25124,7 +25329,7 @@
       <c r="Q363" s="1"/>
       <c r="R363" s="1"/>
       <c r="S363" s="1"/>
-      <c r="T363" s="1"/>
+      <c r="T363" s="33"/>
       <c r="U363" s="1"/>
       <c r="V363" s="1"/>
       <c r="W363" s="1"/>
@@ -25178,7 +25383,7 @@
       <c r="Q364" s="1"/>
       <c r="R364" s="1"/>
       <c r="S364" s="1"/>
-      <c r="T364" s="1"/>
+      <c r="T364" s="33"/>
       <c r="U364" s="1"/>
       <c r="V364" s="1"/>
       <c r="W364" s="1"/>
@@ -25232,7 +25437,7 @@
       <c r="Q365" s="1"/>
       <c r="R365" s="1"/>
       <c r="S365" s="1"/>
-      <c r="T365" s="1"/>
+      <c r="T365" s="33"/>
       <c r="U365" s="1"/>
       <c r="V365" s="1"/>
       <c r="W365" s="1"/>
@@ -25286,7 +25491,7 @@
       <c r="Q366" s="1"/>
       <c r="R366" s="1"/>
       <c r="S366" s="1"/>
-      <c r="T366" s="1"/>
+      <c r="T366" s="33"/>
       <c r="U366" s="1"/>
       <c r="V366" s="1"/>
       <c r="W366" s="1"/>
@@ -25340,7 +25545,7 @@
       <c r="Q367" s="1"/>
       <c r="R367" s="1"/>
       <c r="S367" s="1"/>
-      <c r="T367" s="1"/>
+      <c r="T367" s="33"/>
       <c r="U367" s="1"/>
       <c r="V367" s="1"/>
       <c r="W367" s="1"/>
@@ -25394,7 +25599,7 @@
       <c r="Q368" s="1"/>
       <c r="R368" s="1"/>
       <c r="S368" s="1"/>
-      <c r="T368" s="1"/>
+      <c r="T368" s="33"/>
       <c r="U368" s="1"/>
       <c r="V368" s="1"/>
       <c r="W368" s="1"/>
@@ -25448,7 +25653,7 @@
       <c r="Q369" s="1"/>
       <c r="R369" s="1"/>
       <c r="S369" s="1"/>
-      <c r="T369" s="1"/>
+      <c r="T369" s="33"/>
       <c r="U369" s="1"/>
       <c r="V369" s="1"/>
       <c r="W369" s="1"/>
@@ -25502,7 +25707,7 @@
       <c r="Q370" s="1"/>
       <c r="R370" s="1"/>
       <c r="S370" s="1"/>
-      <c r="T370" s="1"/>
+      <c r="T370" s="33"/>
       <c r="U370" s="1"/>
       <c r="V370" s="1"/>
       <c r="W370" s="1"/>
@@ -25556,7 +25761,7 @@
       <c r="Q371" s="1"/>
       <c r="R371" s="1"/>
       <c r="S371" s="1"/>
-      <c r="T371" s="1"/>
+      <c r="T371" s="33"/>
       <c r="U371" s="1"/>
       <c r="V371" s="1"/>
       <c r="W371" s="1"/>
@@ -25610,7 +25815,7 @@
       <c r="Q372" s="1"/>
       <c r="R372" s="1"/>
       <c r="S372" s="1"/>
-      <c r="T372" s="1"/>
+      <c r="T372" s="33"/>
       <c r="U372" s="1"/>
       <c r="V372" s="1"/>
       <c r="W372" s="1"/>
@@ -25664,7 +25869,7 @@
       <c r="Q373" s="1"/>
       <c r="R373" s="1"/>
       <c r="S373" s="1"/>
-      <c r="T373" s="1"/>
+      <c r="T373" s="33"/>
       <c r="U373" s="1"/>
       <c r="V373" s="1"/>
       <c r="W373" s="1"/>
@@ -25718,7 +25923,7 @@
       <c r="Q374" s="1"/>
       <c r="R374" s="1"/>
       <c r="S374" s="1"/>
-      <c r="T374" s="1"/>
+      <c r="T374" s="33"/>
       <c r="U374" s="1"/>
       <c r="V374" s="1"/>
       <c r="W374" s="1"/>
@@ -25772,7 +25977,7 @@
       <c r="Q375" s="1"/>
       <c r="R375" s="1"/>
       <c r="S375" s="1"/>
-      <c r="T375" s="1"/>
+      <c r="T375" s="33"/>
       <c r="U375" s="1"/>
       <c r="V375" s="1"/>
       <c r="W375" s="1"/>
@@ -25826,7 +26031,7 @@
       <c r="Q376" s="1"/>
       <c r="R376" s="1"/>
       <c r="S376" s="1"/>
-      <c r="T376" s="1"/>
+      <c r="T376" s="33"/>
       <c r="U376" s="1"/>
       <c r="V376" s="1"/>
       <c r="W376" s="1"/>
@@ -25880,7 +26085,7 @@
       <c r="Q377" s="1"/>
       <c r="R377" s="1"/>
       <c r="S377" s="1"/>
-      <c r="T377" s="1"/>
+      <c r="T377" s="33"/>
       <c r="U377" s="1"/>
       <c r="V377" s="1"/>
       <c r="W377" s="1"/>
@@ -25934,7 +26139,7 @@
       <c r="Q378" s="1"/>
       <c r="R378" s="1"/>
       <c r="S378" s="1"/>
-      <c r="T378" s="1"/>
+      <c r="T378" s="33"/>
       <c r="U378" s="1"/>
       <c r="V378" s="1"/>
       <c r="W378" s="1"/>
@@ -25988,7 +26193,7 @@
       <c r="Q379" s="1"/>
       <c r="R379" s="1"/>
       <c r="S379" s="1"/>
-      <c r="T379" s="1"/>
+      <c r="T379" s="33"/>
       <c r="U379" s="1"/>
       <c r="V379" s="1"/>
       <c r="W379" s="1"/>
@@ -26042,7 +26247,7 @@
       <c r="Q380" s="1"/>
       <c r="R380" s="1"/>
       <c r="S380" s="1"/>
-      <c r="T380" s="1"/>
+      <c r="T380" s="33"/>
       <c r="U380" s="1"/>
       <c r="V380" s="1"/>
       <c r="W380" s="1"/>
@@ -26096,7 +26301,7 @@
       <c r="Q381" s="1"/>
       <c r="R381" s="1"/>
       <c r="S381" s="1"/>
-      <c r="T381" s="1"/>
+      <c r="T381" s="33"/>
       <c r="U381" s="1"/>
       <c r="V381" s="1"/>
       <c r="W381" s="1"/>
@@ -26150,7 +26355,7 @@
       <c r="Q382" s="1"/>
       <c r="R382" s="1"/>
       <c r="S382" s="1"/>
-      <c r="T382" s="1"/>
+      <c r="T382" s="33"/>
       <c r="U382" s="1"/>
       <c r="V382" s="1"/>
       <c r="W382" s="1"/>
@@ -26204,7 +26409,7 @@
       <c r="Q383" s="1"/>
       <c r="R383" s="1"/>
       <c r="S383" s="1"/>
-      <c r="T383" s="1"/>
+      <c r="T383" s="33"/>
       <c r="U383" s="1"/>
       <c r="V383" s="1"/>
       <c r="W383" s="1"/>
@@ -26258,7 +26463,7 @@
       <c r="Q384" s="1"/>
       <c r="R384" s="1"/>
       <c r="S384" s="1"/>
-      <c r="T384" s="1"/>
+      <c r="T384" s="33"/>
       <c r="U384" s="1"/>
       <c r="V384" s="1"/>
       <c r="W384" s="1"/>
@@ -26312,7 +26517,7 @@
       <c r="Q385" s="1"/>
       <c r="R385" s="1"/>
       <c r="S385" s="1"/>
-      <c r="T385" s="1"/>
+      <c r="T385" s="33"/>
       <c r="U385" s="1"/>
       <c r="V385" s="1"/>
       <c r="W385" s="1"/>
@@ -26366,7 +26571,7 @@
       <c r="Q386" s="1"/>
       <c r="R386" s="1"/>
       <c r="S386" s="1"/>
-      <c r="T386" s="1"/>
+      <c r="T386" s="33"/>
       <c r="U386" s="1"/>
       <c r="V386" s="1"/>
       <c r="W386" s="1"/>
@@ -26420,7 +26625,7 @@
       <c r="Q387" s="1"/>
       <c r="R387" s="1"/>
       <c r="S387" s="1"/>
-      <c r="T387" s="1"/>
+      <c r="T387" s="33"/>
       <c r="U387" s="1"/>
       <c r="V387" s="1"/>
       <c r="W387" s="1"/>
@@ -26474,7 +26679,7 @@
       <c r="Q388" s="1"/>
       <c r="R388" s="1"/>
       <c r="S388" s="1"/>
-      <c r="T388" s="1"/>
+      <c r="T388" s="33"/>
       <c r="U388" s="1"/>
       <c r="V388" s="1"/>
       <c r="W388" s="1"/>
@@ -26528,7 +26733,7 @@
       <c r="Q389" s="1"/>
       <c r="R389" s="1"/>
       <c r="S389" s="1"/>
-      <c r="T389" s="1"/>
+      <c r="T389" s="33"/>
       <c r="U389" s="1"/>
       <c r="V389" s="1"/>
       <c r="W389" s="1"/>
@@ -26582,7 +26787,7 @@
       <c r="Q390" s="1"/>
       <c r="R390" s="1"/>
       <c r="S390" s="1"/>
-      <c r="T390" s="1"/>
+      <c r="T390" s="33"/>
       <c r="U390" s="1"/>
       <c r="V390" s="1"/>
       <c r="W390" s="1"/>
@@ -26636,7 +26841,7 @@
       <c r="Q391" s="1"/>
       <c r="R391" s="1"/>
       <c r="S391" s="1"/>
-      <c r="T391" s="1"/>
+      <c r="T391" s="33"/>
       <c r="U391" s="1"/>
       <c r="V391" s="1"/>
       <c r="W391" s="1"/>
@@ -26690,7 +26895,7 @@
       <c r="Q392" s="1"/>
       <c r="R392" s="1"/>
       <c r="S392" s="1"/>
-      <c r="T392" s="1"/>
+      <c r="T392" s="33"/>
       <c r="U392" s="1"/>
       <c r="V392" s="1"/>
       <c r="W392" s="1"/>
@@ -26744,7 +26949,7 @@
       <c r="Q393" s="1"/>
       <c r="R393" s="1"/>
       <c r="S393" s="1"/>
-      <c r="T393" s="1"/>
+      <c r="T393" s="33"/>
       <c r="U393" s="1"/>
       <c r="V393" s="1"/>
       <c r="W393" s="1"/>
@@ -26798,7 +27003,7 @@
       <c r="Q394" s="1"/>
       <c r="R394" s="1"/>
       <c r="S394" s="1"/>
-      <c r="T394" s="1"/>
+      <c r="T394" s="33"/>
       <c r="U394" s="1"/>
       <c r="V394" s="1"/>
       <c r="W394" s="1"/>
@@ -26852,7 +27057,7 @@
       <c r="Q395" s="1"/>
       <c r="R395" s="1"/>
       <c r="S395" s="1"/>
-      <c r="T395" s="1"/>
+      <c r="T395" s="33"/>
       <c r="U395" s="1"/>
       <c r="V395" s="1"/>
       <c r="W395" s="1"/>
@@ -26906,7 +27111,7 @@
       <c r="Q396" s="1"/>
       <c r="R396" s="1"/>
       <c r="S396" s="1"/>
-      <c r="T396" s="1"/>
+      <c r="T396" s="33"/>
       <c r="U396" s="1"/>
       <c r="V396" s="1"/>
       <c r="W396" s="1"/>
@@ -26960,7 +27165,7 @@
       <c r="Q397" s="1"/>
       <c r="R397" s="1"/>
       <c r="S397" s="1"/>
-      <c r="T397" s="1"/>
+      <c r="T397" s="33"/>
       <c r="U397" s="1"/>
       <c r="V397" s="1"/>
       <c r="W397" s="1"/>
@@ -27014,7 +27219,7 @@
       <c r="Q398" s="1"/>
       <c r="R398" s="1"/>
       <c r="S398" s="1"/>
-      <c r="T398" s="1"/>
+      <c r="T398" s="33"/>
       <c r="U398" s="1"/>
       <c r="V398" s="1"/>
       <c r="W398" s="1"/>
@@ -27068,7 +27273,7 @@
       <c r="Q399" s="1"/>
       <c r="R399" s="1"/>
       <c r="S399" s="1"/>
-      <c r="T399" s="1"/>
+      <c r="T399" s="33"/>
       <c r="U399" s="1"/>
       <c r="V399" s="1"/>
       <c r="W399" s="1"/>
@@ -27122,7 +27327,7 @@
       <c r="Q400" s="1"/>
       <c r="R400" s="1"/>
       <c r="S400" s="1"/>
-      <c r="T400" s="1"/>
+      <c r="T400" s="33"/>
       <c r="U400" s="1"/>
       <c r="V400" s="1"/>
       <c r="W400" s="1"/>
@@ -27176,7 +27381,7 @@
       <c r="Q401" s="1"/>
       <c r="R401" s="1"/>
       <c r="S401" s="1"/>
-      <c r="T401" s="1"/>
+      <c r="T401" s="33"/>
       <c r="U401" s="1"/>
       <c r="V401" s="1"/>
       <c r="W401" s="1"/>
@@ -27230,7 +27435,7 @@
       <c r="Q402" s="1"/>
       <c r="R402" s="1"/>
       <c r="S402" s="1"/>
-      <c r="T402" s="1"/>
+      <c r="T402" s="33"/>
       <c r="U402" s="1"/>
       <c r="V402" s="1"/>
       <c r="W402" s="1"/>
@@ -27284,7 +27489,7 @@
       <c r="Q403" s="1"/>
       <c r="R403" s="1"/>
       <c r="S403" s="1"/>
-      <c r="T403" s="1"/>
+      <c r="T403" s="33"/>
       <c r="U403" s="1"/>
       <c r="V403" s="1"/>
       <c r="W403" s="1"/>
@@ -27338,7 +27543,7 @@
       <c r="Q404" s="1"/>
       <c r="R404" s="1"/>
       <c r="S404" s="1"/>
-      <c r="T404" s="1"/>
+      <c r="T404" s="33"/>
       <c r="U404" s="1"/>
       <c r="V404" s="1"/>
       <c r="W404" s="1"/>
@@ -27392,7 +27597,7 @@
       <c r="Q405" s="1"/>
       <c r="R405" s="1"/>
       <c r="S405" s="1"/>
-      <c r="T405" s="1"/>
+      <c r="T405" s="33"/>
       <c r="U405" s="1"/>
       <c r="V405" s="1"/>
       <c r="W405" s="1"/>
@@ -27446,7 +27651,7 @@
       <c r="Q406" s="1"/>
       <c r="R406" s="1"/>
       <c r="S406" s="1"/>
-      <c r="T406" s="1"/>
+      <c r="T406" s="33"/>
       <c r="U406" s="1"/>
       <c r="V406" s="1"/>
       <c r="W406" s="1"/>
@@ -27500,7 +27705,7 @@
       <c r="Q407" s="1"/>
       <c r="R407" s="1"/>
       <c r="S407" s="1"/>
-      <c r="T407" s="1"/>
+      <c r="T407" s="33"/>
       <c r="U407" s="1"/>
       <c r="V407" s="1"/>
       <c r="W407" s="1"/>
@@ -27554,7 +27759,7 @@
       <c r="Q408" s="1"/>
       <c r="R408" s="1"/>
       <c r="S408" s="1"/>
-      <c r="T408" s="1"/>
+      <c r="T408" s="33"/>
       <c r="U408" s="1"/>
       <c r="V408" s="1"/>
       <c r="W408" s="1"/>
@@ -27608,7 +27813,7 @@
       <c r="Q409" s="1"/>
       <c r="R409" s="1"/>
       <c r="S409" s="1"/>
-      <c r="T409" s="1"/>
+      <c r="T409" s="33"/>
       <c r="U409" s="1"/>
       <c r="V409" s="1"/>
       <c r="W409" s="1"/>
@@ -27662,7 +27867,7 @@
       <c r="Q410" s="1"/>
       <c r="R410" s="1"/>
       <c r="S410" s="1"/>
-      <c r="T410" s="1"/>
+      <c r="T410" s="33"/>
       <c r="U410" s="1"/>
       <c r="V410" s="1"/>
       <c r="W410" s="1"/>
@@ -27716,7 +27921,7 @@
       <c r="Q411" s="1"/>
       <c r="R411" s="1"/>
       <c r="S411" s="1"/>
-      <c r="T411" s="1"/>
+      <c r="T411" s="33"/>
       <c r="U411" s="1"/>
       <c r="V411" s="1"/>
       <c r="W411" s="1"/>
@@ -27770,7 +27975,7 @@
       <c r="Q412" s="1"/>
       <c r="R412" s="1"/>
       <c r="S412" s="1"/>
-      <c r="T412" s="1"/>
+      <c r="T412" s="33"/>
       <c r="U412" s="1"/>
       <c r="V412" s="1"/>
       <c r="W412" s="1"/>
@@ -27824,7 +28029,7 @@
       <c r="Q413" s="1"/>
       <c r="R413" s="1"/>
       <c r="S413" s="1"/>
-      <c r="T413" s="1"/>
+      <c r="T413" s="33"/>
       <c r="U413" s="1"/>
       <c r="V413" s="1"/>
       <c r="W413" s="1"/>
@@ -27878,7 +28083,7 @@
       <c r="Q414" s="1"/>
       <c r="R414" s="1"/>
       <c r="S414" s="1"/>
-      <c r="T414" s="1"/>
+      <c r="T414" s="33"/>
       <c r="U414" s="1"/>
       <c r="V414" s="1"/>
       <c r="W414" s="1"/>
@@ -27932,7 +28137,7 @@
       <c r="Q415" s="1"/>
       <c r="R415" s="1"/>
       <c r="S415" s="1"/>
-      <c r="T415" s="1"/>
+      <c r="T415" s="33"/>
       <c r="U415" s="1"/>
       <c r="V415" s="1"/>
       <c r="W415" s="1"/>
@@ -27986,7 +28191,7 @@
       <c r="Q416" s="1"/>
       <c r="R416" s="1"/>
       <c r="S416" s="1"/>
-      <c r="T416" s="1"/>
+      <c r="T416" s="33"/>
       <c r="U416" s="1"/>
       <c r="V416" s="1"/>
       <c r="W416" s="1"/>
@@ -28040,7 +28245,7 @@
       <c r="Q417" s="1"/>
       <c r="R417" s="1"/>
       <c r="S417" s="1"/>
-      <c r="T417" s="1"/>
+      <c r="T417" s="33"/>
       <c r="U417" s="1"/>
       <c r="V417" s="1"/>
       <c r="W417" s="1"/>
@@ -28094,7 +28299,7 @@
       <c r="Q418" s="1"/>
       <c r="R418" s="1"/>
       <c r="S418" s="1"/>
-      <c r="T418" s="1"/>
+      <c r="T418" s="33"/>
       <c r="U418" s="1"/>
       <c r="V418" s="1"/>
       <c r="W418" s="1"/>
@@ -28148,7 +28353,7 @@
       <c r="Q419" s="1"/>
       <c r="R419" s="1"/>
       <c r="S419" s="1"/>
-      <c r="T419" s="1"/>
+      <c r="T419" s="33"/>
       <c r="U419" s="1"/>
       <c r="V419" s="1"/>
       <c r="W419" s="1"/>
@@ -28202,7 +28407,7 @@
       <c r="Q420" s="1"/>
       <c r="R420" s="1"/>
       <c r="S420" s="1"/>
-      <c r="T420" s="1"/>
+      <c r="T420" s="33"/>
       <c r="U420" s="1"/>
       <c r="V420" s="1"/>
       <c r="W420" s="1"/>
@@ -28256,7 +28461,7 @@
       <c r="Q421" s="1"/>
       <c r="R421" s="1"/>
       <c r="S421" s="1"/>
-      <c r="T421" s="1"/>
+      <c r="T421" s="33"/>
       <c r="U421" s="1"/>
       <c r="V421" s="1"/>
       <c r="W421" s="1"/>
@@ -28310,7 +28515,7 @@
       <c r="Q422" s="1"/>
       <c r="R422" s="1"/>
       <c r="S422" s="1"/>
-      <c r="T422" s="1"/>
+      <c r="T422" s="33"/>
       <c r="U422" s="1"/>
       <c r="V422" s="1"/>
       <c r="W422" s="1"/>
@@ -28364,7 +28569,7 @@
       <c r="Q423" s="1"/>
       <c r="R423" s="1"/>
       <c r="S423" s="1"/>
-      <c r="T423" s="1"/>
+      <c r="T423" s="33"/>
       <c r="U423" s="1"/>
       <c r="V423" s="1"/>
       <c r="W423" s="1"/>
@@ -28418,7 +28623,7 @@
       <c r="Q424" s="1"/>
       <c r="R424" s="1"/>
       <c r="S424" s="1"/>
-      <c r="T424" s="1"/>
+      <c r="T424" s="33"/>
       <c r="U424" s="1"/>
       <c r="V424" s="1"/>
       <c r="W424" s="1"/>
@@ -28472,7 +28677,7 @@
       <c r="Q425" s="1"/>
       <c r="R425" s="1"/>
       <c r="S425" s="1"/>
-      <c r="T425" s="1"/>
+      <c r="T425" s="33"/>
       <c r="U425" s="1"/>
       <c r="V425" s="1"/>
       <c r="W425" s="1"/>
@@ -28526,7 +28731,7 @@
       <c r="Q426" s="1"/>
       <c r="R426" s="1"/>
       <c r="S426" s="1"/>
-      <c r="T426" s="1"/>
+      <c r="T426" s="33"/>
       <c r="U426" s="1"/>
       <c r="V426" s="1"/>
       <c r="W426" s="1"/>
@@ -28580,7 +28785,7 @@
       <c r="Q427" s="1"/>
       <c r="R427" s="1"/>
       <c r="S427" s="1"/>
-      <c r="T427" s="1"/>
+      <c r="T427" s="33"/>
       <c r="U427" s="1"/>
       <c r="V427" s="1"/>
       <c r="W427" s="1"/>
@@ -28634,7 +28839,7 @@
       <c r="Q428" s="1"/>
       <c r="R428" s="1"/>
       <c r="S428" s="1"/>
-      <c r="T428" s="1"/>
+      <c r="T428" s="33"/>
       <c r="U428" s="1"/>
       <c r="V428" s="1"/>
       <c r="W428" s="1"/>
@@ -28688,7 +28893,7 @@
       <c r="Q429" s="1"/>
       <c r="R429" s="1"/>
       <c r="S429" s="1"/>
-      <c r="T429" s="1"/>
+      <c r="T429" s="33"/>
       <c r="U429" s="1"/>
       <c r="V429" s="1"/>
       <c r="W429" s="1"/>
@@ -28742,7 +28947,7 @@
       <c r="Q430" s="1"/>
       <c r="R430" s="1"/>
       <c r="S430" s="1"/>
-      <c r="T430" s="1"/>
+      <c r="T430" s="33"/>
       <c r="U430" s="1"/>
       <c r="V430" s="1"/>
       <c r="W430" s="1"/>
@@ -28796,7 +29001,7 @@
       <c r="Q431" s="1"/>
       <c r="R431" s="1"/>
       <c r="S431" s="1"/>
-      <c r="T431" s="1"/>
+      <c r="T431" s="33"/>
       <c r="U431" s="1"/>
       <c r="V431" s="1"/>
       <c r="W431" s="1"/>
@@ -28850,7 +29055,7 @@
       <c r="Q432" s="1"/>
       <c r="R432" s="1"/>
       <c r="S432" s="1"/>
-      <c r="T432" s="1"/>
+      <c r="T432" s="33"/>
       <c r="U432" s="1"/>
       <c r="V432" s="1"/>
       <c r="W432" s="1"/>
@@ -28904,7 +29109,7 @@
       <c r="Q433" s="1"/>
       <c r="R433" s="1"/>
       <c r="S433" s="1"/>
-      <c r="T433" s="1"/>
+      <c r="T433" s="33"/>
       <c r="U433" s="1"/>
       <c r="V433" s="1"/>
       <c r="W433" s="1"/>
@@ -28958,7 +29163,7 @@
       <c r="Q434" s="1"/>
       <c r="R434" s="1"/>
       <c r="S434" s="1"/>
-      <c r="T434" s="1"/>
+      <c r="T434" s="33"/>
       <c r="U434" s="1"/>
       <c r="V434" s="1"/>
       <c r="W434" s="1"/>
@@ -29012,7 +29217,7 @@
       <c r="Q435" s="1"/>
       <c r="R435" s="1"/>
       <c r="S435" s="1"/>
-      <c r="T435" s="1"/>
+      <c r="T435" s="33"/>
       <c r="U435" s="1"/>
       <c r="V435" s="1"/>
       <c r="W435" s="1"/>
@@ -29066,7 +29271,7 @@
       <c r="Q436" s="1"/>
       <c r="R436" s="1"/>
       <c r="S436" s="1"/>
-      <c r="T436" s="1"/>
+      <c r="T436" s="33"/>
       <c r="U436" s="1"/>
       <c r="V436" s="1"/>
       <c r="W436" s="1"/>
@@ -29120,7 +29325,7 @@
       <c r="Q437" s="1"/>
       <c r="R437" s="1"/>
       <c r="S437" s="1"/>
-      <c r="T437" s="1"/>
+      <c r="T437" s="33"/>
       <c r="U437" s="1"/>
       <c r="V437" s="1"/>
       <c r="W437" s="1"/>
@@ -29174,7 +29379,7 @@
       <c r="Q438" s="1"/>
       <c r="R438" s="1"/>
       <c r="S438" s="1"/>
-      <c r="T438" s="1"/>
+      <c r="T438" s="33"/>
       <c r="U438" s="1"/>
       <c r="V438" s="1"/>
       <c r="W438" s="1"/>
@@ -29228,7 +29433,7 @@
       <c r="Q439" s="1"/>
       <c r="R439" s="1"/>
       <c r="S439" s="1"/>
-      <c r="T439" s="1"/>
+      <c r="T439" s="33"/>
       <c r="U439" s="1"/>
       <c r="V439" s="1"/>
       <c r="W439" s="1"/>
@@ -29282,7 +29487,7 @@
       <c r="Q440" s="1"/>
       <c r="R440" s="1"/>
       <c r="S440" s="1"/>
-      <c r="T440" s="1"/>
+      <c r="T440" s="33"/>
       <c r="U440" s="1"/>
       <c r="V440" s="1"/>
       <c r="W440" s="1"/>
@@ -29336,7 +29541,7 @@
       <c r="Q441" s="1"/>
       <c r="R441" s="1"/>
       <c r="S441" s="1"/>
-      <c r="T441" s="1"/>
+      <c r="T441" s="33"/>
       <c r="U441" s="1"/>
       <c r="V441" s="1"/>
       <c r="W441" s="1"/>
@@ -29390,7 +29595,7 @@
       <c r="Q442" s="1"/>
       <c r="R442" s="1"/>
       <c r="S442" s="1"/>
-      <c r="T442" s="1"/>
+      <c r="T442" s="33"/>
       <c r="U442" s="1"/>
       <c r="V442" s="1"/>
       <c r="W442" s="1"/>
@@ -29444,7 +29649,7 @@
       <c r="Q443" s="1"/>
       <c r="R443" s="1"/>
       <c r="S443" s="1"/>
-      <c r="T443" s="1"/>
+      <c r="T443" s="33"/>
       <c r="U443" s="1"/>
       <c r="V443" s="1"/>
       <c r="W443" s="1"/>
@@ -29498,7 +29703,7 @@
       <c r="Q444" s="1"/>
       <c r="R444" s="1"/>
       <c r="S444" s="1"/>
-      <c r="T444" s="1"/>
+      <c r="T444" s="33"/>
       <c r="U444" s="1"/>
       <c r="V444" s="1"/>
       <c r="W444" s="1"/>
@@ -29552,7 +29757,7 @@
       <c r="Q445" s="1"/>
       <c r="R445" s="1"/>
       <c r="S445" s="1"/>
-      <c r="T445" s="1"/>
+      <c r="T445" s="33"/>
       <c r="U445" s="1"/>
       <c r="V445" s="1"/>
       <c r="W445" s="1"/>
@@ -29606,7 +29811,7 @@
       <c r="Q446" s="1"/>
       <c r="R446" s="1"/>
       <c r="S446" s="1"/>
-      <c r="T446" s="1"/>
+      <c r="T446" s="33"/>
       <c r="U446" s="1"/>
       <c r="V446" s="1"/>
       <c r="W446" s="1"/>
@@ -29660,7 +29865,7 @@
       <c r="Q447" s="1"/>
       <c r="R447" s="1"/>
       <c r="S447" s="1"/>
-      <c r="T447" s="1"/>
+      <c r="T447" s="33"/>
       <c r="U447" s="1"/>
       <c r="V447" s="1"/>
       <c r="W447" s="1"/>
@@ -29714,7 +29919,7 @@
       <c r="Q448" s="1"/>
       <c r="R448" s="1"/>
       <c r="S448" s="1"/>
-      <c r="T448" s="1"/>
+      <c r="T448" s="33"/>
       <c r="U448" s="1"/>
       <c r="V448" s="1"/>
       <c r="W448" s="1"/>
@@ -29768,7 +29973,7 @@
       <c r="Q449" s="1"/>
       <c r="R449" s="1"/>
       <c r="S449" s="1"/>
-      <c r="T449" s="1"/>
+      <c r="T449" s="33"/>
       <c r="U449" s="1"/>
       <c r="V449" s="1"/>
       <c r="W449" s="1"/>
@@ -29822,7 +30027,7 @@
       <c r="Q450" s="1"/>
       <c r="R450" s="1"/>
       <c r="S450" s="1"/>
-      <c r="T450" s="1"/>
+      <c r="T450" s="33"/>
       <c r="U450" s="1"/>
       <c r="V450" s="1"/>
       <c r="W450" s="1"/>
@@ -29876,7 +30081,7 @@
       <c r="Q451" s="1"/>
       <c r="R451" s="1"/>
       <c r="S451" s="1"/>
-      <c r="T451" s="1"/>
+      <c r="T451" s="33"/>
       <c r="U451" s="1"/>
       <c r="V451" s="1"/>
       <c r="W451" s="1"/>
@@ -29930,7 +30135,7 @@
       <c r="Q452" s="1"/>
       <c r="R452" s="1"/>
       <c r="S452" s="1"/>
-      <c r="T452" s="1"/>
+      <c r="T452" s="33"/>
       <c r="U452" s="1"/>
       <c r="V452" s="1"/>
       <c r="W452" s="1"/>
@@ -29984,7 +30189,7 @@
       <c r="Q453" s="1"/>
       <c r="R453" s="1"/>
       <c r="S453" s="1"/>
-      <c r="T453" s="1"/>
+      <c r="T453" s="33"/>
       <c r="U453" s="1"/>
       <c r="V453" s="1"/>
       <c r="W453" s="1"/>
@@ -30038,7 +30243,7 @@
       <c r="Q454" s="1"/>
       <c r="R454" s="1"/>
       <c r="S454" s="1"/>
-      <c r="T454" s="1"/>
+      <c r="T454" s="33"/>
       <c r="U454" s="1"/>
       <c r="V454" s="1"/>
       <c r="W454" s="1"/>
@@ -30092,7 +30297,7 @@
       <c r="Q455" s="1"/>
       <c r="R455" s="1"/>
       <c r="S455" s="1"/>
-      <c r="T455" s="1"/>
+      <c r="T455" s="33"/>
       <c r="U455" s="1"/>
       <c r="V455" s="1"/>
       <c r="W455" s="1"/>
@@ -30146,7 +30351,7 @@
       <c r="Q456" s="1"/>
       <c r="R456" s="1"/>
       <c r="S456" s="1"/>
-      <c r="T456" s="1"/>
+      <c r="T456" s="33"/>
       <c r="U456" s="1"/>
       <c r="V456" s="1"/>
       <c r="W456" s="1"/>
@@ -30200,7 +30405,7 @@
       <c r="Q457" s="1"/>
       <c r="R457" s="1"/>
       <c r="S457" s="1"/>
-      <c r="T457" s="1"/>
+      <c r="T457" s="33"/>
       <c r="U457" s="1"/>
       <c r="V457" s="1"/>
       <c r="W457" s="1"/>
@@ -30254,7 +30459,7 @@
       <c r="Q458" s="1"/>
       <c r="R458" s="1"/>
       <c r="S458" s="1"/>
-      <c r="T458" s="1"/>
+      <c r="T458" s="33"/>
       <c r="U458" s="1"/>
       <c r="V458" s="1"/>
       <c r="W458" s="1"/>
@@ -30308,7 +30513,7 @@
       <c r="Q459" s="1"/>
       <c r="R459" s="1"/>
       <c r="S459" s="1"/>
-      <c r="T459" s="1"/>
+      <c r="T459" s="33"/>
       <c r="U459" s="1"/>
       <c r="V459" s="1"/>
       <c r="W459" s="1"/>
@@ -30362,7 +30567,7 @@
       <c r="Q460" s="1"/>
       <c r="R460" s="1"/>
       <c r="S460" s="1"/>
-      <c r="T460" s="1"/>
+      <c r="T460" s="33"/>
       <c r="U460" s="1"/>
       <c r="V460" s="1"/>
       <c r="W460" s="1"/>
@@ -30416,7 +30621,7 @@
       <c r="Q461" s="1"/>
       <c r="R461" s="1"/>
       <c r="S461" s="1"/>
-      <c r="T461" s="1"/>
+      <c r="T461" s="33"/>
       <c r="U461" s="1"/>
       <c r="V461" s="1"/>
       <c r="W461" s="1"/>
@@ -30470,7 +30675,7 @@
       <c r="Q462" s="1"/>
       <c r="R462" s="1"/>
       <c r="S462" s="1"/>
-      <c r="T462" s="1"/>
+      <c r="T462" s="33"/>
       <c r="U462" s="1"/>
       <c r="V462" s="1"/>
       <c r="W462" s="1"/>
@@ -30524,7 +30729,7 @@
       <c r="Q463" s="1"/>
       <c r="R463" s="1"/>
       <c r="S463" s="1"/>
-      <c r="T463" s="1"/>
+      <c r="T463" s="33"/>
       <c r="U463" s="1"/>
       <c r="V463" s="1"/>
       <c r="W463" s="1"/>
@@ -30578,7 +30783,7 @@
       <c r="Q464" s="1"/>
       <c r="R464" s="1"/>
       <c r="S464" s="1"/>
-      <c r="T464" s="1"/>
+      <c r="T464" s="33"/>
       <c r="U464" s="1"/>
       <c r="V464" s="1"/>
       <c r="W464" s="1"/>
@@ -30632,7 +30837,7 @@
       <c r="Q465" s="1"/>
       <c r="R465" s="1"/>
       <c r="S465" s="1"/>
-      <c r="T465" s="1"/>
+      <c r="T465" s="33"/>
       <c r="U465" s="1"/>
       <c r="V465" s="1"/>
       <c r="W465" s="1"/>
@@ -30686,7 +30891,7 @@
       <c r="Q466" s="1"/>
       <c r="R466" s="1"/>
       <c r="S466" s="1"/>
-      <c r="T466" s="1"/>
+      <c r="T466" s="33"/>
       <c r="U466" s="1"/>
       <c r="V466" s="1"/>
       <c r="W466" s="1"/>
@@ -30740,7 +30945,7 @@
       <c r="Q467" s="1"/>
       <c r="R467" s="1"/>
       <c r="S467" s="1"/>
-      <c r="T467" s="1"/>
+      <c r="T467" s="33"/>
       <c r="U467" s="1"/>
       <c r="V467" s="1"/>
       <c r="W467" s="1"/>
@@ -30794,7 +30999,7 @@
       <c r="Q468" s="1"/>
       <c r="R468" s="1"/>
       <c r="S468" s="1"/>
-      <c r="T468" s="1"/>
+      <c r="T468" s="33"/>
       <c r="U468" s="1"/>
       <c r="V468" s="1"/>
       <c r="W468" s="1"/>
@@ -30848,7 +31053,7 @@
       <c r="Q469" s="1"/>
       <c r="R469" s="1"/>
       <c r="S469" s="1"/>
-      <c r="T469" s="1"/>
+      <c r="T469" s="33"/>
       <c r="U469" s="1"/>
       <c r="V469" s="1"/>
       <c r="W469" s="1"/>
@@ -30902,7 +31107,7 @@
       <c r="Q470" s="1"/>
       <c r="R470" s="1"/>
       <c r="S470" s="1"/>
-      <c r="T470" s="1"/>
+      <c r="T470" s="33"/>
       <c r="U470" s="1"/>
       <c r="V470" s="1"/>
       <c r="W470" s="1"/>
@@ -30956,7 +31161,7 @@
       <c r="Q471" s="1"/>
       <c r="R471" s="1"/>
       <c r="S471" s="1"/>
-      <c r="T471" s="1"/>
+      <c r="T471" s="33"/>
       <c r="U471" s="1"/>
       <c r="V471" s="1"/>
       <c r="W471" s="1"/>
@@ -31010,7 +31215,7 @@
       <c r="Q472" s="1"/>
       <c r="R472" s="1"/>
       <c r="S472" s="1"/>
-      <c r="T472" s="1"/>
+      <c r="T472" s="33"/>
       <c r="U472" s="1"/>
       <c r="V472" s="1"/>
       <c r="W472" s="1"/>
@@ -31064,7 +31269,7 @@
       <c r="Q473" s="1"/>
       <c r="R473" s="1"/>
       <c r="S473" s="1"/>
-      <c r="T473" s="1"/>
+      <c r="T473" s="33"/>
       <c r="U473" s="1"/>
       <c r="V473" s="1"/>
       <c r="W473" s="1"/>
@@ -31118,7 +31323,7 @@
       <c r="Q474" s="1"/>
       <c r="R474" s="1"/>
       <c r="S474" s="1"/>
-      <c r="T474" s="1"/>
+      <c r="T474" s="33"/>
       <c r="U474" s="1"/>
       <c r="V474" s="1"/>
       <c r="W474" s="1"/>
@@ -31172,7 +31377,7 @@
       <c r="Q475" s="1"/>
       <c r="R475" s="1"/>
       <c r="S475" s="1"/>
-      <c r="T475" s="1"/>
+      <c r="T475" s="33"/>
       <c r="U475" s="1"/>
       <c r="V475" s="1"/>
       <c r="W475" s="1"/>
@@ -31226,7 +31431,7 @@
       <c r="Q476" s="1"/>
       <c r="R476" s="1"/>
       <c r="S476" s="1"/>
-      <c r="T476" s="1"/>
+      <c r="T476" s="33"/>
       <c r="U476" s="1"/>
       <c r="V476" s="1"/>
       <c r="W476" s="1"/>
@@ -31280,7 +31485,7 @@
       <c r="Q477" s="1"/>
       <c r="R477" s="1"/>
       <c r="S477" s="1"/>
-      <c r="T477" s="1"/>
+      <c r="T477" s="33"/>
       <c r="U477" s="1"/>
       <c r="V477" s="1"/>
       <c r="W477" s="1"/>
@@ -31334,7 +31539,7 @@
       <c r="Q478" s="1"/>
       <c r="R478" s="1"/>
       <c r="S478" s="1"/>
-      <c r="T478" s="1"/>
+      <c r="T478" s="33"/>
       <c r="U478" s="1"/>
       <c r="V478" s="1"/>
       <c r="W478" s="1"/>
@@ -31388,7 +31593,7 @@
       <c r="Q479" s="1"/>
       <c r="R479" s="1"/>
       <c r="S479" s="1"/>
-      <c r="T479" s="1"/>
+      <c r="T479" s="33"/>
       <c r="U479" s="1"/>
       <c r="V479" s="1"/>
       <c r="W479" s="1"/>
@@ -31442,7 +31647,7 @@
       <c r="Q480" s="1"/>
       <c r="R480" s="1"/>
       <c r="S480" s="1"/>
-      <c r="T480" s="1"/>
+      <c r="T480" s="33"/>
       <c r="U480" s="1"/>
       <c r="V480" s="1"/>
       <c r="W480" s="1"/>
@@ -31496,7 +31701,7 @@
       <c r="Q481" s="1"/>
       <c r="R481" s="1"/>
       <c r="S481" s="1"/>
-      <c r="T481" s="1"/>
+      <c r="T481" s="33"/>
       <c r="U481" s="1"/>
       <c r="V481" s="1"/>
       <c r="W481" s="1"/>
@@ -31550,7 +31755,7 @@
       <c r="Q482" s="1"/>
       <c r="R482" s="1"/>
       <c r="S482" s="1"/>
-      <c r="T482" s="1"/>
+      <c r="T482" s="33"/>
       <c r="U482" s="1"/>
       <c r="V482" s="1"/>
       <c r="W482" s="1"/>
@@ -31604,7 +31809,7 @@
       <c r="Q483" s="1"/>
       <c r="R483" s="1"/>
       <c r="S483" s="1"/>
-      <c r="T483" s="1"/>
+      <c r="T483" s="33"/>
       <c r="U483" s="1"/>
       <c r="V483" s="1"/>
       <c r="W483" s="1"/>
@@ -31658,7 +31863,7 @@
       <c r="Q484" s="1"/>
       <c r="R484" s="1"/>
       <c r="S484" s="1"/>
-      <c r="T484" s="1"/>
+      <c r="T484" s="33"/>
       <c r="U484" s="1"/>
       <c r="V484" s="1"/>
       <c r="W484" s="1"/>
@@ -31712,7 +31917,7 @@
       <c r="Q485" s="1"/>
       <c r="R485" s="1"/>
       <c r="S485" s="1"/>
-      <c r="T485" s="1"/>
+      <c r="T485" s="33"/>
       <c r="U485" s="1"/>
       <c r="V485" s="1"/>
       <c r="W485" s="1"/>
@@ -31766,7 +31971,7 @@
       <c r="Q486" s="1"/>
       <c r="R486" s="1"/>
       <c r="S486" s="1"/>
-      <c r="T486" s="1"/>
+      <c r="T486" s="33"/>
       <c r="U486" s="1"/>
       <c r="V486" s="1"/>
       <c r="W486" s="1"/>
@@ -31820,7 +32025,7 @@
       <c r="Q487" s="1"/>
       <c r="R487" s="1"/>
       <c r="S487" s="1"/>
-      <c r="T487" s="1"/>
+      <c r="T487" s="33"/>
       <c r="U487" s="1"/>
       <c r="V487" s="1"/>
       <c r="W487" s="1"/>
@@ -31874,7 +32079,7 @@
       <c r="Q488" s="1"/>
       <c r="R488" s="1"/>
       <c r="S488" s="1"/>
-      <c r="T488" s="1"/>
+      <c r="T488" s="33"/>
       <c r="U488" s="1"/>
       <c r="V488" s="1"/>
       <c r="W488" s="1"/>
@@ -31928,7 +32133,7 @@
       <c r="Q489" s="1"/>
       <c r="R489" s="1"/>
       <c r="S489" s="1"/>
-      <c r="T489" s="1"/>
+      <c r="T489" s="33"/>
       <c r="U489" s="1"/>
       <c r="V489" s="1"/>
       <c r="W489" s="1"/>
@@ -31982,7 +32187,7 @@
       <c r="Q490" s="1"/>
       <c r="R490" s="1"/>
       <c r="S490" s="1"/>
-      <c r="T490" s="1"/>
+      <c r="T490" s="33"/>
       <c r="U490" s="1"/>
       <c r="V490" s="1"/>
       <c r="W490" s="1"/>
@@ -32036,7 +32241,7 @@
       <c r="Q491" s="1"/>
       <c r="R491" s="1"/>
       <c r="S491" s="1"/>
-      <c r="T491" s="1"/>
+      <c r="T491" s="33"/>
       <c r="U491" s="1"/>
       <c r="V491" s="1"/>
       <c r="W491" s="1"/>
@@ -32090,7 +32295,7 @@
       <c r="Q492" s="1"/>
       <c r="R492" s="1"/>
       <c r="S492" s="1"/>
-      <c r="T492" s="1"/>
+      <c r="T492" s="33"/>
       <c r="U492" s="1"/>
       <c r="V492" s="1"/>
       <c r="W492" s="1"/>
@@ -32144,7 +32349,7 @@
       <c r="Q493" s="1"/>
       <c r="R493" s="1"/>
       <c r="S493" s="1"/>
-      <c r="T493" s="1"/>
+      <c r="T493" s="33"/>
       <c r="U493" s="1"/>
       <c r="V493" s="1"/>
       <c r="W493" s="1"/>
@@ -32198,7 +32403,7 @@
       <c r="Q494" s="1"/>
       <c r="R494" s="1"/>
       <c r="S494" s="1"/>
-      <c r="T494" s="1"/>
+      <c r="T494" s="33"/>
       <c r="U494" s="1"/>
       <c r="V494" s="1"/>
       <c r="W494" s="1"/>
@@ -32252,7 +32457,7 @@
       <c r="Q495" s="1"/>
       <c r="R495" s="1"/>
       <c r="S495" s="1"/>
-      <c r="T495" s="1"/>
+      <c r="T495" s="33"/>
       <c r="U495" s="1"/>
       <c r="V495" s="1"/>
       <c r="W495" s="1"/>
@@ -32306,7 +32511,7 @@
       <c r="Q496" s="1"/>
       <c r="R496" s="1"/>
       <c r="S496" s="1"/>
-      <c r="T496" s="1"/>
+      <c r="T496" s="33"/>
       <c r="U496" s="1"/>
       <c r="V496" s="1"/>
       <c r="W496" s="1"/>
@@ -32360,7 +32565,7 @@
       <c r="Q497" s="1"/>
       <c r="R497" s="1"/>
       <c r="S497" s="1"/>
-      <c r="T497" s="1"/>
+      <c r="T497" s="33"/>
       <c r="U497" s="1"/>
       <c r="V497" s="1"/>
       <c r="W497" s="1"/>
@@ -32414,7 +32619,7 @@
       <c r="Q498" s="1"/>
       <c r="R498" s="1"/>
       <c r="S498" s="1"/>
-      <c r="T498" s="1"/>
+      <c r="T498" s="33"/>
       <c r="U498" s="1"/>
       <c r="V498" s="1"/>
       <c r="W498" s="1"/>

--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/06,26/26,06,26 ПОКОМ ЗПФ/Копия дв 250626 бррсч пок зпф от Боярко.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/06,26/26,06,26 ПОКОМ ЗПФ/Копия дв 250626 бррсч пок зпф от Боярко.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\06,26\26,06,26 ПОКОМ ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\06,26\26,06,26 ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F3371B7-6E2A-4523-A3DE-C07088A73293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A45315-3B02-46F1-BCFE-4828B472198B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,15 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AK$68</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1997,7 +2005,7 @@
       </c>
       <c r="V10" s="19"/>
       <c r="W10" s="1">
-        <f t="shared" si="3"/>
+        <f>(F10+O10+T10)/P10</f>
         <v>27.17821782178218</v>
       </c>
       <c r="X10" s="1">
